--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_power.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_power.xlsx
@@ -647,10 +647,10 @@
         <v>0.0946214406592598</v>
       </c>
       <c r="X2">
-        <v>0.08422719927330792</v>
+        <v>0.08421680235761825</v>
       </c>
       <c r="Y2">
-        <v>0.01039424138595188</v>
+        <v>0.01040463830164155</v>
       </c>
       <c r="Z2">
         <v>0.3874417493129406</v>
@@ -659,10 +659,10 @@
         <v>0.07811963553753908</v>
       </c>
       <c r="AB2">
-        <v>0.07759362658110296</v>
+        <v>0.07758629188985477</v>
       </c>
       <c r="AC2">
-        <v>0.0005260089564361192</v>
+        <v>0.0005333436476843006</v>
       </c>
       <c r="AD2">
         <v>334.5</v>
@@ -781,10 +781,10 @@
         <v>0.0946214406592598</v>
       </c>
       <c r="X3">
-        <v>0.08422719927330792</v>
+        <v>0.08421680235761825</v>
       </c>
       <c r="Y3">
-        <v>0.01039424138595188</v>
+        <v>0.01040463830164155</v>
       </c>
       <c r="Z3">
         <v>0.3874417493129406</v>
@@ -793,10 +793,10 @@
         <v>0.07811963553753908</v>
       </c>
       <c r="AB3">
-        <v>0.07759362658110296</v>
+        <v>0.07758629188985477</v>
       </c>
       <c r="AC3">
-        <v>0.0005260089564361192</v>
+        <v>0.0005333436476843006</v>
       </c>
       <c r="AD3">
         <v>334.5</v>
@@ -1151,13 +1151,13 @@
         <v>801.2</v>
       </c>
       <c r="L2">
-        <v>1223.18181577091</v>
+        <v>1223.19707140406</v>
       </c>
       <c r="M2">
         <v>1009.5</v>
       </c>
       <c r="N2">
-        <v>1096.98181577091</v>
+        <v>1096.99707140406</v>
       </c>
       <c r="O2">
         <v>334.5</v>
@@ -1166,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.077593626581103</v>
+        <v>0.0775862918898548</v>
       </c>
       <c r="R2">
-        <v>0.07460601801812709</v>
+        <v>0.0745982242224212</v>
       </c>
       <c r="S2">
         <v>0.0617047822134061</v>
       </c>
       <c r="T2">
-        <v>0.0540247822134061</v>
+        <v>0.0529047822134061</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.08422719927330791</v>
+        <v>0.08421680235761821</v>
       </c>
       <c r="X2">
-        <v>0.07460601801812709</v>
+        <v>0.0745982242224212</v>
       </c>
       <c r="Y2">
         <v>0.594295714465122</v>
@@ -1230,7 +1230,7 @@
         <v>801.2</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823122</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07460601801812715</v>
+        <v>0.07459822422242116</v>
       </c>
       <c r="C2">
-        <v>1223.18181577091</v>
+        <v>1223.197071404056</v>
       </c>
       <c r="D2">
-        <v>1096.98181577091</v>
+        <v>1096.997071404056</v>
       </c>
       <c r="E2">
         <v>-334.5</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07460601801812715</v>
+        <v>0.07459822422242116</v>
       </c>
       <c r="T2">
         <v>0.4454993697880389</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07463065380422496</v>
+        <v>0.07461167559611039</v>
       </c>
       <c r="C3">
-        <v>1211.041488235076</v>
+        <v>1211.412213605504</v>
       </c>
       <c r="D3">
-        <v>1096.198488235076</v>
+        <v>1096.569213605504</v>
       </c>
       <c r="E3">
         <v>-323.143</v>
@@ -1533,37 +1533,37 @@
         <v>163.7</v>
       </c>
       <c r="M3">
-        <v>0.7669493144970659</v>
+        <v>0.7510495144970659</v>
       </c>
       <c r="N3">
-        <v>162.9330506855029</v>
+        <v>162.9489504855029</v>
       </c>
       <c r="O3">
-        <v>32.58661013710059</v>
+        <v>32.58979009710059</v>
       </c>
       <c r="P3">
-        <v>130.3464405484023</v>
+        <v>130.3591603884024</v>
       </c>
       <c r="Q3">
-        <v>236.7464405484024</v>
+        <v>236.7591603884024</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07483879392130394</v>
+        <v>0.07483093714543063</v>
       </c>
       <c r="T3">
         <v>0.449099364695417</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>213.4430488504286</v>
+        <v>217.9616614353587</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07465528959032276</v>
+        <v>0.0746251269697996</v>
       </c>
       <c r="C4">
-        <v>1198.902278610539</v>
+        <v>1199.627689428489</v>
       </c>
       <c r="D4">
-        <v>1095.416278610539</v>
+        <v>1096.141689428489</v>
       </c>
       <c r="E4">
         <v>-311.786</v>
@@ -1615,37 +1615,37 @@
         <v>163.7</v>
       </c>
       <c r="M4">
-        <v>1.533898628994132</v>
+        <v>1.502099028994132</v>
       </c>
       <c r="N4">
-        <v>162.1661013710059</v>
+        <v>162.1979009710059</v>
       </c>
       <c r="O4">
-        <v>32.43322027420117</v>
+        <v>32.43958019420117</v>
       </c>
       <c r="P4">
-        <v>129.7328810968047</v>
+        <v>129.7583207768047</v>
       </c>
       <c r="Q4">
-        <v>236.1328810968047</v>
+        <v>236.1583207768047</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07507632035311698</v>
+        <v>0.07506839931176681</v>
       </c>
       <c r="T4">
         <v>0.4527728288866191</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>106.7215244252143</v>
+        <v>108.9808307176793</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07467992537642058</v>
+        <v>0.0746385783434888</v>
       </c>
       <c r="C5">
-        <v>1186.764184505899</v>
+        <v>1187.843498482953</v>
       </c>
       <c r="D5">
-        <v>1094.635184505898</v>
+        <v>1095.714498482953</v>
       </c>
       <c r="E5">
         <v>-300.429</v>
@@ -1697,37 +1697,37 @@
         <v>163.7</v>
       </c>
       <c r="M5">
-        <v>2.300847943491197</v>
+        <v>2.253148543491197</v>
       </c>
       <c r="N5">
-        <v>161.3991520565088</v>
+        <v>161.4468514565088</v>
       </c>
       <c r="O5">
-        <v>32.27983041130176</v>
+        <v>32.28937029130176</v>
       </c>
       <c r="P5">
-        <v>129.119321645207</v>
+        <v>129.157481165207</v>
       </c>
       <c r="Q5">
-        <v>235.5193216452071</v>
+        <v>235.5574811652071</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07531874423713236</v>
+        <v>0.07531075760524394</v>
       </c>
       <c r="T5">
         <v>0.4565220346075367</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>71.14768295014289</v>
+        <v>72.65388714511957</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07470456116251836</v>
+        <v>0.07465202971717803</v>
       </c>
       <c r="C6">
-        <v>1174.627203536567</v>
+        <v>1176.059640379442</v>
       </c>
       <c r="D6">
-        <v>1093.855203536567</v>
+        <v>1095.287640379442</v>
       </c>
       <c r="E6">
         <v>-289.072</v>
@@ -1779,37 +1779,37 @@
         <v>163.7</v>
       </c>
       <c r="M6">
-        <v>3.067797257988264</v>
+        <v>3.004198057988264</v>
       </c>
       <c r="N6">
-        <v>160.6322027420117</v>
+        <v>160.6958019420117</v>
       </c>
       <c r="O6">
-        <v>32.12644054840234</v>
+        <v>32.13916038840235</v>
       </c>
       <c r="P6">
-        <v>128.5057621936094</v>
+        <v>128.5566415536094</v>
       </c>
       <c r="Q6">
-        <v>234.9057621936094</v>
+        <v>234.9566415536094</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07556621861873139</v>
+        <v>0.0755581650298352</v>
       </c>
       <c r="T6">
         <v>0.4603493487809736</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>53.36076221260715</v>
+        <v>54.49041535883966</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07472919694861617</v>
+        <v>0.07466548109086725</v>
       </c>
       <c r="C7">
-        <v>1162.491333324748</v>
+        <v>1164.276114729112</v>
       </c>
       <c r="D7">
-        <v>1093.076333324748</v>
+        <v>1094.861114729112</v>
       </c>
       <c r="E7">
         <v>-277.715</v>
@@ -1861,37 +1861,37 @@
         <v>163.7</v>
       </c>
       <c r="M7">
-        <v>3.834746572485329</v>
+        <v>3.75524757248533</v>
       </c>
       <c r="N7">
-        <v>159.8652534275147</v>
+        <v>159.9447524275147</v>
       </c>
       <c r="O7">
-        <v>31.97305068550293</v>
+        <v>31.98895048550293</v>
       </c>
       <c r="P7">
-        <v>127.8922027420117</v>
+        <v>127.9558019420117</v>
       </c>
       <c r="Q7">
-        <v>234.2922027420118</v>
+        <v>234.3558019420118</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07581890298731145</v>
+        <v>0.07581078103178626</v>
       </c>
       <c r="T7">
         <v>0.4642572379896405</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>42.68860977008573</v>
+        <v>43.59233228707173</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.074753832734714</v>
+        <v>0.07467893246455647</v>
       </c>
       <c r="C8">
-        <v>1150.356571499413</v>
+        <v>1152.492921143724</v>
       </c>
       <c r="D8">
-        <v>1092.298571499413</v>
+        <v>1094.434921143724</v>
       </c>
       <c r="E8">
         <v>-266.358</v>
@@ -1943,37 +1943,37 @@
         <v>163.7</v>
       </c>
       <c r="M8">
-        <v>4.601695886982395</v>
+        <v>4.506297086982395</v>
       </c>
       <c r="N8">
-        <v>159.0983041130176</v>
+        <v>159.1937029130176</v>
       </c>
       <c r="O8">
-        <v>31.81966082260352</v>
+        <v>31.83874058260352</v>
       </c>
       <c r="P8">
-        <v>127.2786432904141</v>
+        <v>127.3549623304141</v>
       </c>
       <c r="Q8">
-        <v>233.6786432904141</v>
+        <v>233.7549623304141</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07607696361905281</v>
+        <v>0.07606877184228948</v>
       </c>
       <c r="T8">
         <v>0.4682482737772154</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.57384147507145</v>
+        <v>36.32694357255979</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.0747784685208118</v>
+        <v>0.07469238383824568</v>
       </c>
       <c r="C9">
-        <v>1138.222915696281</v>
+        <v>1140.710059235643</v>
       </c>
       <c r="D9">
-        <v>1091.521915696281</v>
+        <v>1094.009059235643</v>
       </c>
       <c r="E9">
         <v>-255.001</v>
@@ -2025,37 +2025,37 @@
         <v>163.7</v>
       </c>
       <c r="M9">
-        <v>5.368645201479461</v>
+        <v>5.257346601479462</v>
       </c>
       <c r="N9">
-        <v>158.3313547985205</v>
+        <v>158.4426533985205</v>
       </c>
       <c r="O9">
-        <v>31.66627095970411</v>
+        <v>31.6885306797041</v>
       </c>
       <c r="P9">
-        <v>126.6650838388164</v>
+        <v>126.7541227188164</v>
       </c>
       <c r="Q9">
-        <v>233.0650838388165</v>
+        <v>233.1541227188164</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07634057394179933</v>
+        <v>0.07633231084226588</v>
       </c>
       <c r="T9">
         <v>0.4723251382914047</v>
       </c>
       <c r="U9">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.4918641214898</v>
+        <v>31.13738020505124</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07480310430690962</v>
+        <v>0.07470583521193491</v>
       </c>
       <c r="C10">
-        <v>1126.090363557784</v>
+        <v>1128.927528617837</v>
       </c>
       <c r="D10">
-        <v>1090.746363557784</v>
+        <v>1093.583528617836</v>
       </c>
       <c r="E10">
         <v>-243.644</v>
@@ -2107,37 +2107,37 @@
         <v>163.7</v>
       </c>
       <c r="M10">
-        <v>6.135594515976527</v>
+        <v>6.008396115976527</v>
       </c>
       <c r="N10">
-        <v>157.5644054840235</v>
+        <v>157.6916038840235</v>
       </c>
       <c r="O10">
-        <v>31.51288109680469</v>
+        <v>31.5383207768047</v>
       </c>
       <c r="P10">
-        <v>126.0515243872188</v>
+        <v>126.1532831072188</v>
       </c>
       <c r="Q10">
-        <v>232.4515243872188</v>
+        <v>232.5532831072188</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07660991492373601</v>
+        <v>0.07660157895093742</v>
       </c>
       <c r="T10">
         <v>0.4764906302950329</v>
       </c>
       <c r="U10">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.68038110630358</v>
+        <v>27.24520767941983</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07482774009300741</v>
+        <v>0.07471928658562413</v>
       </c>
       <c r="C11">
-        <v>1113.958912733055</v>
+        <v>1117.145328903875</v>
       </c>
       <c r="D11">
-        <v>1089.971912733055</v>
+        <v>1093.158328903875</v>
       </c>
       <c r="E11">
         <v>-232.287</v>
@@ -2189,37 +2189,37 @@
         <v>163.7</v>
       </c>
       <c r="M11">
-        <v>6.902543830473592</v>
+        <v>6.759445630473592</v>
       </c>
       <c r="N11">
-        <v>156.7974561695264</v>
+        <v>156.9405543695264</v>
       </c>
       <c r="O11">
-        <v>31.35949123390528</v>
+        <v>31.38811087390528</v>
       </c>
       <c r="P11">
-        <v>125.4379649356211</v>
+        <v>125.5524434956211</v>
       </c>
       <c r="Q11">
-        <v>231.8379649356211</v>
+        <v>231.9524434956212</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07688517548769325</v>
+        <v>0.07687676504001932</v>
       </c>
       <c r="T11">
         <v>0.4807476715734661</v>
       </c>
       <c r="U11">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.71589431671429</v>
+        <v>24.21796238170653</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07485237587910522</v>
+        <v>0.07473273795931334</v>
       </c>
       <c r="C12">
-        <v>1101.828560877895</v>
+        <v>1105.363459707928</v>
       </c>
       <c r="D12">
-        <v>1089.198560877895</v>
+        <v>1092.733459707928</v>
       </c>
       <c r="E12">
         <v>-220.93</v>
@@ -2271,37 +2271,37 @@
         <v>163.7</v>
       </c>
       <c r="M12">
-        <v>7.669493144970659</v>
+        <v>7.510495144970659</v>
       </c>
       <c r="N12">
-        <v>156.0305068550293</v>
+        <v>156.1895048550293</v>
       </c>
       <c r="O12">
-        <v>31.20610137100587</v>
+        <v>31.23790097100587</v>
       </c>
       <c r="P12">
-        <v>124.8244054840235</v>
+        <v>124.9516038840235</v>
       </c>
       <c r="Q12">
-        <v>231.2244054840235</v>
+        <v>231.3516038840235</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07716655295307179</v>
+        <v>0.07715806637552527</v>
       </c>
       <c r="T12">
         <v>0.485099313769198</v>
       </c>
       <c r="U12">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.34430488504286</v>
+        <v>21.79616614353587</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07487701166520301</v>
+        <v>0.07474618933300257</v>
       </c>
       <c r="C13">
-        <v>1089.699305654757</v>
+        <v>1093.581920644766</v>
       </c>
       <c r="D13">
-        <v>1088.426305654757</v>
+        <v>1092.308920644766</v>
       </c>
       <c r="E13">
         <v>-209.573</v>
@@ -2353,37 +2353,37 @@
         <v>163.7</v>
       </c>
       <c r="M13">
-        <v>8.436442459467724</v>
+        <v>8.261544659467726</v>
       </c>
       <c r="N13">
-        <v>155.2635575405323</v>
+        <v>155.4384553405323</v>
       </c>
       <c r="O13">
-        <v>31.05271150810646</v>
+        <v>31.08769106810646</v>
       </c>
       <c r="P13">
-        <v>124.2108460324258</v>
+        <v>124.3507642724258</v>
       </c>
       <c r="Q13">
-        <v>230.6108460324259</v>
+        <v>230.7507642724258</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07745425350755994</v>
+        <v>0.07744568908935719</v>
       </c>
       <c r="T13">
         <v>0.4895487456771933</v>
       </c>
       <c r="U13">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.40391353185715</v>
+        <v>19.81469649412352</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07490164745130083</v>
+        <v>0.07475964070669179</v>
       </c>
       <c r="C14">
-        <v>1077.571144732714</v>
+        <v>1081.800711329759</v>
       </c>
       <c r="D14">
-        <v>1087.655144732714</v>
+        <v>1091.884711329759</v>
       </c>
       <c r="E14">
         <v>-198.216</v>
@@ -2435,37 +2435,37 @@
         <v>163.7</v>
       </c>
       <c r="M14">
-        <v>9.203391773964789</v>
+        <v>9.012594173964789</v>
       </c>
       <c r="N14">
-        <v>154.4966082260352</v>
+        <v>154.6874058260352</v>
       </c>
       <c r="O14">
-        <v>30.89932164520704</v>
+        <v>30.93748116520704</v>
       </c>
       <c r="P14">
-        <v>123.5972865808282</v>
+        <v>123.7499246608282</v>
       </c>
       <c r="Q14">
-        <v>229.9972865808282</v>
+        <v>230.1499246608282</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07774849271101375</v>
+        <v>0.07773984868304892</v>
       </c>
       <c r="T14">
         <v>0.4940993010376432</v>
       </c>
       <c r="U14">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.78692073753572</v>
+        <v>18.16347178627989</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07492628323739862</v>
+        <v>0.07477309208038101</v>
       </c>
       <c r="C15">
-        <v>1065.444075787445</v>
+        <v>1070.019831378872</v>
       </c>
       <c r="D15">
-        <v>1086.885075787445</v>
+        <v>1091.460831378872</v>
       </c>
       <c r="E15">
         <v>-186.859</v>
@@ -2517,37 +2517,37 @@
         <v>163.7</v>
       </c>
       <c r="M15">
-        <v>9.970341088461858</v>
+        <v>9.763643688461858</v>
       </c>
       <c r="N15">
-        <v>153.7296589115381</v>
+        <v>153.9363563115381</v>
       </c>
       <c r="O15">
-        <v>30.74593178230763</v>
+        <v>30.78727126230763</v>
       </c>
       <c r="P15">
-        <v>122.9837271292305</v>
+        <v>123.1490850492305</v>
       </c>
       <c r="Q15">
-        <v>229.3837271292306</v>
+        <v>229.5490850492305</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07804949603408717</v>
+        <v>0.07804077056625082</v>
       </c>
       <c r="T15">
         <v>0.4987544668661493</v>
       </c>
       <c r="U15">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.41869606541758</v>
+        <v>16.76628164887374</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07495091902349645</v>
+        <v>0.07478654345407022</v>
       </c>
       <c r="C16">
-        <v>1053.318096501205</v>
+        <v>1058.239280408667</v>
       </c>
       <c r="D16">
-        <v>1086.116096501205</v>
+        <v>1091.037280408667</v>
       </c>
       <c r="E16">
         <v>-175.502</v>
@@ -2599,37 +2599,37 @@
         <v>163.7</v>
       </c>
       <c r="M16">
-        <v>10.73729040295892</v>
+        <v>10.51469320295892</v>
       </c>
       <c r="N16">
-        <v>152.9627095970411</v>
+        <v>153.1853067970411</v>
       </c>
       <c r="O16">
-        <v>30.59254191940821</v>
+        <v>30.63706135940821</v>
       </c>
       <c r="P16">
-        <v>122.3701676776328</v>
+        <v>122.5482454376328</v>
       </c>
       <c r="Q16">
-        <v>228.7701676776329</v>
+        <v>228.9482454376329</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.0783574994344414</v>
+        <v>0.07834869063278299</v>
       </c>
       <c r="T16">
         <v>0.5035178923650858</v>
       </c>
       <c r="U16">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.2459320607449</v>
+        <v>15.56869010252562</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07497555480959425</v>
+        <v>0.07479999482775944</v>
       </c>
       <c r="C17">
-        <v>1041.193204562803</v>
+        <v>1046.459058036302</v>
       </c>
       <c r="D17">
-        <v>1085.348204562803</v>
+        <v>1090.614058036302</v>
       </c>
       <c r="E17">
         <v>-164.145</v>
@@ -2681,37 +2681,37 @@
         <v>163.7</v>
       </c>
       <c r="M17">
-        <v>11.50423971745599</v>
+        <v>11.26574271745599</v>
       </c>
       <c r="N17">
-        <v>152.195760282544</v>
+        <v>152.434257282544</v>
       </c>
       <c r="O17">
-        <v>30.4391520565088</v>
+        <v>30.4868514565088</v>
       </c>
       <c r="P17">
-        <v>121.7566082260352</v>
+        <v>121.9474058260352</v>
       </c>
       <c r="Q17">
-        <v>228.1566082260352</v>
+        <v>228.3474058260352</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07867274997362746</v>
+        <v>0.07866385587735121</v>
       </c>
       <c r="T17">
         <v>0.5083933984639973</v>
       </c>
       <c r="U17">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.22953659002858</v>
+        <v>14.53077742902391</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07500019059569205</v>
+        <v>0.07481344620144864</v>
       </c>
       <c r="C18">
-        <v>1029.06939766758</v>
+        <v>1034.679163879527</v>
       </c>
       <c r="D18">
-        <v>1084.58139766758</v>
+        <v>1090.191163879527</v>
       </c>
       <c r="E18">
         <v>-152.788</v>
@@ -2763,37 +2763,37 @@
         <v>163.7</v>
       </c>
       <c r="M18">
-        <v>12.27118903195305</v>
+        <v>12.01679223195305</v>
       </c>
       <c r="N18">
-        <v>151.4288109680469</v>
+        <v>151.6832077680469</v>
       </c>
       <c r="O18">
-        <v>30.28576219360939</v>
+        <v>30.33664155360939</v>
       </c>
       <c r="P18">
-        <v>121.1430487744376</v>
+        <v>121.3465662144376</v>
       </c>
       <c r="Q18">
-        <v>227.5430487744376</v>
+        <v>227.7465662144376</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07899550647803225</v>
+        <v>0.0789865250563139</v>
       </c>
       <c r="T18">
         <v>0.5133849880414543</v>
       </c>
       <c r="U18">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.34019055315179</v>
+        <v>13.62260383970992</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07517442638178985</v>
+        <v>0.07482689757513787</v>
       </c>
       <c r="C19">
-        <v>1012.31995738124</v>
+        <v>1022.899597556685</v>
       </c>
       <c r="D19">
-        <v>1079.18895738124</v>
+        <v>1089.768597556684</v>
       </c>
       <c r="E19">
         <v>-141.431</v>
@@ -2845,45 +2845,45 @@
         <v>163.7</v>
       </c>
       <c r="M19">
-        <v>13.25051424645012</v>
+        <v>12.76784174645012</v>
       </c>
       <c r="N19">
-        <v>150.4494857535499</v>
+        <v>150.9321582535499</v>
       </c>
       <c r="O19">
-        <v>30.08989715070998</v>
+        <v>30.18643165070997</v>
       </c>
       <c r="P19">
-        <v>120.3595886028399</v>
+        <v>120.7457266028399</v>
       </c>
       <c r="Q19">
-        <v>226.7595886028399</v>
+        <v>227.1457266028399</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07932604024760341</v>
+        <v>0.07931696939621546</v>
       </c>
       <c r="T19">
         <v>0.518496856885838</v>
       </c>
       <c r="U19">
-        <v>0.06863097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05490478221340607</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.35423750016767</v>
+        <v>12.82127420207992</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07520786216788768</v>
+        <v>0.0750563489488271</v>
       </c>
       <c r="C20">
-        <v>999.9342764268756</v>
+        <v>1004.384649481731</v>
       </c>
       <c r="D20">
-        <v>1078.160276426875</v>
+        <v>1082.610649481731</v>
       </c>
       <c r="E20">
         <v>-130.074</v>
@@ -2927,37 +2927,37 @@
         <v>163.7</v>
       </c>
       <c r="M20">
-        <v>14.02995626094718</v>
+        <v>13.82553026094718</v>
       </c>
       <c r="N20">
-        <v>149.6700437390528</v>
+        <v>149.8744697390528</v>
       </c>
       <c r="O20">
-        <v>29.93400874781056</v>
+        <v>29.97489394781056</v>
       </c>
       <c r="P20">
-        <v>119.7360349912422</v>
+        <v>119.8995757912423</v>
       </c>
       <c r="Q20">
-        <v>226.1360349912423</v>
+        <v>226.2995757912423</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07966463581643241</v>
+        <v>0.07965547335416341</v>
       </c>
       <c r="T20">
         <v>0.5237334054581335</v>
       </c>
       <c r="U20">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.66789097238058</v>
+        <v>11.8404138510623</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0752412979539855</v>
+        <v>0.07508180032251632</v>
       </c>
       <c r="C21">
-        <v>987.5505546786352</v>
+        <v>992.2394596762432</v>
       </c>
       <c r="D21">
-        <v>1077.133554678635</v>
+        <v>1081.822459676243</v>
       </c>
       <c r="E21">
         <v>-118.717</v>
@@ -3009,37 +3009,37 @@
         <v>163.7</v>
       </c>
       <c r="M21">
-        <v>14.80939827544425</v>
+        <v>14.59361527544425</v>
       </c>
       <c r="N21">
-        <v>148.8906017245557</v>
+        <v>149.1063847245557</v>
       </c>
       <c r="O21">
-        <v>29.77812034491114</v>
+        <v>29.82127694491115</v>
       </c>
       <c r="P21">
-        <v>119.1124813796446</v>
+        <v>119.2851077796446</v>
       </c>
       <c r="Q21">
-        <v>225.5124813796446</v>
+        <v>225.6851077796446</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08001159176967695</v>
+        <v>0.08000233543452984</v>
       </c>
       <c r="T21">
         <v>0.5290992515260413</v>
       </c>
       <c r="U21">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.05379144751844</v>
+        <v>11.2172341746906</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07527473374008328</v>
+        <v>0.07510725169620554</v>
       </c>
       <c r="C22">
-        <v>975.1687865446446</v>
+        <v>980.0954167118763</v>
       </c>
       <c r="D22">
-        <v>1076.108786544645</v>
+        <v>1081.035416711876</v>
       </c>
       <c r="E22">
         <v>-107.36</v>
@@ -3091,37 +3091,37 @@
         <v>163.7</v>
       </c>
       <c r="M22">
-        <v>15.58884028994132</v>
+        <v>15.36170028994132</v>
       </c>
       <c r="N22">
-        <v>148.1111597100587</v>
+        <v>148.3382997100587</v>
       </c>
       <c r="O22">
-        <v>29.62223194201174</v>
+        <v>29.66765994201173</v>
       </c>
       <c r="P22">
-        <v>118.4889277680469</v>
+        <v>118.6706397680469</v>
       </c>
       <c r="Q22">
-        <v>224.888927768047</v>
+        <v>225.070639768047</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08036722162175258</v>
+        <v>0.0803578690669054</v>
       </c>
       <c r="T22">
         <v>0.5345992437456466</v>
       </c>
       <c r="U22">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.50110187514252</v>
+        <v>10.65637246595607</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07530816952618109</v>
+        <v>0.07513270306989475</v>
       </c>
       <c r="C23">
-        <v>962.7889664542868</v>
+        <v>967.9525180874143</v>
       </c>
       <c r="D23">
-        <v>1075.085966454287</v>
+        <v>1080.249518087414</v>
       </c>
       <c r="E23">
         <v>-96.00299999999999</v>
@@ -3173,37 +3173,37 @@
         <v>163.7</v>
       </c>
       <c r="M23">
-        <v>16.36828230443838</v>
+        <v>16.12978530443839</v>
       </c>
       <c r="N23">
-        <v>147.3317176955616</v>
+        <v>147.5702146955616</v>
       </c>
       <c r="O23">
-        <v>29.46634353911232</v>
+        <v>29.51404293911233</v>
       </c>
       <c r="P23">
-        <v>117.8653741564493</v>
+        <v>118.0561717564493</v>
       </c>
       <c r="Q23">
-        <v>224.2653741564493</v>
+        <v>224.4561717564493</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08073185476122255</v>
+        <v>0.08072240355073351</v>
       </c>
       <c r="T23">
         <v>0.5402384762746092</v>
       </c>
       <c r="U23">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.00104940489763</v>
+        <v>10.1489261580534</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07572880531227889</v>
+        <v>0.07545735444358397</v>
       </c>
       <c r="C24">
-        <v>938.728603613567</v>
+        <v>946.6701199661816</v>
       </c>
       <c r="D24">
-        <v>1062.382603613567</v>
+        <v>1070.324119966182</v>
       </c>
       <c r="E24">
         <v>-84.64599999999999</v>
@@ -3255,37 +3255,37 @@
         <v>163.7</v>
       </c>
       <c r="M24">
-        <v>17.69740311893545</v>
+        <v>17.32262211893545</v>
       </c>
       <c r="N24">
-        <v>146.0025968810645</v>
+        <v>146.3773778810645</v>
       </c>
       <c r="O24">
-        <v>29.20051937621291</v>
+        <v>29.27547557621291</v>
       </c>
       <c r="P24">
-        <v>116.8020775048516</v>
+        <v>117.1019023048516</v>
       </c>
       <c r="Q24">
-        <v>223.2020775048517</v>
+        <v>223.5019023048517</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08110583746837123</v>
+        <v>0.08109628507260849</v>
       </c>
       <c r="T24">
         <v>0.5460223045094426</v>
       </c>
       <c r="U24">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.249944689616532</v>
+        <v>9.450070484482755</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07577984109837671</v>
+        <v>0.07549640581727318</v>
       </c>
       <c r="C25">
-        <v>925.8506958763912</v>
+        <v>934.1314981023008</v>
       </c>
       <c r="D25">
-        <v>1060.861695876391</v>
+        <v>1069.142498102301</v>
       </c>
       <c r="E25">
         <v>-73.28899999999999</v>
@@ -3337,37 +3337,37 @@
         <v>163.7</v>
       </c>
       <c r="M25">
-        <v>18.50183053343251</v>
+        <v>18.11001403343251</v>
       </c>
       <c r="N25">
-        <v>145.1981694665675</v>
+        <v>145.5899859665675</v>
       </c>
       <c r="O25">
-        <v>29.03963389331349</v>
+        <v>29.1179971933135</v>
       </c>
       <c r="P25">
-        <v>116.158535573254</v>
+        <v>116.471988773254</v>
       </c>
       <c r="Q25">
-        <v>222.558535573254</v>
+        <v>222.871988773254</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08148953401206924</v>
+        <v>0.08147987780284388</v>
       </c>
       <c r="T25">
         <v>0.5519563620490768</v>
       </c>
       <c r="U25">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.847773181372334</v>
+        <v>9.039197854722635</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.0758308768844745</v>
+        <v>0.0755354571909624</v>
       </c>
       <c r="C26">
-        <v>912.9771365793151</v>
+        <v>921.5954823471411</v>
       </c>
       <c r="D26">
-        <v>1059.345136579315</v>
+        <v>1067.963482347141</v>
       </c>
       <c r="E26">
         <v>-61.93200000000002</v>
@@ -3419,37 +3419,37 @@
         <v>163.7</v>
       </c>
       <c r="M26">
-        <v>19.30625794792958</v>
+        <v>18.89740594792958</v>
       </c>
       <c r="N26">
-        <v>144.3937420520704</v>
+        <v>144.8025940520704</v>
       </c>
       <c r="O26">
-        <v>28.87874841041409</v>
+        <v>28.96051881041409</v>
       </c>
       <c r="P26">
-        <v>115.5149936416563</v>
+        <v>115.8420752416563</v>
       </c>
       <c r="Q26">
-        <v>221.9149936416564</v>
+        <v>222.2420752416564</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08188332783323296</v>
+        <v>0.08187356507861177</v>
       </c>
       <c r="T26">
         <v>0.5580465789976486</v>
       </c>
       <c r="U26">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.479115965481821</v>
+        <v>8.66256461077586</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07588191267057232</v>
+        <v>0.07557450856465162</v>
       </c>
       <c r="C27">
-        <v>900.1079070999665</v>
+        <v>909.0620640884028</v>
       </c>
       <c r="D27">
-        <v>1057.832907099966</v>
+        <v>1066.787064088403</v>
       </c>
       <c r="E27">
         <v>-50.57499999999999</v>
@@ -3501,37 +3501,37 @@
         <v>163.7</v>
       </c>
       <c r="M27">
-        <v>20.11068536242665</v>
+        <v>19.68479786242665</v>
       </c>
       <c r="N27">
-        <v>143.5893146375734</v>
+        <v>144.0152021375733</v>
       </c>
       <c r="O27">
-        <v>28.71786292751467</v>
+        <v>28.80304042751467</v>
       </c>
       <c r="P27">
-        <v>114.8714517100587</v>
+        <v>115.2121617100587</v>
       </c>
       <c r="Q27">
-        <v>221.2714517100587</v>
+        <v>221.6121617100587</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08228762282296107</v>
+        <v>0.08227775068173347</v>
       </c>
       <c r="T27">
         <v>0.5642992017315159</v>
       </c>
       <c r="U27">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.139951326862548</v>
+        <v>8.316062026344824</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07593294845667013</v>
+        <v>0.07561355993834085</v>
       </c>
       <c r="C28">
-        <v>887.2429889221577</v>
+        <v>896.5312347516914</v>
       </c>
       <c r="D28">
-        <v>1056.324988922158</v>
+        <v>1065.613234751691</v>
       </c>
       <c r="E28">
         <v>-39.21799999999996</v>
@@ -3583,37 +3583,37 @@
         <v>163.7</v>
       </c>
       <c r="M28">
-        <v>20.91511277692371</v>
+        <v>20.47218977692371</v>
       </c>
       <c r="N28">
-        <v>142.7848872230763</v>
+        <v>143.2278102230763</v>
       </c>
       <c r="O28">
-        <v>28.55697744461526</v>
+        <v>28.64556204461526</v>
       </c>
       <c r="P28">
-        <v>114.227909778461</v>
+        <v>114.582248178461</v>
       </c>
       <c r="Q28">
-        <v>220.6279097784611</v>
+        <v>220.9822481784611</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08270284470430345</v>
+        <v>0.08269286022007469</v>
       </c>
       <c r="T28">
         <v>0.5707208142690012</v>
       </c>
       <c r="U28">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.826876275829372</v>
+        <v>7.996213486870023</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07630798424276794</v>
+        <v>0.07565261131203006</v>
       </c>
       <c r="C29">
-        <v>864.9355749255343</v>
+        <v>884.0029858003112</v>
       </c>
       <c r="D29">
-        <v>1045.374574925534</v>
+        <v>1064.441985800311</v>
       </c>
       <c r="E29">
         <v>-27.86099999999999</v>
@@ -3665,45 +3665,45 @@
         <v>163.7</v>
       </c>
       <c r="M29">
-        <v>22.17949869142078</v>
+        <v>21.25958169142078</v>
       </c>
       <c r="N29">
-        <v>141.5205013085792</v>
+        <v>142.4404183085792</v>
       </c>
       <c r="O29">
-        <v>28.30410026171585</v>
+        <v>28.48808366171584</v>
       </c>
       <c r="P29">
-        <v>113.2164010468634</v>
+        <v>113.9523346468634</v>
       </c>
       <c r="Q29">
-        <v>219.6164010468634</v>
+        <v>220.3523346468634</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08312944252760041</v>
+        <v>0.08311934262248002</v>
       </c>
       <c r="T29">
         <v>0.5773183613965546</v>
       </c>
       <c r="U29">
-        <v>0.07233097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.05786478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.380689810781005</v>
+        <v>7.700057431800762</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07637102002886573</v>
+        <v>0.07587086268571927</v>
       </c>
       <c r="C30">
-        <v>851.7602841922951</v>
+        <v>866.1471939266344</v>
       </c>
       <c r="D30">
-        <v>1043.556284192295</v>
+        <v>1057.943193926634</v>
       </c>
       <c r="E30">
         <v>-16.50399999999996</v>
@@ -3747,37 +3747,37 @@
         <v>163.7</v>
       </c>
       <c r="M30">
-        <v>23.00096160591784</v>
+        <v>22.30137040591785</v>
       </c>
       <c r="N30">
-        <v>140.6990383940822</v>
+        <v>141.3986295940821</v>
       </c>
       <c r="O30">
-        <v>28.13980767881643</v>
+        <v>28.27972591881643</v>
       </c>
       <c r="P30">
-        <v>112.5592307152657</v>
+        <v>113.1189036752657</v>
       </c>
       <c r="Q30">
-        <v>218.9592307152658</v>
+        <v>219.5189036752657</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08356789029043338</v>
+        <v>0.08355767175828552</v>
       </c>
       <c r="T30">
         <v>0.5840991737220954</v>
       </c>
       <c r="U30">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.117093746110256</v>
+        <v>7.340356086662768</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07643405581496354</v>
+        <v>0.07591631405940849</v>
       </c>
       <c r="C31">
-        <v>838.5913078282586</v>
+        <v>853.4467758920089</v>
       </c>
       <c r="D31">
-        <v>1041.744307828259</v>
+        <v>1056.599775892009</v>
       </c>
       <c r="E31">
         <v>-5.146999999999991</v>
@@ -3829,37 +3829,37 @@
         <v>163.7</v>
       </c>
       <c r="M31">
-        <v>23.82242452041491</v>
+        <v>23.09784792041491</v>
       </c>
       <c r="N31">
-        <v>139.8775754795851</v>
+        <v>140.6021520795851</v>
       </c>
       <c r="O31">
-        <v>27.97551509591702</v>
+        <v>28.12043041591701</v>
       </c>
       <c r="P31">
-        <v>111.9020603836681</v>
+        <v>112.4817216636681</v>
       </c>
       <c r="Q31">
-        <v>218.3020603836681</v>
+        <v>218.8817216636681</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08401868869447293</v>
+        <v>0.08400834819369118</v>
       </c>
       <c r="T31">
         <v>0.5910709948455389</v>
       </c>
       <c r="U31">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.871676720382316</v>
+        <v>7.087240359536466</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07649709160106134</v>
+        <v>0.07596176543309771</v>
       </c>
       <c r="C32">
-        <v>825.428612998621</v>
+        <v>840.7497653808907</v>
       </c>
       <c r="D32">
-        <v>1039.938612998621</v>
+        <v>1055.259765380891</v>
       </c>
       <c r="E32">
         <v>6.20999999999998</v>
@@ -3911,37 +3911,37 @@
         <v>163.7</v>
       </c>
       <c r="M32">
-        <v>24.64388743491197</v>
+        <v>23.89432543491198</v>
       </c>
       <c r="N32">
-        <v>139.056112565088</v>
+        <v>139.805674565088</v>
       </c>
       <c r="O32">
-        <v>27.81122251301761</v>
+        <v>27.9611349130176</v>
       </c>
       <c r="P32">
-        <v>111.2448900520704</v>
+        <v>111.8445396520704</v>
       </c>
       <c r="Q32">
-        <v>217.6448900520705</v>
+        <v>218.2445396520704</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08448236705291361</v>
+        <v>0.08447190109867986</v>
       </c>
       <c r="T32">
         <v>0.5982420108582237</v>
       </c>
       <c r="U32">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.642620829702906</v>
+        <v>6.850999014218583</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07656012738715914</v>
+        <v>0.07600721680678693</v>
       </c>
       <c r="C33">
-        <v>812.2721670958379</v>
+        <v>828.056149445141</v>
       </c>
       <c r="D33">
-        <v>1038.139167095838</v>
+        <v>1053.923149445141</v>
       </c>
       <c r="E33">
         <v>17.56700000000001</v>
@@ -3993,37 +3993,37 @@
         <v>163.7</v>
       </c>
       <c r="M33">
-        <v>25.46535034940904</v>
+        <v>24.69080294940904</v>
       </c>
       <c r="N33">
-        <v>138.2346496505909</v>
+        <v>139.009197050591</v>
       </c>
       <c r="O33">
-        <v>27.64692993011819</v>
+        <v>27.80183941011819</v>
       </c>
       <c r="P33">
-        <v>110.5877197204727</v>
+        <v>111.2073576404728</v>
       </c>
       <c r="Q33">
-        <v>216.9877197204728</v>
+        <v>217.6073576404728</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08495948536377285</v>
+        <v>0.08494889031975514</v>
       </c>
       <c r="T33">
         <v>0.6056208824075079</v>
       </c>
       <c r="U33">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.428342738422167</v>
+        <v>6.629999046017985</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07662316317325696</v>
+        <v>0.07605266818047614</v>
       </c>
       <c r="C34">
-        <v>799.1219377376635</v>
+        <v>815.3659152021387</v>
       </c>
       <c r="D34">
-        <v>1036.345937737663</v>
+        <v>1052.589915202139</v>
       </c>
       <c r="E34">
         <v>28.92400000000004</v>
@@ -4075,37 +4075,37 @@
         <v>163.7</v>
       </c>
       <c r="M34">
-        <v>26.28681326390611</v>
+        <v>25.48728046390611</v>
       </c>
       <c r="N34">
-        <v>137.4131867360939</v>
+        <v>138.2127195360939</v>
       </c>
       <c r="O34">
-        <v>27.48263734721878</v>
+        <v>27.64254390721878</v>
       </c>
       <c r="P34">
-        <v>109.9305493888751</v>
+        <v>110.5701756288751</v>
       </c>
       <c r="Q34">
-        <v>216.3305493888751</v>
+        <v>216.9701756288752</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08545063656612797</v>
+        <v>0.08543990863556795</v>
       </c>
       <c r="T34">
         <v>0.6132167795905947</v>
       </c>
       <c r="U34">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.227457027846473</v>
+        <v>6.422811575829923</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07705579895935476</v>
+        <v>0.07609811955416536</v>
       </c>
       <c r="C35">
-        <v>775.6226132602505</v>
+        <v>802.6790498343669</v>
       </c>
       <c r="D35">
-        <v>1024.20361326025</v>
+        <v>1051.260049834367</v>
       </c>
       <c r="E35">
         <v>40.28100000000001</v>
@@ -4157,45 +4157,45 @@
         <v>163.7</v>
       </c>
       <c r="M35">
-        <v>27.63296957840317</v>
+        <v>26.28375797840317</v>
       </c>
       <c r="N35">
-        <v>136.0670304215968</v>
+        <v>137.4162420215968</v>
       </c>
       <c r="O35">
-        <v>27.21340608431937</v>
+        <v>27.48324840431937</v>
       </c>
       <c r="P35">
-        <v>108.8536243372775</v>
+        <v>109.9329936172774</v>
       </c>
       <c r="Q35">
-        <v>215.2536243372775</v>
+        <v>216.3329936172775</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08595644899840413</v>
+        <v>0.08594558421453935</v>
       </c>
       <c r="T35">
         <v>0.6210394199731767</v>
       </c>
       <c r="U35">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05898478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>5.924082807514882</v>
+        <v>6.228180922016895</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07713003474545256</v>
+        <v>0.07641557092785459</v>
       </c>
       <c r="C36">
-        <v>762.2106596599525</v>
+        <v>782.1265930322562</v>
       </c>
       <c r="D36">
-        <v>1022.148659659953</v>
+        <v>1042.064593032256</v>
       </c>
       <c r="E36">
         <v>51.63800000000003</v>
@@ -4239,37 +4239,37 @@
         <v>163.7</v>
       </c>
       <c r="M36">
-        <v>28.47033229290024</v>
+        <v>27.46637349290024</v>
       </c>
       <c r="N36">
-        <v>135.2296677070997</v>
+        <v>136.2336265070998</v>
       </c>
       <c r="O36">
-        <v>27.04593354141995</v>
+        <v>27.24672530141995</v>
       </c>
       <c r="P36">
-        <v>108.1837341656798</v>
+        <v>108.9869012056798</v>
       </c>
       <c r="Q36">
-        <v>214.5837341656798</v>
+        <v>215.3869012056798</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08647758908014319</v>
+        <v>0.08646658329590381</v>
       </c>
       <c r="T36">
         <v>0.6290991100643216</v>
       </c>
       <c r="U36">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.749845077882091</v>
+        <v>5.960015072332525</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07720427053155038</v>
+        <v>0.0764690223015438</v>
       </c>
       <c r="C37">
-        <v>748.8069356314909</v>
+        <v>769.2370937205535</v>
       </c>
       <c r="D37">
-        <v>1020.101935631491</v>
+        <v>1040.532093720554</v>
       </c>
       <c r="E37">
         <v>62.99500000000006</v>
@@ -4321,37 +4321,37 @@
         <v>163.7</v>
       </c>
       <c r="M37">
-        <v>29.30769500739731</v>
+        <v>28.27420800739731</v>
       </c>
       <c r="N37">
-        <v>134.3923049926027</v>
+        <v>135.4257919926027</v>
       </c>
       <c r="O37">
-        <v>26.87846099852054</v>
+        <v>27.08515839852054</v>
       </c>
       <c r="P37">
-        <v>107.5138439940821</v>
+        <v>108.3406335940821</v>
       </c>
       <c r="Q37">
-        <v>213.9138439940822</v>
+        <v>214.7406335940822</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08701476424132039</v>
+        <v>0.08700361311823336</v>
       </c>
       <c r="T37">
         <v>0.6374067906198095</v>
       </c>
       <c r="U37">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.585563789942602</v>
+        <v>5.789728927408738</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07727850631764818</v>
+        <v>0.07652247367523303</v>
       </c>
       <c r="C38">
-        <v>735.4113918376125</v>
+        <v>756.3520952917248</v>
       </c>
       <c r="D38">
-        <v>1018.063391837612</v>
+        <v>1039.004095291725</v>
       </c>
       <c r="E38">
         <v>74.35199999999998</v>
@@ -4403,37 +4403,37 @@
         <v>163.7</v>
       </c>
       <c r="M38">
-        <v>30.14505772189437</v>
+        <v>29.08204252189437</v>
       </c>
       <c r="N38">
-        <v>133.5549422781056</v>
+        <v>134.6179574781056</v>
       </c>
       <c r="O38">
-        <v>26.71098845562112</v>
+        <v>26.92359149562112</v>
       </c>
       <c r="P38">
-        <v>106.8439538224845</v>
+        <v>107.6943659824845</v>
       </c>
       <c r="Q38">
-        <v>213.2439538224845</v>
+        <v>214.0943659824845</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08756872612628437</v>
+        <v>0.08755742512251069</v>
       </c>
       <c r="T38">
         <v>0.6459740861926564</v>
       </c>
       <c r="U38">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.430409240221975</v>
+        <v>5.628903123869607</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07735274210374599</v>
+        <v>0.07657592504892224</v>
       </c>
       <c r="C39">
-        <v>722.0239793346539</v>
+        <v>743.4715779465041</v>
       </c>
       <c r="D39">
-        <v>1016.032979334654</v>
+        <v>1037.480577946504</v>
       </c>
       <c r="E39">
         <v>85.709</v>
@@ -4485,37 +4485,37 @@
         <v>163.7</v>
       </c>
       <c r="M39">
-        <v>30.98242043639144</v>
+        <v>29.88987703639144</v>
       </c>
       <c r="N39">
-        <v>132.7175795636086</v>
+        <v>133.8101229636085</v>
       </c>
       <c r="O39">
-        <v>26.54351591272171</v>
+        <v>26.76202459272171</v>
       </c>
       <c r="P39">
-        <v>106.1740636508868</v>
+        <v>107.0480983708868</v>
       </c>
       <c r="Q39">
-        <v>212.5740636508869</v>
+        <v>213.4480983708869</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08814027410283451</v>
+        <v>0.08812881846025714</v>
       </c>
       <c r="T39">
         <v>0.6548133594027366</v>
       </c>
       <c r="U39">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.283641422918678</v>
+        <v>5.476770607008266</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07742697788984379</v>
+        <v>0.07662937642261144</v>
       </c>
       <c r="C40">
-        <v>708.6446495686253</v>
+        <v>730.595522001583</v>
       </c>
       <c r="D40">
-        <v>1014.010649568625</v>
+        <v>1035.961522001583</v>
       </c>
       <c r="E40">
         <v>97.06600000000003</v>
@@ -4567,37 +4567,37 @@
         <v>163.7</v>
       </c>
       <c r="M40">
-        <v>31.8197831508885</v>
+        <v>30.69771155088851</v>
       </c>
       <c r="N40">
-        <v>131.8802168491115</v>
+        <v>133.0022884491115</v>
       </c>
       <c r="O40">
-        <v>26.3760433698223</v>
+        <v>26.6004576898223</v>
       </c>
       <c r="P40">
-        <v>105.5041734792892</v>
+        <v>106.4018307592892</v>
       </c>
       <c r="Q40">
-        <v>211.9041734792892</v>
+        <v>212.8018307592892</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08873025911088628</v>
+        <v>0.08871864384115669</v>
       </c>
       <c r="T40">
         <v>0.663937770458303</v>
       </c>
       <c r="U40">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.144598227578713</v>
+        <v>5.332645064718576</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07750121367594159</v>
+        <v>0.07668282779630067</v>
       </c>
       <c r="C41">
-        <v>695.2733543713398</v>
+        <v>717.7239078887631</v>
       </c>
       <c r="D41">
-        <v>1011.99635437134</v>
+        <v>1034.446907888763</v>
       </c>
       <c r="E41">
         <v>108.4230000000001</v>
@@ -4649,37 +4649,37 @@
         <v>163.7</v>
       </c>
       <c r="M41">
-        <v>32.65714586538557</v>
+        <v>31.50554606538557</v>
       </c>
       <c r="N41">
-        <v>131.0428541346144</v>
+        <v>132.1944539346144</v>
       </c>
       <c r="O41">
-        <v>26.20857082692288</v>
+        <v>26.43889078692288</v>
       </c>
       <c r="P41">
-        <v>104.8342833076915</v>
+        <v>105.7555631476915</v>
       </c>
       <c r="Q41">
-        <v>211.2342833076916</v>
+        <v>212.1555631476916</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08933958788969383</v>
+        <v>0.08932780775913493</v>
       </c>
       <c r="T41">
         <v>0.673361342532085</v>
       </c>
       <c r="U41">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.012685452512591</v>
+        <v>5.195910575879637</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07757544946203941</v>
+        <v>0.0767362791699899</v>
       </c>
       <c r="C42">
-        <v>681.9100459565882</v>
+        <v>704.8567161541182</v>
       </c>
       <c r="D42">
-        <v>1009.990045956588</v>
+        <v>1032.936716154118</v>
       </c>
       <c r="E42">
         <v>119.78</v>
@@ -4731,37 +4731,37 @@
         <v>163.7</v>
       </c>
       <c r="M42">
-        <v>33.49450857988263</v>
+        <v>32.31338057988264</v>
       </c>
       <c r="N42">
-        <v>130.2054914201174</v>
+        <v>131.3866194201173</v>
       </c>
       <c r="O42">
-        <v>26.04109828402348</v>
+        <v>26.27732388402347</v>
       </c>
       <c r="P42">
-        <v>104.1643931360939</v>
+        <v>105.1092955360939</v>
       </c>
       <c r="Q42">
-        <v>210.5643931360939</v>
+        <v>211.5092955360939</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08996922762779497</v>
+        <v>0.08995727714104579</v>
       </c>
       <c r="T42">
         <v>0.683099033674993</v>
       </c>
       <c r="U42">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.887368316199778</v>
+        <v>5.066012811482646</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07764968524813722</v>
+        <v>0.0767897305436791</v>
       </c>
       <c r="C43">
-        <v>668.5546769163633</v>
+        <v>691.9939274571599</v>
       </c>
       <c r="D43">
-        <v>1007.991676916363</v>
+        <v>1031.43092745716</v>
       </c>
       <c r="E43">
         <v>131.1370000000001</v>
@@ -4813,37 +4813,37 @@
         <v>163.7</v>
       </c>
       <c r="M43">
-        <v>34.3318712943797</v>
+        <v>33.12121509437971</v>
       </c>
       <c r="N43">
-        <v>129.3681287056203</v>
+        <v>130.5787849056203</v>
       </c>
       <c r="O43">
-        <v>25.87362574112406</v>
+        <v>26.11575698112406</v>
       </c>
       <c r="P43">
-        <v>103.4945029644962</v>
+        <v>104.4630279244962</v>
       </c>
       <c r="Q43">
-        <v>209.8945029644963</v>
+        <v>210.8630279244963</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09062021108583174</v>
+        <v>0.09060808446810614</v>
       </c>
       <c r="T43">
         <v>0.6931668160430843</v>
       </c>
       <c r="U43">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.768164210926612</v>
+        <v>4.942451523397704</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07772392103423502</v>
+        <v>0.07684318191736833</v>
       </c>
       <c r="C44">
-        <v>655.2072002171211</v>
+        <v>679.13552257001</v>
       </c>
       <c r="D44">
-        <v>1006.001200217121</v>
+        <v>1029.92952257001</v>
       </c>
       <c r="E44">
         <v>142.494</v>
@@ -4895,37 +4895,37 @@
         <v>163.7</v>
       </c>
       <c r="M44">
-        <v>35.16923400887676</v>
+        <v>33.92904960887677</v>
       </c>
       <c r="N44">
-        <v>128.5307659911232</v>
+        <v>129.7709503911232</v>
       </c>
       <c r="O44">
-        <v>25.70615319822464</v>
+        <v>25.95419007822465</v>
       </c>
       <c r="P44">
-        <v>102.8246127928986</v>
+        <v>103.8167603128986</v>
       </c>
       <c r="Q44">
-        <v>209.2246127928986</v>
+        <v>210.2167603128986</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09129364224931805</v>
+        <v>0.0912813334271341</v>
       </c>
       <c r="T44">
         <v>0.70358176332042</v>
       </c>
       <c r="U44">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.654636491618836</v>
+        <v>4.824774106173949</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07779815682033284</v>
+        <v>0.07689663329105756</v>
       </c>
       <c r="C45">
-        <v>641.8675691960938</v>
+        <v>666.2814823765865</v>
       </c>
       <c r="D45">
-        <v>1004.018569196094</v>
+        <v>1028.432482376586</v>
       </c>
       <c r="E45">
         <v>153.851</v>
@@ -4977,37 +4977,37 @@
         <v>163.7</v>
       </c>
       <c r="M45">
-        <v>36.00659672337383</v>
+        <v>34.73688412337383</v>
       </c>
       <c r="N45">
-        <v>127.6934032766262</v>
+        <v>128.9631158766261</v>
       </c>
       <c r="O45">
-        <v>25.53868065532523</v>
+        <v>25.79262317532523</v>
       </c>
       <c r="P45">
-        <v>102.1547226213009</v>
+        <v>103.1704927013009</v>
       </c>
       <c r="Q45">
-        <v>208.554722621301</v>
+        <v>209.570492701301</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09199070257643548</v>
+        <v>0.09197820515665428</v>
       </c>
       <c r="T45">
         <v>0.7143621473443291</v>
       </c>
       <c r="U45">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.54638913134863</v>
+        <v>4.71257005719316</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07878759260643063</v>
+        <v>0.07695008466474679</v>
       </c>
       <c r="C46">
-        <v>604.8125945481365</v>
+        <v>653.4317878717877</v>
       </c>
       <c r="D46">
-        <v>978.3205945481367</v>
+        <v>1026.939787871788</v>
       </c>
       <c r="E46">
         <v>165.208</v>
@@ -5059,45 +5059,45 @@
         <v>163.7</v>
       </c>
       <c r="M46">
-        <v>38.14320023787089</v>
+        <v>35.5447186378709</v>
       </c>
       <c r="N46">
-        <v>125.5567997621291</v>
+        <v>128.1552813621291</v>
       </c>
       <c r="O46">
-        <v>25.11135995242582</v>
+        <v>25.63105627242582</v>
       </c>
       <c r="P46">
-        <v>100.4454398097033</v>
+        <v>102.5242250897033</v>
       </c>
       <c r="Q46">
-        <v>206.8454398097033</v>
+        <v>208.9242250897033</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09271265791523564</v>
+        <v>0.09269996516222875</v>
       </c>
       <c r="T46">
         <v>0.7255275450833776</v>
       </c>
       <c r="U46">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.291721695587269</v>
+        <v>4.605466192256952</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07888262839252844</v>
+        <v>0.07700353603843599</v>
       </c>
       <c r="C47">
-        <v>591.0563664715664</v>
+        <v>640.5864201606921</v>
       </c>
       <c r="D47">
-        <v>975.9213664715664</v>
+        <v>1025.451420160692</v>
       </c>
       <c r="E47">
         <v>176.5650000000001</v>
@@ -5141,45 +5141,45 @@
         <v>163.7</v>
       </c>
       <c r="M47">
-        <v>39.01009115236796</v>
+        <v>36.35255315236797</v>
       </c>
       <c r="N47">
-        <v>124.689908847632</v>
+        <v>127.347446847632</v>
       </c>
       <c r="O47">
-        <v>24.93798176952641</v>
+        <v>25.46948936952641</v>
       </c>
       <c r="P47">
-        <v>99.75192707810562</v>
+        <v>101.8779574781056</v>
       </c>
       <c r="Q47">
-        <v>206.1519270781056</v>
+        <v>208.2779574781057</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09346086617544674</v>
+        <v>0.09344797098618773</v>
       </c>
       <c r="T47">
         <v>0.7370989572856643</v>
       </c>
       <c r="U47">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.196350102351996</v>
+        <v>4.503122499095686</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07897766417862626</v>
+        <v>0.07797698741212521</v>
       </c>
       <c r="C48">
-        <v>577.3118773141666</v>
+        <v>602.8587455580744</v>
       </c>
       <c r="D48">
-        <v>973.5338773141667</v>
+        <v>999.0807455580745</v>
       </c>
       <c r="E48">
         <v>187.922</v>
@@ -5223,37 +5223,37 @@
         <v>163.7</v>
       </c>
       <c r="M48">
-        <v>39.87698206686503</v>
+        <v>38.46644266686503</v>
       </c>
       <c r="N48">
-        <v>123.823017933135</v>
+        <v>125.233557333135</v>
       </c>
       <c r="O48">
-        <v>24.76460358662699</v>
+        <v>25.04671146662699</v>
       </c>
       <c r="P48">
-        <v>99.05841434650797</v>
+        <v>100.186845866508</v>
       </c>
       <c r="Q48">
-        <v>205.458414346508</v>
+        <v>206.586845866508</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.0942367858527027</v>
+        <v>0.09422368072955262</v>
       </c>
       <c r="T48">
         <v>0.749098940310258</v>
       </c>
       <c r="U48">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.105125100126953</v>
+        <v>4.25565736394468</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07907269996472405</v>
+        <v>0.07805043878581443</v>
       </c>
       <c r="C49">
-        <v>563.579041132091</v>
+        <v>589.5668812704422</v>
       </c>
       <c r="D49">
-        <v>971.1580411320911</v>
+        <v>997.1458812704423</v>
       </c>
       <c r="E49">
         <v>199.2790000000001</v>
@@ -5305,37 +5305,37 @@
         <v>163.7</v>
       </c>
       <c r="M49">
-        <v>40.7438729813621</v>
+        <v>39.3026696813621</v>
       </c>
       <c r="N49">
-        <v>122.9561270186379</v>
+        <v>124.3973303186379</v>
       </c>
       <c r="O49">
-        <v>24.59122540372758</v>
+        <v>24.87946606372758</v>
       </c>
       <c r="P49">
-        <v>98.36490161491031</v>
+        <v>99.51786425491032</v>
       </c>
       <c r="Q49">
-        <v>204.7649016149103</v>
+        <v>205.9178642549103</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09504198551777962</v>
+        <v>0.09502866253870486</v>
       </c>
       <c r="T49">
         <v>0.7615517528829495</v>
       </c>
       <c r="U49">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.017782012890208</v>
+        <v>4.165111462584155</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08020453575082186</v>
+        <v>0.07812389015950363</v>
       </c>
       <c r="C50">
-        <v>524.79310138694</v>
+        <v>576.2824967858717</v>
       </c>
       <c r="D50">
-        <v>943.7291013869399</v>
+        <v>995.2184967858717</v>
       </c>
       <c r="E50">
         <v>210.636</v>
@@ -5387,45 +5387,45 @@
         <v>163.7</v>
       </c>
       <c r="M50">
-        <v>43.08263109585916</v>
+        <v>40.13889669585915</v>
       </c>
       <c r="N50">
-        <v>120.6173689041408</v>
+        <v>123.5611033041408</v>
       </c>
       <c r="O50">
-        <v>24.12347378082817</v>
+        <v>24.71222066082817</v>
       </c>
       <c r="P50">
-        <v>96.49389512331267</v>
+        <v>98.84888264331266</v>
       </c>
       <c r="Q50">
-        <v>202.8938951233127</v>
+        <v>205.2488826433127</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09587815440074413</v>
+        <v>0.09586460518667064</v>
       </c>
       <c r="T50">
         <v>0.7744835197853599</v>
       </c>
       <c r="U50">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.06322478221340606</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.799675085668894</v>
+        <v>4.078338307113652</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08032117153691966</v>
+        <v>0.07956934153319287</v>
       </c>
       <c r="C51">
-        <v>510.6973495679496</v>
+        <v>528.4569403522006</v>
       </c>
       <c r="D51">
-        <v>940.9903495679496</v>
+        <v>958.7499403522007</v>
       </c>
       <c r="E51">
         <v>221.9930000000001</v>
@@ -5469,37 +5469,37 @@
         <v>163.7</v>
       </c>
       <c r="M51">
-        <v>43.98018591035623</v>
+        <v>42.92284921035623</v>
       </c>
       <c r="N51">
-        <v>119.7198140896438</v>
+        <v>120.7771507896438</v>
       </c>
       <c r="O51">
-        <v>23.94396281792875</v>
+        <v>24.15543015792876</v>
       </c>
       <c r="P51">
-        <v>95.77585127171501</v>
+        <v>96.62172063171502</v>
       </c>
       <c r="Q51">
-        <v>202.175851271715</v>
+        <v>203.0217206317151</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09674711422029547</v>
+        <v>0.09673332989926253</v>
       </c>
       <c r="T51">
         <v>0.7879224148015903</v>
       </c>
       <c r="U51">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.06322478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.722130696165447</v>
+        <v>3.813819515981787</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08043780732301747</v>
+        <v>0.07967079290688207</v>
       </c>
       <c r="C52">
-        <v>496.6174477569665</v>
+        <v>514.6404540971001</v>
       </c>
       <c r="D52">
-        <v>938.2674477569665</v>
+        <v>956.2904540971001</v>
       </c>
       <c r="E52">
         <v>233.35</v>
@@ -5551,37 +5551,37 @@
         <v>163.7</v>
       </c>
       <c r="M52">
-        <v>44.87774072485329</v>
+        <v>43.79882572485329</v>
       </c>
       <c r="N52">
-        <v>118.8222592751467</v>
+        <v>119.9011742751467</v>
       </c>
       <c r="O52">
-        <v>23.76445185502934</v>
+        <v>23.98023485502934</v>
       </c>
       <c r="P52">
-        <v>95.05780742011737</v>
+        <v>95.92093942011736</v>
       </c>
       <c r="Q52">
-        <v>201.4578074201174</v>
+        <v>202.3209394201174</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09765083243262887</v>
+        <v>0.09763680360035809</v>
       </c>
       <c r="T52">
         <v>0.80189886561847</v>
       </c>
       <c r="U52">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.06322478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.647688082242138</v>
+        <v>3.737543125662151</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08055444310911528</v>
+        <v>0.07977224428057131</v>
       </c>
       <c r="C53">
-        <v>482.5532587576062</v>
+        <v>500.8365542201005</v>
       </c>
       <c r="D53">
-        <v>935.5602587576061</v>
+        <v>953.8435542201006</v>
       </c>
       <c r="E53">
         <v>244.707</v>
@@ -5633,37 +5633,37 @@
         <v>163.7</v>
       </c>
       <c r="M53">
-        <v>45.77529553935035</v>
+        <v>44.67480223935036</v>
       </c>
       <c r="N53">
-        <v>117.9247044606496</v>
+        <v>119.0251977606496</v>
       </c>
       <c r="O53">
-        <v>23.58494089212993</v>
+        <v>23.80503955212993</v>
       </c>
       <c r="P53">
-        <v>94.33976356851971</v>
+        <v>95.22015820851971</v>
       </c>
       <c r="Q53">
-        <v>200.7397635685197</v>
+        <v>201.6201582085197</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09859143710260855</v>
+        <v>0.09857715377904941</v>
       </c>
       <c r="T53">
         <v>0.8164457838156306</v>
       </c>
       <c r="U53">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.06322478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.5761647865119</v>
+        <v>3.664257966335442</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08067107889521308</v>
+        <v>0.0798736956542605</v>
       </c>
       <c r="C54">
-        <v>468.504646952342</v>
+        <v>487.0451443519312</v>
       </c>
       <c r="D54">
-        <v>932.868646952342</v>
+        <v>951.4091443519313</v>
       </c>
       <c r="E54">
         <v>256.0640000000001</v>
@@ -5715,37 +5715,37 @@
         <v>163.7</v>
       </c>
       <c r="M54">
-        <v>46.67285035384743</v>
+        <v>45.55077875384742</v>
       </c>
       <c r="N54">
-        <v>117.0271496461526</v>
+        <v>118.1492212461526</v>
       </c>
       <c r="O54">
-        <v>23.40542992923051</v>
+        <v>23.62984424923052</v>
       </c>
       <c r="P54">
-        <v>93.62171971692206</v>
+        <v>94.51937699692205</v>
       </c>
       <c r="Q54">
-        <v>200.0217197169221</v>
+        <v>200.9193769969221</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09957123363383735</v>
+        <v>0.09955668521518617</v>
       </c>
       <c r="T54">
         <v>0.8315988236043392</v>
       </c>
       <c r="U54">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.06322478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.507392386771286</v>
+        <v>3.593791466982837</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.0827805146813109</v>
+        <v>0.07997514702794974</v>
       </c>
       <c r="C55">
-        <v>411.008828807887</v>
+        <v>473.2661291046322</v>
       </c>
       <c r="D55">
-        <v>886.729828807887</v>
+        <v>948.9871291046323</v>
       </c>
       <c r="E55">
         <v>267.421</v>
@@ -5797,45 +5797,45 @@
         <v>163.7</v>
       </c>
       <c r="M55">
-        <v>50.3994338683445</v>
+        <v>46.42675526834449</v>
       </c>
       <c r="N55">
-        <v>113.3005661316555</v>
+        <v>117.2732447316555</v>
       </c>
       <c r="O55">
-        <v>22.6601132263311</v>
+        <v>23.4546489463311</v>
       </c>
       <c r="P55">
-        <v>90.64045290532439</v>
+        <v>93.81859578532439</v>
       </c>
       <c r="Q55">
-        <v>197.0404529053244</v>
+        <v>200.2185957853244</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1005927236344802</v>
+        <v>0.1005778988400947</v>
       </c>
       <c r="T55">
         <v>0.847396673596823</v>
       </c>
       <c r="U55">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.06698478221340608</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.248052357644016</v>
+        <v>3.52598408081335</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.0829347504674087</v>
+        <v>0.08128619840163896</v>
       </c>
       <c r="C56">
-        <v>396.4566996305591</v>
+        <v>431.6835829588158</v>
       </c>
       <c r="D56">
-        <v>883.5346996305591</v>
+        <v>918.7615829588158</v>
       </c>
       <c r="E56">
         <v>278.778</v>
@@ -5879,37 +5879,37 @@
         <v>163.7</v>
       </c>
       <c r="M56">
-        <v>51.35036658284156</v>
+        <v>49.01991018284156</v>
       </c>
       <c r="N56">
-        <v>112.3496334171584</v>
+        <v>114.6800898171584</v>
       </c>
       <c r="O56">
-        <v>22.46992668343169</v>
+        <v>22.93601796343169</v>
       </c>
       <c r="P56">
-        <v>89.87970673372675</v>
+        <v>91.74407185372675</v>
       </c>
       <c r="Q56">
-        <v>196.2797067337268</v>
+        <v>198.1440718537268</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1016586262438466</v>
+        <v>0.1016435130573906</v>
       </c>
       <c r="T56">
         <v>0.8638813866324581</v>
       </c>
       <c r="U56">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.06698478221340608</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.187903239909867</v>
+        <v>3.339459403116163</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08308898625350651</v>
+        <v>0.08141004977532817</v>
       </c>
       <c r="C57">
-        <v>381.9275136247155</v>
+        <v>417.5704952663456</v>
       </c>
       <c r="D57">
-        <v>880.3625136247156</v>
+        <v>916.0054952663456</v>
       </c>
       <c r="E57">
         <v>290.1350000000001</v>
@@ -5961,37 +5961,37 @@
         <v>163.7</v>
       </c>
       <c r="M57">
-        <v>52.30129929733863</v>
+        <v>49.92768629733863</v>
       </c>
       <c r="N57">
-        <v>111.3987007026614</v>
+        <v>113.7723137026614</v>
       </c>
       <c r="O57">
-        <v>22.27974014053227</v>
+        <v>22.75446274053228</v>
       </c>
       <c r="P57">
-        <v>89.11896056212909</v>
+        <v>91.01785096212909</v>
       </c>
       <c r="Q57">
-        <v>195.5189605621291</v>
+        <v>197.4178509621291</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1027719023025181</v>
+        <v>0.1027564879065663</v>
       </c>
       <c r="T57">
         <v>0.8810987535807882</v>
       </c>
       <c r="U57">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.06698478221340608</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.129941362820597</v>
+        <v>3.278741959423142</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08324322203960433</v>
+        <v>0.0815339011490174</v>
       </c>
       <c r="C58">
-        <v>367.4210245533803</v>
+        <v>403.4738934636426</v>
       </c>
       <c r="D58">
-        <v>877.2130245533804</v>
+        <v>913.2658934636428</v>
       </c>
       <c r="E58">
         <v>301.4920000000001</v>
@@ -6043,37 +6043,37 @@
         <v>163.7</v>
       </c>
       <c r="M58">
-        <v>53.25223201183569</v>
+        <v>50.8354624118357</v>
       </c>
       <c r="N58">
-        <v>110.4477679881643</v>
+        <v>112.8645375881643</v>
       </c>
       <c r="O58">
-        <v>22.08955359763286</v>
+        <v>22.57290751763286</v>
       </c>
       <c r="P58">
-        <v>88.35821439053143</v>
+        <v>90.29163007053144</v>
       </c>
       <c r="Q58">
-        <v>194.7582143905315</v>
+        <v>196.6916300705315</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1039357818184021</v>
+        <v>0.1039200525216136</v>
       </c>
       <c r="T58">
         <v>0.8990987281176787</v>
       </c>
       <c r="U58">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.06698478221340608</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.074049552770229</v>
+        <v>3.220192995862014</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08339745782570213</v>
+        <v>0.08165775252270661</v>
       </c>
       <c r="C59">
-        <v>352.9369896906588</v>
+        <v>389.3936300731099</v>
       </c>
       <c r="D59">
-        <v>874.0859896906588</v>
+        <v>910.5426300731099</v>
       </c>
       <c r="E59">
         <v>312.849</v>
@@ -6125,37 +6125,37 @@
         <v>163.7</v>
       </c>
       <c r="M59">
-        <v>54.20316472633276</v>
+        <v>51.74323852633276</v>
       </c>
       <c r="N59">
-        <v>109.4968352736672</v>
+        <v>111.9567614736672</v>
       </c>
       <c r="O59">
-        <v>21.89936705473345</v>
+        <v>22.39135229473345</v>
       </c>
       <c r="P59">
-        <v>87.59746821893378</v>
+        <v>89.56540917893378</v>
       </c>
       <c r="Q59">
-        <v>193.9974682189338</v>
+        <v>195.9654091789338</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1051537952652574</v>
+        <v>0.1051377364210817</v>
       </c>
       <c r="T59">
         <v>0.917935910772564</v>
       </c>
       <c r="U59">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V59">
         <v>0.2</v>
       </c>
       <c r="W59">
-        <v>0.06698478221340608</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.020118858861979</v>
+        <v>3.163698381899522</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08786689361179992</v>
+        <v>0.08178160389639583</v>
       </c>
       <c r="C60">
-        <v>259.7417606391697</v>
+        <v>375.3295593709701</v>
       </c>
       <c r="D60">
-        <v>792.2477606391697</v>
+        <v>907.83555937097</v>
       </c>
       <c r="E60">
         <v>324.206</v>
@@ -6207,45 +6207,45 @@
         <v>163.7</v>
       </c>
       <c r="M60">
-        <v>61.28006324082982</v>
+        <v>52.65101464082983</v>
       </c>
       <c r="N60">
-        <v>102.4199367591702</v>
+        <v>111.0489853591702</v>
       </c>
       <c r="O60">
-        <v>20.48398735183403</v>
+        <v>22.20979707183403</v>
       </c>
       <c r="P60">
-        <v>81.93594940733614</v>
+        <v>88.83918828733613</v>
       </c>
       <c r="Q60">
-        <v>188.3359494073362</v>
+        <v>195.2391882873362</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1064298093524391</v>
+        <v>0.1064134052681436</v>
       </c>
       <c r="T60">
         <v>0.9376701021253008</v>
       </c>
       <c r="U60">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V60">
         <v>0.2</v>
       </c>
       <c r="W60">
-        <v>0.07442478221340607</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.671341890700426</v>
+        <v>3.109151858073669</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08809552939789773</v>
+        <v>0.08190545527008505</v>
       </c>
       <c r="C61">
-        <v>244.6083476311841</v>
+        <v>361.2815373612744</v>
       </c>
       <c r="D61">
-        <v>788.471347631184</v>
+        <v>905.1445373612744</v>
       </c>
       <c r="E61">
         <v>335.563</v>
@@ -6289,45 +6289,45 @@
         <v>163.7</v>
       </c>
       <c r="M61">
-        <v>62.33661605532688</v>
+        <v>53.55879075532689</v>
       </c>
       <c r="N61">
-        <v>101.3633839446731</v>
+        <v>110.1412092446731</v>
       </c>
       <c r="O61">
-        <v>20.27267678893462</v>
+        <v>22.02824184893462</v>
       </c>
       <c r="P61">
-        <v>81.09070715573849</v>
+        <v>88.11296739573848</v>
       </c>
       <c r="Q61">
-        <v>187.4907071557385</v>
+        <v>194.5129673957385</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1077680680292394</v>
+        <v>0.1077513018638426</v>
       </c>
       <c r="T61">
         <v>0.9583669369586594</v>
       </c>
       <c r="U61">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.07442478221340607</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.626064909502114</v>
+        <v>3.056454368953776</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08832416518399554</v>
+        <v>0.08202930664377428</v>
       </c>
       <c r="C62">
-        <v>229.5107659350584</v>
+        <v>347.2494217503698</v>
       </c>
       <c r="D62">
-        <v>784.7307659350583</v>
+        <v>902.4694217503699</v>
       </c>
       <c r="E62">
         <v>346.92</v>
@@ -6371,45 +6371,45 @@
         <v>163.7</v>
       </c>
       <c r="M62">
-        <v>63.39316886982395</v>
+        <v>54.46656686982395</v>
       </c>
       <c r="N62">
-        <v>100.3068311301761</v>
+        <v>109.233433130176</v>
       </c>
       <c r="O62">
-        <v>20.06136622603521</v>
+        <v>21.84668662603521</v>
       </c>
       <c r="P62">
-        <v>80.24546490414085</v>
+        <v>87.38674650414083</v>
       </c>
       <c r="Q62">
-        <v>186.6454649041409</v>
+        <v>193.7867465041409</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1091732396398797</v>
+        <v>0.1091560932893266</v>
       </c>
       <c r="T62">
         <v>0.9800986135336857</v>
       </c>
       <c r="U62">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V62">
         <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.07442478221340607</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.582297161010412</v>
+        <v>3.005513462804547</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08855280097009335</v>
+        <v>0.08595955801746348</v>
       </c>
       <c r="C63">
-        <v>214.4485079974053</v>
+        <v>258.5097477468194</v>
       </c>
       <c r="D63">
-        <v>781.0255079974053</v>
+        <v>825.0867477468194</v>
       </c>
       <c r="E63">
         <v>358.277</v>
@@ -6453,37 +6453,37 @@
         <v>163.7</v>
       </c>
       <c r="M63">
-        <v>64.44972168432102</v>
+        <v>60.77800358432103</v>
       </c>
       <c r="N63">
-        <v>99.25027831567897</v>
+        <v>102.921996415679</v>
       </c>
       <c r="O63">
-        <v>19.85005566313579</v>
+        <v>20.5843992831358</v>
       </c>
       <c r="P63">
-        <v>79.40022265254318</v>
+        <v>82.33759713254317</v>
       </c>
       <c r="Q63">
-        <v>185.8002226525432</v>
+        <v>188.7375971325432</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.110650471333117</v>
+        <v>0.1106329253007328</v>
       </c>
       <c r="T63">
         <v>1.002944735061277</v>
       </c>
       <c r="U63">
-        <v>0.09303097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.07442478221340607</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.539964420665978</v>
+        <v>2.693408640395518</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.09111263675619115</v>
+        <v>0.08614580939115271</v>
       </c>
       <c r="C64">
-        <v>163.8759567907057</v>
+        <v>243.8136520529763</v>
       </c>
       <c r="D64">
-        <v>741.8099567907057</v>
+        <v>821.7476520529763</v>
       </c>
       <c r="E64">
         <v>369.634</v>
@@ -6535,45 +6535,45 @@
         <v>163.7</v>
       </c>
       <c r="M64">
-        <v>68.81570429881808</v>
+        <v>61.77436429881809</v>
       </c>
       <c r="N64">
-        <v>94.88429570118191</v>
+        <v>101.9256357011819</v>
       </c>
       <c r="O64">
-        <v>18.97685914023638</v>
+        <v>20.38512714023638</v>
       </c>
       <c r="P64">
-        <v>75.90743656094553</v>
+        <v>81.54050856094553</v>
       </c>
       <c r="Q64">
-        <v>182.3074365609456</v>
+        <v>187.9405085609455</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1122054520628405</v>
+        <v>0.1121874853127393</v>
       </c>
       <c r="T64">
         <v>1.02699328403769</v>
       </c>
       <c r="U64">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.378817475865194</v>
+        <v>2.649966565550429</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.09137887254228896</v>
+        <v>0.08633206076484193</v>
       </c>
       <c r="C65">
-        <v>148.665255495987</v>
+        <v>229.1444738198594</v>
       </c>
       <c r="D65">
-        <v>737.956255495987</v>
+        <v>818.4354738198593</v>
       </c>
       <c r="E65">
         <v>380.991</v>
@@ -6617,45 +6617,45 @@
         <v>163.7</v>
       </c>
       <c r="M65">
-        <v>69.92563501331514</v>
+        <v>62.77072501331515</v>
       </c>
       <c r="N65">
-        <v>93.77436498668484</v>
+        <v>100.9292749866848</v>
       </c>
       <c r="O65">
-        <v>18.75487299733697</v>
+        <v>20.18585499733697</v>
       </c>
       <c r="P65">
-        <v>75.01949198934787</v>
+        <v>80.74341998934787</v>
       </c>
       <c r="Q65">
-        <v>181.4194919893479</v>
+        <v>187.1434199893479</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1138444858049815</v>
+        <v>0.1138260755956651</v>
       </c>
       <c r="T65">
         <v>1.052341754580395</v>
       </c>
       <c r="U65">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.341058468311778</v>
+        <v>2.607903604192486</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09164510832838677</v>
+        <v>0.08651831213853114</v>
       </c>
       <c r="C66">
-        <v>133.4943872104486</v>
+        <v>214.501888869424</v>
       </c>
       <c r="D66">
-        <v>734.1423872104486</v>
+        <v>815.149888869424</v>
       </c>
       <c r="E66">
         <v>392.3480000000001</v>
@@ -6699,45 +6699,45 @@
         <v>163.7</v>
       </c>
       <c r="M66">
-        <v>71.03556572781221</v>
+        <v>63.76708572781223</v>
       </c>
       <c r="N66">
-        <v>92.66443427218778</v>
+        <v>99.93291427218776</v>
       </c>
       <c r="O66">
-        <v>18.53288685443756</v>
+        <v>19.98658285443755</v>
       </c>
       <c r="P66">
-        <v>74.13154741775023</v>
+        <v>79.9463314177502</v>
       </c>
       <c r="Q66">
-        <v>180.5315474177503</v>
+        <v>186.3463314177502</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1155745769772413</v>
+        <v>0.1155556986720868</v>
       </c>
       <c r="T66">
         <v>1.079098473486583</v>
       </c>
       <c r="U66">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.304479429744406</v>
+        <v>2.567155110376977</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.09191134411448457</v>
+        <v>0.08670456351222036</v>
       </c>
       <c r="C67">
-        <v>118.3627375206265</v>
+        <v>199.8855782084237</v>
       </c>
       <c r="D67">
-        <v>730.3677375206265</v>
+        <v>811.8905782084237</v>
       </c>
       <c r="E67">
         <v>403.705</v>
@@ -6781,45 +6781,45 @@
         <v>163.7</v>
       </c>
       <c r="M67">
-        <v>72.14549644230928</v>
+        <v>64.76344644230929</v>
       </c>
       <c r="N67">
-        <v>91.55450355769071</v>
+        <v>98.9365535576907</v>
       </c>
       <c r="O67">
-        <v>18.31090071153814</v>
+        <v>19.78731071153814</v>
       </c>
       <c r="P67">
-        <v>73.24360284615257</v>
+        <v>79.14924284615256</v>
       </c>
       <c r="Q67">
-        <v>179.6436028461526</v>
+        <v>185.5492428461526</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1174035305022018</v>
+        <v>0.1173841573528755</v>
       </c>
       <c r="T67">
         <v>1.10738414775884</v>
       </c>
       <c r="U67">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.269025900056031</v>
+        <v>2.527660416371178</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09217757990058238</v>
+        <v>0.08895001488590959</v>
       </c>
       <c r="C68">
-        <v>103.2697045846353</v>
+        <v>151.1912092549711</v>
       </c>
       <c r="D68">
-        <v>726.6317045846353</v>
+        <v>774.5532092549711</v>
       </c>
       <c r="E68">
         <v>415.062</v>
@@ -6863,37 +6863,37 @@
         <v>163.7</v>
       </c>
       <c r="M68">
-        <v>73.25542715680633</v>
+        <v>68.68309895680635</v>
       </c>
       <c r="N68">
-        <v>90.44457284319365</v>
+        <v>95.01690104319364</v>
       </c>
       <c r="O68">
-        <v>18.08891456863873</v>
+        <v>19.00338020863873</v>
       </c>
       <c r="P68">
-        <v>72.35565827455493</v>
+        <v>76.01352083455491</v>
       </c>
       <c r="Q68">
-        <v>178.7556582745549</v>
+        <v>182.413520834555</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1193400695286305</v>
+        <v>0.1193201724266517</v>
       </c>
       <c r="T68">
         <v>1.137333685223582</v>
       </c>
       <c r="U68">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V68">
         <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.234646719752152</v>
+        <v>2.383410220073911</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.09244381568668018</v>
+        <v>0.08916746625959879</v>
       </c>
       <c r="C69">
-        <v>88.21469881227006</v>
+        <v>136.4000050348095</v>
       </c>
       <c r="D69">
-        <v>722.9336988122701</v>
+        <v>771.1190050348096</v>
       </c>
       <c r="E69">
         <v>426.4190000000001</v>
@@ -6945,37 +6945,37 @@
         <v>163.7</v>
       </c>
       <c r="M69">
-        <v>74.36535787130342</v>
+        <v>69.72375197130341</v>
       </c>
       <c r="N69">
-        <v>89.33464212869657</v>
+        <v>93.97624802869657</v>
       </c>
       <c r="O69">
-        <v>17.86692842573931</v>
+        <v>18.79524960573931</v>
       </c>
       <c r="P69">
-        <v>71.46771370295725</v>
+        <v>75.18099842295726</v>
       </c>
       <c r="Q69">
-        <v>177.8677137029573</v>
+        <v>181.5809984229573</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.121393974556661</v>
+        <v>0.1213735217473234</v>
       </c>
       <c r="T69">
         <v>1.169098346171036</v>
       </c>
       <c r="U69">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V69">
         <v>0.2</v>
       </c>
       <c r="W69">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.201293783636448</v>
+        <v>2.347836933207136</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09271005147277799</v>
+        <v>0.08938491763328801</v>
       </c>
       <c r="C70">
-        <v>73.1971425548254</v>
+        <v>121.6391194507116</v>
       </c>
       <c r="D70">
-        <v>719.2731425548254</v>
+        <v>767.7151194507117</v>
       </c>
       <c r="E70">
         <v>437.7760000000001</v>
@@ -7027,37 +7027,37 @@
         <v>163.7</v>
       </c>
       <c r="M70">
-        <v>75.47528858580047</v>
+        <v>70.76440498580048</v>
       </c>
       <c r="N70">
-        <v>88.22471141419952</v>
+        <v>92.93559501419951</v>
       </c>
       <c r="O70">
-        <v>17.6449422828399</v>
+        <v>18.5871190028399</v>
       </c>
       <c r="P70">
-        <v>70.57976913135961</v>
+        <v>74.34847601135961</v>
       </c>
       <c r="Q70">
-        <v>176.9797691313597</v>
+        <v>180.7484760113596</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1235762486489433</v>
+        <v>0.1235552054005371</v>
       </c>
       <c r="T70">
         <v>1.202848298427705</v>
       </c>
       <c r="U70">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V70">
         <v>0.2</v>
       </c>
       <c r="W70">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.168921816230029</v>
+        <v>2.313309919483501</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09297628725887579</v>
+        <v>0.08960236900697724</v>
       </c>
       <c r="C71">
-        <v>58.21646980429102</v>
+        <v>106.9081527681981</v>
       </c>
       <c r="D71">
-        <v>715.6494698042911</v>
+        <v>764.3411527681982</v>
       </c>
       <c r="E71">
         <v>449.1330000000002</v>
@@ -7109,37 +7109,37 @@
         <v>163.7</v>
       </c>
       <c r="M71">
-        <v>76.58521930029755</v>
+        <v>71.80505800029755</v>
       </c>
       <c r="N71">
-        <v>87.11478069970244</v>
+        <v>91.89494199970244</v>
       </c>
       <c r="O71">
-        <v>17.42295613994049</v>
+        <v>18.37898839994049</v>
       </c>
       <c r="P71">
-        <v>69.69182455976195</v>
+        <v>73.51595359976196</v>
       </c>
       <c r="Q71">
-        <v>176.091824559762</v>
+        <v>179.915953599762</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1258993146181471</v>
+        <v>0.1258776428378292</v>
       </c>
       <c r="T71">
         <v>1.238775666958999</v>
       </c>
       <c r="U71">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V71">
         <v>0.2</v>
       </c>
       <c r="W71">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.137488166719449</v>
+        <v>2.279783688766349</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0932425230449736</v>
+        <v>0.08981982038066645</v>
       </c>
       <c r="C72">
-        <v>43.27212590159479</v>
+        <v>92.20671224907994</v>
       </c>
       <c r="D72">
-        <v>712.0621259015949</v>
+        <v>760.99671224908</v>
       </c>
       <c r="E72">
         <v>460.4900000000001</v>
@@ -7191,37 +7191,37 @@
         <v>163.7</v>
       </c>
       <c r="M72">
-        <v>77.69515001479461</v>
+        <v>72.84571101479462</v>
       </c>
       <c r="N72">
-        <v>86.00484998520538</v>
+        <v>90.85428898520537</v>
       </c>
       <c r="O72">
-        <v>17.20096999704108</v>
+        <v>18.17085779704108</v>
       </c>
       <c r="P72">
-        <v>68.80387998816431</v>
+        <v>72.68343118816429</v>
       </c>
       <c r="Q72">
-        <v>175.2038799881643</v>
+        <v>179.0834311881643</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1283772516519645</v>
+        <v>0.1283549094376074</v>
       </c>
       <c r="T72">
         <v>1.277098193392378</v>
       </c>
       <c r="U72">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V72">
         <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.1069526214806</v>
+        <v>2.247215350355401</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.0935087588310714</v>
+        <v>0.09003727175435566</v>
       </c>
       <c r="C73">
-        <v>28.36356725357689</v>
+        <v>77.53441199906092</v>
       </c>
       <c r="D73">
-        <v>708.5105672535768</v>
+        <v>757.6814119990609</v>
       </c>
       <c r="E73">
         <v>471.847</v>
@@ -7273,37 +7273,37 @@
         <v>163.7</v>
       </c>
       <c r="M73">
-        <v>78.80508072929166</v>
+        <v>73.88636402929167</v>
       </c>
       <c r="N73">
-        <v>84.89491927070833</v>
+        <v>89.81363597070832</v>
       </c>
       <c r="O73">
-        <v>16.97898385414167</v>
+        <v>17.96272719414166</v>
       </c>
       <c r="P73">
-        <v>67.91593541656667</v>
+        <v>71.85090877656665</v>
       </c>
       <c r="Q73">
-        <v>174.3159354165667</v>
+        <v>178.2509087765667</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1310260808950107</v>
+        <v>0.131003022009784</v>
       </c>
       <c r="T73">
         <v>1.318063652683232</v>
       </c>
       <c r="U73">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V73">
         <v>0.2</v>
       </c>
       <c r="W73">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.077277232445662</v>
+        <v>2.215564429927861</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09377499461716921</v>
+        <v>0.09025472312804489</v>
       </c>
       <c r="C74">
-        <v>13.49026105839118</v>
+        <v>62.8908728193062</v>
       </c>
       <c r="D74">
-        <v>704.9942610583911</v>
+        <v>754.3948728193061</v>
       </c>
       <c r="E74">
         <v>483.204</v>
@@ -7355,37 +7355,37 @@
         <v>163.7</v>
       </c>
       <c r="M74">
-        <v>79.91501144378873</v>
+        <v>74.92701704378874</v>
       </c>
       <c r="N74">
-        <v>83.78498855621126</v>
+        <v>88.77298295621125</v>
       </c>
       <c r="O74">
-        <v>16.75699771124225</v>
+        <v>17.75459659124225</v>
       </c>
       <c r="P74">
-        <v>67.02799084496901</v>
+        <v>71.018386364969</v>
       </c>
       <c r="Q74">
-        <v>173.427990844969</v>
+        <v>177.418386364969</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1338641122268459</v>
+        <v>0.1338402854799733</v>
       </c>
       <c r="T74">
         <v>1.361955216209147</v>
       </c>
       <c r="U74">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V74">
         <v>0.2</v>
       </c>
       <c r="W74">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.048426159772806</v>
+        <v>2.184792701734418</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09404123040326701</v>
+        <v>0.0904721745017341</v>
       </c>
       <c r="C75">
-        <v>-1.348314960956259</v>
+        <v>48.27572206185857</v>
       </c>
       <c r="D75">
-        <v>701.5126850390437</v>
+        <v>751.1367220618586</v>
       </c>
       <c r="E75">
         <v>494.561</v>
@@ -7437,37 +7437,37 @@
         <v>163.7</v>
       </c>
       <c r="M75">
-        <v>81.0249421582858</v>
+        <v>75.9676700582858</v>
       </c>
       <c r="N75">
-        <v>82.67505784171419</v>
+        <v>87.73232994171418</v>
       </c>
       <c r="O75">
-        <v>16.53501156834284</v>
+        <v>17.54646598834284</v>
       </c>
       <c r="P75">
-        <v>66.14004627337135</v>
+        <v>70.18586395337135</v>
       </c>
       <c r="Q75">
-        <v>172.5400462733714</v>
+        <v>176.5858639533714</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.13691236810178</v>
+        <v>0.136887716614621</v>
       </c>
       <c r="T75">
         <v>1.409098006662908</v>
       </c>
       <c r="U75">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V75">
         <v>0.2</v>
       </c>
       <c r="W75">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.020365527447151</v>
+        <v>2.154864034587371</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1039570661893648</v>
+        <v>0.09068962587542333</v>
       </c>
       <c r="C76">
-        <v>-121.6892793701351</v>
+        <v>33.68859348878266</v>
       </c>
       <c r="D76">
-        <v>592.5287206298649</v>
+        <v>747.9065934887826</v>
       </c>
       <c r="E76">
         <v>505.918</v>
@@ -7519,45 +7519,45 @@
         <v>163.7</v>
       </c>
       <c r="M76">
-        <v>95.83368627278287</v>
+        <v>77.00832307278287</v>
       </c>
       <c r="N76">
-        <v>67.86631372721712</v>
+        <v>86.69167692721712</v>
       </c>
       <c r="O76">
-        <v>13.57326274544342</v>
+        <v>17.33833538544343</v>
       </c>
       <c r="P76">
-        <v>54.2930509817737</v>
+        <v>69.35334154177369</v>
       </c>
       <c r="Q76">
-        <v>160.6930509817737</v>
+        <v>175.7533415417737</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1401951051978628</v>
+        <v>0.140169565528857</v>
       </c>
       <c r="T76">
         <v>1.459867165613112</v>
       </c>
       <c r="U76">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V76">
         <v>0.2</v>
       </c>
       <c r="W76">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.708167622124449</v>
+        <v>2.125744250336191</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1043537019754626</v>
+        <v>0.09090707724911254</v>
       </c>
       <c r="C77">
-        <v>-136.705668381481</v>
+        <v>19.12912713493029</v>
       </c>
       <c r="D77">
-        <v>588.869331618519</v>
+        <v>744.7041271349303</v>
       </c>
       <c r="E77">
         <v>517.2750000000001</v>
@@ -7601,45 +7601,45 @@
         <v>163.7</v>
       </c>
       <c r="M77">
-        <v>97.12873608727995</v>
+        <v>78.04897608727994</v>
       </c>
       <c r="N77">
-        <v>66.57126391272004</v>
+        <v>85.65102391272005</v>
       </c>
       <c r="O77">
-        <v>13.31425278254401</v>
+        <v>17.13020478254401</v>
       </c>
       <c r="P77">
-        <v>53.25701113017603</v>
+        <v>68.52081913017604</v>
       </c>
       <c r="Q77">
-        <v>159.6570111301761</v>
+        <v>174.9208191301761</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1437404612616323</v>
+        <v>0.143713962356232</v>
       </c>
       <c r="T77">
         <v>1.514697857279332</v>
       </c>
       <c r="U77">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V77">
         <v>0.2</v>
       </c>
       <c r="W77">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.685392053829456</v>
+        <v>2.097400993665041</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1047503377615604</v>
+        <v>0.09112452862280176</v>
       </c>
       <c r="C78">
-        <v>-151.6771349003457</v>
+        <v>4.596969174215133</v>
       </c>
       <c r="D78">
-        <v>585.2548650996544</v>
+        <v>741.5289691742151</v>
       </c>
       <c r="E78">
         <v>528.6320000000001</v>
@@ -7683,45 +7683,45 @@
         <v>163.7</v>
       </c>
       <c r="M78">
-        <v>98.42378590177701</v>
+        <v>79.08962910177701</v>
       </c>
       <c r="N78">
-        <v>65.27621409822298</v>
+        <v>84.61037089822298</v>
       </c>
       <c r="O78">
-        <v>13.0552428196446</v>
+        <v>16.9220741796446</v>
       </c>
       <c r="P78">
-        <v>52.22097127857838</v>
+        <v>67.68829671857839</v>
       </c>
       <c r="Q78">
-        <v>158.6209712785784</v>
+        <v>174.0882967185784</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1475812636640493</v>
+        <v>0.1475537255858881</v>
       </c>
       <c r="T78">
         <v>1.574097773251071</v>
       </c>
       <c r="U78">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V78">
         <v>0.2</v>
       </c>
       <c r="W78">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.663215842594858</v>
+        <v>2.069803612169449</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1051469735476583</v>
+        <v>0.09134197999649098</v>
       </c>
       <c r="C79">
-        <v>-166.6045010800719</v>
+        <v>-9.908228210705374</v>
       </c>
       <c r="D79">
-        <v>581.684498919928</v>
+        <v>738.3807717892946</v>
       </c>
       <c r="E79">
         <v>539.989</v>
@@ -7765,45 +7765,45 @@
         <v>163.7</v>
       </c>
       <c r="M79">
-        <v>99.71883571627407</v>
+        <v>80.13028211627407</v>
       </c>
       <c r="N79">
-        <v>63.98116428372592</v>
+        <v>83.56971788372591</v>
       </c>
       <c r="O79">
-        <v>12.79623285674518</v>
+        <v>16.71394357674518</v>
       </c>
       <c r="P79">
-        <v>51.18493142698073</v>
+        <v>66.85577430698073</v>
       </c>
       <c r="Q79">
-        <v>157.5849314269808</v>
+        <v>173.2557743069808</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1517560488840677</v>
+        <v>0.151727381270297</v>
       </c>
       <c r="T79">
         <v>1.638662899307308</v>
       </c>
       <c r="U79">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V79">
         <v>0.2</v>
       </c>
       <c r="W79">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.641615636846873</v>
+        <v>2.042923045777638</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1055436093337561</v>
+        <v>0.0915594313701802</v>
       </c>
       <c r="C80">
-        <v>-181.4885691333587</v>
+        <v>-24.3868069554436</v>
       </c>
       <c r="D80">
-        <v>578.1574308666413</v>
+        <v>735.2591930445565</v>
       </c>
       <c r="E80">
         <v>551.3460000000001</v>
@@ -7847,45 +7847,45 @@
         <v>163.7</v>
       </c>
       <c r="M80">
-        <v>101.0138855307711</v>
+        <v>81.17093513077114</v>
       </c>
       <c r="N80">
-        <v>62.68611446922884</v>
+        <v>82.52906486922885</v>
       </c>
       <c r="O80">
-        <v>12.53722289384577</v>
+        <v>16.50581297384577</v>
       </c>
       <c r="P80">
-        <v>50.14889157538308</v>
+        <v>66.02325189538308</v>
       </c>
       <c r="Q80">
-        <v>156.5488915753831</v>
+        <v>172.4232518953831</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1563103600331787</v>
+        <v>0.156280460198743</v>
       </c>
       <c r="T80">
         <v>1.709097582277749</v>
       </c>
       <c r="U80">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V80">
         <v>0.2</v>
       </c>
       <c r="W80">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.620569282528324</v>
+        <v>2.016731724677924</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1059402451198539</v>
+        <v>0.1007512827438694</v>
       </c>
       <c r="C81">
-        <v>-196.3301219331727</v>
+        <v>-147.2169861234677</v>
       </c>
       <c r="D81">
-        <v>574.6728780668274</v>
+        <v>623.7860138765324</v>
       </c>
       <c r="E81">
         <v>562.7030000000001</v>
@@ -7929,37 +7929,37 @@
         <v>163.7</v>
       </c>
       <c r="M81">
-        <v>102.3089353452682</v>
+        <v>94.95187074526821</v>
       </c>
       <c r="N81">
-        <v>61.39106465473178</v>
+        <v>68.74812925473178</v>
       </c>
       <c r="O81">
-        <v>12.27821293094636</v>
+        <v>13.74962585094636</v>
       </c>
       <c r="P81">
-        <v>49.11285172378543</v>
+        <v>54.99850340378542</v>
       </c>
       <c r="Q81">
-        <v>155.5128517237854</v>
+        <v>161.3985034037855</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1612984151012527</v>
+        <v>0.161267165691803</v>
       </c>
       <c r="T81">
         <v>1.786240330292994</v>
       </c>
       <c r="U81">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V81">
         <v>0.2</v>
       </c>
       <c r="W81">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.600055747306446</v>
+        <v>1.724031329926775</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1063368809059517</v>
+        <v>0.1010823341175586</v>
       </c>
       <c r="C82">
-        <v>-211.1299235920592</v>
+        <v>-161.9615929458035</v>
       </c>
       <c r="D82">
-        <v>571.2300764079408</v>
+        <v>620.3984070541965</v>
       </c>
       <c r="E82">
         <v>574.0600000000001</v>
@@ -8011,37 +8011,37 @@
         <v>163.7</v>
       </c>
       <c r="M82">
-        <v>103.6039851597653</v>
+        <v>96.15379315976527</v>
       </c>
       <c r="N82">
-        <v>60.09601484023472</v>
+        <v>67.54620684023472</v>
       </c>
       <c r="O82">
-        <v>12.01920296804694</v>
+        <v>13.50924136804694</v>
       </c>
       <c r="P82">
-        <v>48.07681187218778</v>
+        <v>54.03696547218777</v>
       </c>
       <c r="Q82">
-        <v>154.4768118721878</v>
+        <v>160.4369654721878</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1667852756761341</v>
+        <v>0.1667525417341689</v>
       </c>
       <c r="T82">
         <v>1.871097353109764</v>
       </c>
       <c r="U82">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V82">
         <v>0.2</v>
       </c>
       <c r="W82">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.580055050465115</v>
+        <v>1.70248093830269</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1067335166920495</v>
+        <v>0.1014133854912478</v>
       </c>
       <c r="C83">
-        <v>-225.8887200207538</v>
+        <v>-176.6696042239267</v>
       </c>
       <c r="D83">
-        <v>567.8282799792463</v>
+        <v>617.0473957760734</v>
       </c>
       <c r="E83">
         <v>585.4170000000001</v>
@@ -8093,37 +8093,37 @@
         <v>163.7</v>
       </c>
       <c r="M83">
-        <v>104.8990349742623</v>
+        <v>97.35571557426235</v>
       </c>
       <c r="N83">
-        <v>58.80096502573764</v>
+        <v>66.34428442573764</v>
       </c>
       <c r="O83">
-        <v>11.76019300514753</v>
+        <v>13.26885688514753</v>
       </c>
       <c r="P83">
-        <v>47.04077202059011</v>
+        <v>53.07542754059011</v>
       </c>
       <c r="Q83">
-        <v>153.4407720205901</v>
+        <v>159.4754275405901</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1728497005220556</v>
+        <v>0.1728153257809945</v>
       </c>
       <c r="T83">
         <v>1.964886694117772</v>
       </c>
       <c r="U83">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V83">
         <v>0.2</v>
       </c>
       <c r="W83">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.560548197990237</v>
+        <v>1.681462655113768</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1071301524781473</v>
+        <v>0.1017444368649371</v>
       </c>
       <c r="C84">
-        <v>-240.607239466951</v>
+        <v>-191.3416097720046</v>
       </c>
       <c r="D84">
-        <v>564.4667605330491</v>
+        <v>613.7323902279954</v>
       </c>
       <c r="E84">
         <v>596.7740000000001</v>
@@ -8175,37 +8175,37 @@
         <v>163.7</v>
       </c>
       <c r="M84">
-        <v>106.1940847887594</v>
+        <v>98.55763798875941</v>
       </c>
       <c r="N84">
-        <v>57.50591521124058</v>
+        <v>65.14236201124058</v>
       </c>
       <c r="O84">
-        <v>11.50118304224812</v>
+        <v>13.02847240224812</v>
       </c>
       <c r="P84">
-        <v>46.00473216899246</v>
+        <v>52.11388960899247</v>
       </c>
       <c r="Q84">
-        <v>152.4047321689925</v>
+        <v>158.5138896089925</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1795879503508573</v>
+        <v>0.1795517524996894</v>
       </c>
       <c r="T84">
         <v>2.069097073015559</v>
       </c>
       <c r="U84">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V84">
         <v>0.2</v>
       </c>
       <c r="W84">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.541517122404991</v>
+        <v>1.660957012978234</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1075267882642451</v>
+        <v>0.1020754882386263</v>
       </c>
       <c r="C85">
-        <v>-255.286193035051</v>
+        <v>-205.9781867971408</v>
       </c>
       <c r="D85">
-        <v>561.144806964949</v>
+        <v>610.4528132028593</v>
       </c>
       <c r="E85">
         <v>608.1310000000001</v>
@@ -8257,37 +8257,37 @@
         <v>163.7</v>
       </c>
       <c r="M85">
-        <v>107.4891346032565</v>
+        <v>99.75956040325647</v>
       </c>
       <c r="N85">
-        <v>56.21086539674351</v>
+        <v>63.94043959674352</v>
       </c>
       <c r="O85">
-        <v>11.2421730793487</v>
+        <v>12.7880879193487</v>
       </c>
       <c r="P85">
-        <v>44.96869231739481</v>
+        <v>51.15235167739481</v>
       </c>
       <c r="Q85">
-        <v>151.3686923173948</v>
+        <v>157.5523516773949</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1871189354536356</v>
+        <v>0.1870807000088192</v>
       </c>
       <c r="T85">
         <v>2.185567496489556</v>
       </c>
       <c r="U85">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V85">
         <v>0.2</v>
       </c>
       <c r="W85">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.522944626954328</v>
+        <v>1.640945482701388</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1079234240503429</v>
+        <v>0.1024065396123155</v>
       </c>
       <c r="C86">
-        <v>-269.9262751876596</v>
+        <v>-220.5799002344224</v>
       </c>
       <c r="D86">
-        <v>557.8617248123404</v>
+        <v>607.2080997655776</v>
       </c>
       <c r="E86">
         <v>619.4880000000001</v>
@@ -8339,37 +8339,37 @@
         <v>163.7</v>
       </c>
       <c r="M86">
-        <v>108.7841844177535</v>
+        <v>100.9614828177535</v>
       </c>
       <c r="N86">
-        <v>54.91581558224645</v>
+        <v>62.73851718224645</v>
       </c>
       <c r="O86">
-        <v>10.98316311644929</v>
+        <v>12.54770343644929</v>
       </c>
       <c r="P86">
-        <v>43.93265246579716</v>
+        <v>50.19081374579716</v>
       </c>
       <c r="Q86">
-        <v>150.3326524657972</v>
+        <v>156.5908137457972</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1955912936942612</v>
+        <v>0.19555076595659</v>
       </c>
       <c r="T86">
         <v>2.316596722897802</v>
       </c>
       <c r="U86">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V86">
         <v>0.2</v>
       </c>
       <c r="W86">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.5048143337763</v>
+        <v>1.621410417431134</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1547362335885957</v>
+        <v>0.1027375909860047</v>
       </c>
       <c r="C87">
-        <v>-509.1518816998206</v>
+        <v>-235.1473030713413</v>
       </c>
       <c r="D87">
-        <v>329.9931183001794</v>
+        <v>603.9976969286587</v>
       </c>
       <c r="E87">
         <v>630.845</v>
@@ -8421,45 +8421,45 @@
         <v>163.7</v>
       </c>
       <c r="M87">
-        <v>173.2127972322506</v>
+        <v>102.1634052322506</v>
       </c>
       <c r="N87">
-        <v>-9.51279723225062</v>
+        <v>61.53659476774939</v>
       </c>
       <c r="O87">
-        <v>-1.902559446450124</v>
+        <v>12.30731895354988</v>
       </c>
       <c r="P87">
-        <v>-7.610237785800495</v>
+        <v>49.22927581419951</v>
       </c>
       <c r="Q87">
-        <v>98.78976221419954</v>
+        <v>155.6292758141996</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2069862537308416</v>
+        <v>0.2051501740307304</v>
       </c>
       <c r="T87">
-        <v>2.492825437045726</v>
+        <v>2.465096512827148</v>
       </c>
       <c r="U87">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V87">
-        <v>0.1890160572610631</v>
+        <v>0.2</v>
       </c>
       <c r="W87">
-        <v>0.1455156417987876</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.9450802863053156</v>
+        <v>1.602335000755473</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1560725433662633</v>
+        <v>0.1030686423596939</v>
       </c>
       <c r="C88">
-        <v>-524.3122698935382</v>
+        <v>-249.6809366619763</v>
       </c>
       <c r="D88">
-        <v>326.1897301064618</v>
+        <v>600.8210633380237</v>
       </c>
       <c r="E88">
         <v>642.202</v>
@@ -8503,45 +8503,45 @@
         <v>163.7</v>
       </c>
       <c r="M88">
-        <v>175.2505948467477</v>
+        <v>103.3653276467477</v>
       </c>
       <c r="N88">
-        <v>-11.55059484674769</v>
+        <v>60.33467235325233</v>
       </c>
       <c r="O88">
-        <v>-2.310118969349537</v>
+        <v>12.06693447065047</v>
       </c>
       <c r="P88">
-        <v>-9.240475877398149</v>
+        <v>48.26773788260186</v>
       </c>
       <c r="Q88">
-        <v>97.15952412260188</v>
+        <v>154.6677378826019</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2184995575687589</v>
+        <v>0.2161209261154623</v>
       </c>
       <c r="T88">
-        <v>2.670884396834706</v>
+        <v>2.634810558460687</v>
       </c>
       <c r="U88">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V88">
-        <v>0.1868181961301205</v>
+        <v>0.2</v>
       </c>
       <c r="W88">
-        <v>0.1459100061705082</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.9340909806506027</v>
+        <v>1.583703198421107</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1574088531439309</v>
+        <v>0.1033996937333831</v>
       </c>
       <c r="C89">
-        <v>-539.3859839521425</v>
+        <v>-264.181331031314</v>
       </c>
       <c r="D89">
-        <v>322.4730160478576</v>
+        <v>597.677668968686</v>
       </c>
       <c r="E89">
         <v>653.5590000000001</v>
@@ -8585,45 +8585,45 @@
         <v>163.7</v>
       </c>
       <c r="M89">
-        <v>177.2883924612448</v>
+        <v>104.5672500612447</v>
       </c>
       <c r="N89">
-        <v>-13.58839246124478</v>
+        <v>59.13274993875525</v>
       </c>
       <c r="O89">
-        <v>-2.717678492248956</v>
+        <v>11.82654998775105</v>
       </c>
       <c r="P89">
-        <v>-10.87071396899582</v>
+        <v>47.3061999510042</v>
       </c>
       <c r="Q89">
-        <v>95.5292860310042</v>
+        <v>153.7061999510042</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2317841389202019</v>
+        <v>0.2287794862132298</v>
       </c>
       <c r="T89">
-        <v>2.876337042745068</v>
+        <v>2.830634457268616</v>
       </c>
       <c r="U89">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V89">
-        <v>0.184670860542418</v>
+        <v>0.2</v>
       </c>
       <c r="W89">
-        <v>0.146295304694603</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.9233543027120898</v>
+        <v>1.565499713381784</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1587451629215985</v>
+        <v>0.1037307451070724</v>
       </c>
       <c r="C90">
-        <v>-554.3759532786402</v>
+        <v>-278.649005170065</v>
       </c>
       <c r="D90">
-        <v>318.8400467213599</v>
+        <v>594.566994829935</v>
       </c>
       <c r="E90">
         <v>664.9160000000001</v>
@@ -8667,45 +8667,45 @@
         <v>163.7</v>
       </c>
       <c r="M90">
-        <v>179.3261900757418</v>
+        <v>105.7691724757418</v>
       </c>
       <c r="N90">
-        <v>-15.62619007574182</v>
+        <v>57.93082752425819</v>
       </c>
       <c r="O90">
-        <v>-3.125238015148364</v>
+        <v>11.58616550485164</v>
       </c>
       <c r="P90">
-        <v>-12.50095206059345</v>
+        <v>46.34466201940656</v>
       </c>
       <c r="Q90">
-        <v>93.89904793940659</v>
+        <v>152.7446620194066</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2472828171635521</v>
+        <v>0.243547806327292</v>
       </c>
       <c r="T90">
-        <v>3.116031796307158</v>
+        <v>3.059095672544534</v>
       </c>
       <c r="U90">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V90">
-        <v>0.1825723280362542</v>
+        <v>0.2</v>
       </c>
       <c r="W90">
-        <v>0.1466718464340593</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.9128616401812708</v>
+        <v>1.547709943911537</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.160081472699266</v>
+        <v>0.1040617964807616</v>
       </c>
       <c r="C91">
-        <v>-569.2849767364986</v>
+        <v>-293.0844673203227</v>
       </c>
       <c r="D91">
-        <v>315.2880232635014</v>
+        <v>591.4885326796773</v>
       </c>
       <c r="E91">
         <v>676.273</v>
@@ -8749,45 +8749,45 @@
         <v>163.7</v>
       </c>
       <c r="M91">
-        <v>181.3639876902389</v>
+        <v>106.9710948902389</v>
       </c>
       <c r="N91">
-        <v>-17.66398769023888</v>
+        <v>56.72890510976113</v>
       </c>
       <c r="O91">
-        <v>-3.532797538047777</v>
+        <v>11.34578102195223</v>
       </c>
       <c r="P91">
-        <v>-14.13119015219111</v>
+        <v>45.3831240878089</v>
       </c>
       <c r="Q91">
-        <v>92.26880984780892</v>
+        <v>151.7831240878089</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2655994369056932</v>
+        <v>0.2610012755530018</v>
       </c>
       <c r="T91">
-        <v>3.399307414153263</v>
+        <v>3.329095290597891</v>
       </c>
       <c r="U91">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V91">
-        <v>0.1805209535639367</v>
+        <v>0.2</v>
       </c>
       <c r="W91">
-        <v>0.147039926561393</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.9026047678196835</v>
+        <v>1.530319944541744</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1614177824769336</v>
+        <v>0.1043928478544508</v>
       </c>
       <c r="C92">
-        <v>-584.1157298408825</v>
+        <v>-307.4882152523935</v>
       </c>
       <c r="D92">
-        <v>311.8142701591176</v>
+        <v>588.4417847476066</v>
       </c>
       <c r="E92">
         <v>687.6300000000001</v>
@@ -8831,45 +8831,45 @@
         <v>163.7</v>
       </c>
       <c r="M92">
-        <v>183.401785304736</v>
+        <v>108.1730173047359</v>
       </c>
       <c r="N92">
-        <v>-19.70178530473598</v>
+        <v>55.52698269526405</v>
       </c>
       <c r="O92">
-        <v>-3.940357060947196</v>
+        <v>11.10539653905281</v>
       </c>
       <c r="P92">
-        <v>-15.76142824378878</v>
+        <v>44.42158615621124</v>
       </c>
       <c r="Q92">
-        <v>90.63857175621125</v>
+        <v>150.8215861562113</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2875793805962625</v>
+        <v>0.2819454386238536</v>
       </c>
       <c r="T92">
-        <v>3.73923815556859</v>
+        <v>3.65309483226192</v>
       </c>
       <c r="U92">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V92">
-        <v>0.178515165191004</v>
+        <v>0.2</v>
       </c>
       <c r="W92">
-        <v>0.1473998271303415</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.8925758259550202</v>
+        <v>1.513316389602391</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1627540922546012</v>
+        <v>0.1469815930701214</v>
       </c>
       <c r="C93">
-        <v>-598.8707714796842</v>
+        <v>-553.3707548481361</v>
       </c>
       <c r="D93">
-        <v>308.4162285203159</v>
+        <v>353.916245151864</v>
       </c>
       <c r="E93">
         <v>698.9870000000001</v>
@@ -8913,37 +8913,37 @@
         <v>163.7</v>
       </c>
       <c r="M93">
-        <v>185.439582919233</v>
+        <v>168.077001319233</v>
       </c>
       <c r="N93">
-        <v>-21.73958291923304</v>
+        <v>-4.377001319233017</v>
       </c>
       <c r="O93">
-        <v>-4.347916583846609</v>
+        <v>-0.8754002638466034</v>
       </c>
       <c r="P93">
-        <v>-17.39166633538644</v>
+        <v>-3.501601055386414</v>
       </c>
       <c r="Q93">
-        <v>89.0083336646136</v>
+        <v>102.8983989446136</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3144437562180695</v>
+        <v>0.3090604319460724</v>
       </c>
       <c r="T93">
-        <v>4.154709061742878</v>
+        <v>4.072555155355404</v>
       </c>
       <c r="U93">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V93">
-        <v>0.176553460079015</v>
+        <v>0.194791671335307</v>
       </c>
       <c r="W93">
-        <v>0.1477518177966757</v>
+        <v>0.1309518177966757</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8827673003950749</v>
+        <v>0.9739583566765351</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1640904020322687</v>
+        <v>0.148149902847789</v>
       </c>
       <c r="C94">
-        <v>-613.5525501998313</v>
+        <v>-568.5553660555727</v>
       </c>
       <c r="D94">
-        <v>305.0914498001687</v>
+        <v>350.0886339444273</v>
       </c>
       <c r="E94">
         <v>710.3440000000001</v>
@@ -8995,37 +8995,37 @@
         <v>163.7</v>
       </c>
       <c r="M94">
-        <v>187.4773805337301</v>
+        <v>169.9240013337301</v>
       </c>
       <c r="N94">
-        <v>-23.77738053373008</v>
+        <v>-6.224001333730087</v>
       </c>
       <c r="O94">
-        <v>-4.755476106746016</v>
+        <v>-1.244800266746017</v>
       </c>
       <c r="P94">
-        <v>-19.02190442698407</v>
+        <v>-4.97920106698407</v>
       </c>
       <c r="Q94">
-        <v>87.37809557301597</v>
+        <v>101.420798933016</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3480242257453283</v>
+        <v>0.3419679859393316</v>
       </c>
       <c r="T94">
-        <v>4.674047694460739</v>
+        <v>4.581624549774831</v>
       </c>
       <c r="U94">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V94">
-        <v>0.1746344007303301</v>
+        <v>0.1926743705599232</v>
       </c>
       <c r="W94">
-        <v>0.1480961564920027</v>
+        <v>0.1312961564920027</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8731720036516504</v>
+        <v>0.9633718527996161</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1654267118099363</v>
+        <v>0.1493182126254566</v>
       </c>
       <c r="C95">
-        <v>-628.1634100913279</v>
+        <v>-583.658071691216</v>
       </c>
       <c r="D95">
-        <v>301.8375899086722</v>
+        <v>346.3429283087839</v>
       </c>
       <c r="E95">
         <v>721.701</v>
@@ -9077,37 +9077,37 @@
         <v>163.7</v>
       </c>
       <c r="M95">
-        <v>189.5151781482271</v>
+        <v>171.7710013482271</v>
       </c>
       <c r="N95">
-        <v>-25.81517814822715</v>
+        <v>-8.071001348227128</v>
       </c>
       <c r="O95">
-        <v>-5.16303562964543</v>
+        <v>-1.614200269645426</v>
       </c>
       <c r="P95">
-        <v>-20.65214251858172</v>
+        <v>-6.456801078581702</v>
       </c>
       <c r="Q95">
-        <v>85.74785748141832</v>
+        <v>99.94319892141833</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.391199115137518</v>
+        <v>0.3842776982163789</v>
       </c>
       <c r="T95">
-        <v>5.341768793669416</v>
+        <v>5.236142342599806</v>
       </c>
       <c r="U95">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V95">
-        <v>0.1727566114751652</v>
+        <v>0.1906026031345477</v>
       </c>
       <c r="W95">
-        <v>0.1484330900540968</v>
+        <v>0.1316330900540968</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8637830573758261</v>
+        <v>0.9530130156727387</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1667630215876039</v>
+        <v>0.1504865224031242</v>
       </c>
       <c r="C96">
-        <v>-642.7055962987394</v>
+        <v>-598.6814729228524</v>
       </c>
       <c r="D96">
-        <v>298.6524037012609</v>
+        <v>342.6765270771479</v>
       </c>
       <c r="E96">
         <v>733.0580000000002</v>
@@ -9159,37 +9159,37 @@
         <v>163.7</v>
       </c>
       <c r="M96">
-        <v>191.5529757627242</v>
+        <v>173.6180013627242</v>
       </c>
       <c r="N96">
-        <v>-27.85297576272424</v>
+        <v>-9.918001362724226</v>
       </c>
       <c r="O96">
-        <v>-5.570595152544849</v>
+        <v>-1.983600272544845</v>
       </c>
       <c r="P96">
-        <v>-22.28238061017939</v>
+        <v>-7.934401090179381</v>
       </c>
       <c r="Q96">
-        <v>84.11761938982065</v>
+        <v>98.46559890982066</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4487656343271045</v>
+        <v>0.4406906479191089</v>
       </c>
       <c r="T96">
-        <v>6.232063592614321</v>
+        <v>6.108832733033109</v>
       </c>
       <c r="U96">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V96">
-        <v>0.1709187751828762</v>
+        <v>0.1885749158671589</v>
       </c>
       <c r="W96">
-        <v>0.1487628548169975</v>
+        <v>0.1319628548169975</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8545938759143811</v>
+        <v>0.9428745793357944</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1680993313652715</v>
+        <v>0.1516548321807917</v>
       </c>
       <c r="C97">
-        <v>-657.181260187358</v>
+        <v>-613.6280619277456</v>
       </c>
       <c r="D97">
-        <v>295.5337398126421</v>
+        <v>339.0869380722545</v>
       </c>
       <c r="E97">
         <v>744.4150000000002</v>
@@ -9241,37 +9241,37 @@
         <v>163.7</v>
       </c>
       <c r="M97">
-        <v>193.5907733772213</v>
+        <v>175.4650013772213</v>
       </c>
       <c r="N97">
-        <v>-29.89077337722131</v>
+        <v>-11.7650013772213</v>
       </c>
       <c r="O97">
-        <v>-5.978154675444262</v>
+        <v>-2.353000275444259</v>
       </c>
       <c r="P97">
-        <v>-23.91261870177705</v>
+        <v>-9.412001101777037</v>
       </c>
       <c r="Q97">
-        <v>82.48738129822299</v>
+        <v>96.987998898223</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5293587611925255</v>
+        <v>0.5196687775029308</v>
       </c>
       <c r="T97">
-        <v>7.478476311137188</v>
+        <v>7.330599279639735</v>
       </c>
       <c r="U97">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V97">
-        <v>0.1691196301809512</v>
+        <v>0.1865899167527678</v>
       </c>
       <c r="W97">
-        <v>0.1490856771638371</v>
+        <v>0.132285677163837</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.845598150904756</v>
+        <v>0.9329495837638387</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.169435641142939</v>
+        <v>0.1528231419584593</v>
       </c>
       <c r="C98">
-        <v>-671.5924641890307</v>
+        <v>-628.5002275419251</v>
       </c>
       <c r="D98">
-        <v>292.4795358109693</v>
+        <v>335.5717724580747</v>
       </c>
       <c r="E98">
         <v>755.7719999999999</v>
@@ -9323,37 +9323,37 @@
         <v>163.7</v>
       </c>
       <c r="M98">
-        <v>195.6285709917183</v>
+        <v>177.3120013917183</v>
       </c>
       <c r="N98">
-        <v>-31.92857099171835</v>
+        <v>-13.61200139171834</v>
       </c>
       <c r="O98">
-        <v>-6.38571419834367</v>
+        <v>-2.722400278343668</v>
       </c>
       <c r="P98">
-        <v>-25.54285679337467</v>
+        <v>-10.88960111337467</v>
       </c>
       <c r="Q98">
-        <v>80.85714320662535</v>
+        <v>95.51039888662537</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6502484514906556</v>
+        <v>0.6381359718786623</v>
       </c>
       <c r="T98">
-        <v>9.348095388921465</v>
+        <v>9.163249099549649</v>
       </c>
       <c r="U98">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V98">
-        <v>0.1673579673665663</v>
+        <v>0.1846462717865931</v>
       </c>
       <c r="W98">
-        <v>0.1494017740451175</v>
+        <v>0.1326017740451175</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8367898368328316</v>
+        <v>0.9232313589329656</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1707719509206066</v>
+        <v>0.1539914517361269</v>
       </c>
       <c r="C99">
-        <v>-685.9411863505819</v>
+        <v>-643.3002605616919</v>
       </c>
       <c r="D99">
-        <v>289.487813649418</v>
+        <v>332.128739438308</v>
       </c>
       <c r="E99">
         <v>767.1289999999999</v>
@@ -9405,37 +9405,37 @@
         <v>163.7</v>
       </c>
       <c r="M99">
-        <v>197.6663686062154</v>
+        <v>179.1590014062154</v>
       </c>
       <c r="N99">
-        <v>-33.96636860621538</v>
+        <v>-15.45900140621538</v>
       </c>
       <c r="O99">
-        <v>-6.793273721243077</v>
+        <v>-3.091800281243076</v>
       </c>
       <c r="P99">
-        <v>-27.17309488497231</v>
+        <v>-12.3672011249723</v>
       </c>
       <c r="Q99">
-        <v>79.22690511502773</v>
+        <v>94.03279887502774</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8517312686542075</v>
+        <v>0.8355812958382163</v>
       </c>
       <c r="T99">
-        <v>12.46412718522862</v>
+        <v>12.2176654660662</v>
       </c>
       <c r="U99">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V99">
-        <v>0.1656326274968079</v>
+        <v>0.1827427019743602</v>
       </c>
       <c r="W99">
-        <v>0.1497113534649282</v>
+        <v>0.1329113534649282</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8281631374840396</v>
+        <v>0.9137135098718011</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1721082606982742</v>
+        <v>0.1551597615137945</v>
       </c>
       <c r="C100">
-        <v>-700.229324605913</v>
+        <v>-658.0303587220744</v>
       </c>
       <c r="D100">
-        <v>286.5566753940871</v>
+        <v>328.7556412779257</v>
       </c>
       <c r="E100">
         <v>778.4860000000001</v>
@@ -9487,37 +9487,37 @@
         <v>163.7</v>
       </c>
       <c r="M100">
-        <v>199.7041662207125</v>
+        <v>181.0060014207125</v>
       </c>
       <c r="N100">
-        <v>-36.00416622071251</v>
+        <v>-17.30600142071248</v>
       </c>
       <c r="O100">
-        <v>-7.200833244142501</v>
+        <v>-3.461200284142496</v>
       </c>
       <c r="P100">
-        <v>-28.80333297657</v>
+        <v>-13.84480113656998</v>
       </c>
       <c r="Q100">
-        <v>77.59666702343003</v>
+        <v>92.55519886343005</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.254696902981312</v>
+        <v>1.230471943757325</v>
       </c>
       <c r="T100">
-        <v>18.69619077784293</v>
+        <v>18.3264981990993</v>
       </c>
       <c r="U100">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V100">
-        <v>0.1639424986447996</v>
+        <v>0.1808779805256422</v>
       </c>
       <c r="W100">
-        <v>0.1500146149373959</v>
+        <v>0.1332146149373959</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8197124932239981</v>
+        <v>0.9043899026282112</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1734445704759418</v>
+        <v>0.156328071291462</v>
       </c>
       <c r="C101">
-        <v>-714.4587007911666</v>
+        <v>-672.6926313749658</v>
       </c>
       <c r="D101">
-        <v>283.6842992088335</v>
+        <v>325.4503686250343</v>
       </c>
       <c r="E101">
         <v>789.8430000000001</v>
@@ -9569,37 +9569,37 @@
         <v>163.7</v>
       </c>
       <c r="M101">
-        <v>201.7419638352096</v>
+        <v>182.8530014352095</v>
       </c>
       <c r="N101">
-        <v>-38.04196383520957</v>
+        <v>-19.15300143520955</v>
       </c>
       <c r="O101">
-        <v>-7.608392767041915</v>
+        <v>-3.830600287041909</v>
       </c>
       <c r="P101">
-        <v>-30.43357106816766</v>
+        <v>-15.32240114816764</v>
       </c>
       <c r="Q101">
-        <v>75.96642893183238</v>
+        <v>91.07759885183239</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.463593805962622</v>
+        <v>2.415143887514649</v>
       </c>
       <c r="T101">
-        <v>37.39238155568586</v>
+        <v>36.6529963981986</v>
       </c>
       <c r="U101">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V101">
-        <v>0.1622865138100037</v>
+        <v>0.1790509302173024</v>
       </c>
       <c r="W101">
-        <v>0.1503117499154702</v>
+        <v>0.1335117499154702</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.8114325690500184</v>
+        <v>0.895254651086512</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_power.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_power.xlsx
@@ -1133,43 +1133,43 @@
         <v>6.36964980544747</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>217.961661435359</v>
       </c>
       <c r="G2">
         <v>1.23843021103295</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.042047389855609</v>
       </c>
       <c r="I2">
         <v>0.294532006691908</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>801.2</v>
       </c>
       <c r="L2">
-        <v>1223.19707140406</v>
+        <v>1211.4122136055</v>
       </c>
       <c r="M2">
         <v>1009.5</v>
       </c>
       <c r="N2">
-        <v>1096.99707140406</v>
+        <v>1096.5692136055</v>
       </c>
       <c r="O2">
         <v>334.5</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>11.357</v>
       </c>
       <c r="Q2">
         <v>0.0775862918898548</v>
       </c>
       <c r="R2">
-        <v>0.0745982242224212</v>
+        <v>0.0746116755961104</v>
       </c>
       <c r="S2">
         <v>0.0617047822134061</v>
@@ -1191,13 +1191,13 @@
         <v>0.08421680235761821</v>
       </c>
       <c r="X2">
-        <v>0.0745982242224212</v>
+        <v>0.0748309371454306</v>
       </c>
       <c r="Y2">
         <v>0.594295714465122</v>
       </c>
       <c r="Z2">
-        <v>0.445499369788039</v>
+        <v>0.449099364695417</v>
       </c>
       <c r="AA2">
         <v>334.5</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07459822422242116</v>
+        <v>0.07461167559611039</v>
       </c>
       <c r="C2">
-        <v>1223.197071404056</v>
+        <v>1211.412213605504</v>
       </c>
       <c r="D2">
-        <v>1096.997071404056</v>
+        <v>1096.569213605504</v>
       </c>
       <c r="E2">
-        <v>-334.5</v>
+        <v>-323.143</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.357</v>
       </c>
       <c r="G2">
         <v>126.2</v>
@@ -1451,28 +1451,28 @@
         <v>163.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7510495144970659</v>
       </c>
       <c r="N2">
-        <v>163.7</v>
+        <v>162.9489504855029</v>
       </c>
       <c r="O2">
-        <v>32.74</v>
+        <v>32.58979009710059</v>
       </c>
       <c r="P2">
-        <v>130.96</v>
+        <v>130.3591603884024</v>
       </c>
       <c r="Q2">
-        <v>237.36</v>
+        <v>236.7591603884024</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07459822422242116</v>
+        <v>0.07483093714543063</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.449099364695417</v>
       </c>
       <c r="U2">
         <v>0.06613097776675758</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>217.9616614353587</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07461167559611039</v>
+        <v>0.0746251269697996</v>
       </c>
       <c r="C3">
-        <v>1211.412213605504</v>
+        <v>1199.627689428489</v>
       </c>
       <c r="D3">
-        <v>1096.569213605504</v>
+        <v>1096.141689428489</v>
       </c>
       <c r="E3">
-        <v>-323.143</v>
+        <v>-311.786</v>
       </c>
       <c r="F3">
-        <v>11.357</v>
+        <v>22.714</v>
       </c>
       <c r="G3">
         <v>126.2</v>
@@ -1533,28 +1533,28 @@
         <v>163.7</v>
       </c>
       <c r="M3">
-        <v>0.7510495144970659</v>
+        <v>1.502099028994132</v>
       </c>
       <c r="N3">
-        <v>162.9489504855029</v>
+        <v>162.1979009710059</v>
       </c>
       <c r="O3">
-        <v>32.58979009710059</v>
+        <v>32.43958019420117</v>
       </c>
       <c r="P3">
-        <v>130.3591603884024</v>
+        <v>129.7583207768047</v>
       </c>
       <c r="Q3">
-        <v>236.7591603884024</v>
+        <v>236.1583207768047</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07483093714543063</v>
+        <v>0.07506839931176681</v>
       </c>
       <c r="T3">
-        <v>0.449099364695417</v>
+        <v>0.4527728288866191</v>
       </c>
       <c r="U3">
         <v>0.06613097776675758</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>217.9616614353587</v>
+        <v>108.9808307176793</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0746251269697996</v>
+        <v>0.0746385783434888</v>
       </c>
       <c r="C4">
-        <v>1199.627689428489</v>
+        <v>1187.843498482953</v>
       </c>
       <c r="D4">
-        <v>1096.141689428489</v>
+        <v>1095.714498482953</v>
       </c>
       <c r="E4">
-        <v>-311.786</v>
+        <v>-300.429</v>
       </c>
       <c r="F4">
-        <v>22.714</v>
+        <v>34.071</v>
       </c>
       <c r="G4">
         <v>126.2</v>
@@ -1615,28 +1615,28 @@
         <v>163.7</v>
       </c>
       <c r="M4">
-        <v>1.502099028994132</v>
+        <v>2.253148543491197</v>
       </c>
       <c r="N4">
-        <v>162.1979009710059</v>
+        <v>161.4468514565088</v>
       </c>
       <c r="O4">
-        <v>32.43958019420117</v>
+        <v>32.28937029130176</v>
       </c>
       <c r="P4">
-        <v>129.7583207768047</v>
+        <v>129.157481165207</v>
       </c>
       <c r="Q4">
-        <v>236.1583207768047</v>
+        <v>235.5574811652071</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07506839931176681</v>
+        <v>0.07531075760524394</v>
       </c>
       <c r="T4">
-        <v>0.4527728288866191</v>
+        <v>0.4565220346075367</v>
       </c>
       <c r="U4">
         <v>0.06613097776675758</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>108.9808307176793</v>
+        <v>72.65388714511957</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0746385783434888</v>
+        <v>0.07465202971717803</v>
       </c>
       <c r="C5">
-        <v>1187.843498482953</v>
+        <v>1176.059640379442</v>
       </c>
       <c r="D5">
-        <v>1095.714498482953</v>
+        <v>1095.287640379442</v>
       </c>
       <c r="E5">
-        <v>-300.429</v>
+        <v>-289.072</v>
       </c>
       <c r="F5">
-        <v>34.071</v>
+        <v>45.428</v>
       </c>
       <c r="G5">
         <v>126.2</v>
@@ -1697,28 +1697,28 @@
         <v>163.7</v>
       </c>
       <c r="M5">
-        <v>2.253148543491197</v>
+        <v>3.004198057988264</v>
       </c>
       <c r="N5">
-        <v>161.4468514565088</v>
+        <v>160.6958019420117</v>
       </c>
       <c r="O5">
-        <v>32.28937029130176</v>
+        <v>32.13916038840235</v>
       </c>
       <c r="P5">
-        <v>129.157481165207</v>
+        <v>128.5566415536094</v>
       </c>
       <c r="Q5">
-        <v>235.5574811652071</v>
+        <v>234.9566415536094</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07531075760524394</v>
+        <v>0.0755581650298352</v>
       </c>
       <c r="T5">
-        <v>0.4565220346075367</v>
+        <v>0.4603493487809736</v>
       </c>
       <c r="U5">
         <v>0.06613097776675758</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>72.65388714511957</v>
+        <v>54.49041535883966</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07465202971717803</v>
+        <v>0.07466548109086725</v>
       </c>
       <c r="C6">
-        <v>1176.059640379442</v>
+        <v>1164.276114729112</v>
       </c>
       <c r="D6">
-        <v>1095.287640379442</v>
+        <v>1094.861114729112</v>
       </c>
       <c r="E6">
-        <v>-289.072</v>
+        <v>-277.715</v>
       </c>
       <c r="F6">
-        <v>45.428</v>
+        <v>56.785</v>
       </c>
       <c r="G6">
         <v>126.2</v>
@@ -1779,28 +1779,28 @@
         <v>163.7</v>
       </c>
       <c r="M6">
-        <v>3.004198057988264</v>
+        <v>3.75524757248533</v>
       </c>
       <c r="N6">
-        <v>160.6958019420117</v>
+        <v>159.9447524275147</v>
       </c>
       <c r="O6">
-        <v>32.13916038840235</v>
+        <v>31.98895048550293</v>
       </c>
       <c r="P6">
-        <v>128.5566415536094</v>
+        <v>127.9558019420117</v>
       </c>
       <c r="Q6">
-        <v>234.9566415536094</v>
+        <v>234.3558019420118</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0755581650298352</v>
+        <v>0.07581078103178626</v>
       </c>
       <c r="T6">
-        <v>0.4603493487809736</v>
+        <v>0.4642572379896405</v>
       </c>
       <c r="U6">
         <v>0.06613097776675758</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.49041535883966</v>
+        <v>43.59233228707173</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07466548109086725</v>
+        <v>0.07467893246455647</v>
       </c>
       <c r="C7">
-        <v>1164.276114729112</v>
+        <v>1152.492921143724</v>
       </c>
       <c r="D7">
-        <v>1094.861114729112</v>
+        <v>1094.434921143724</v>
       </c>
       <c r="E7">
-        <v>-277.715</v>
+        <v>-266.358</v>
       </c>
       <c r="F7">
-        <v>56.785</v>
+        <v>68.14200000000001</v>
       </c>
       <c r="G7">
         <v>126.2</v>
@@ -1861,28 +1861,28 @@
         <v>163.7</v>
       </c>
       <c r="M7">
-        <v>3.75524757248533</v>
+        <v>4.506297086982396</v>
       </c>
       <c r="N7">
-        <v>159.9447524275147</v>
+        <v>159.1937029130176</v>
       </c>
       <c r="O7">
-        <v>31.98895048550293</v>
+        <v>31.83874058260352</v>
       </c>
       <c r="P7">
-        <v>127.9558019420117</v>
+        <v>127.3549623304141</v>
       </c>
       <c r="Q7">
-        <v>234.3558019420118</v>
+        <v>233.7549623304141</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07581078103178626</v>
+        <v>0.07606877184228948</v>
       </c>
       <c r="T7">
-        <v>0.4642572379896405</v>
+        <v>0.4682482737772154</v>
       </c>
       <c r="U7">
         <v>0.06613097776675758</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.59233228707173</v>
+        <v>36.32694357255978</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07467893246455647</v>
+        <v>0.0746923838382457</v>
       </c>
       <c r="C8">
-        <v>1152.492921143724</v>
+        <v>1140.710059235643</v>
       </c>
       <c r="D8">
-        <v>1094.434921143724</v>
+        <v>1094.009059235643</v>
       </c>
       <c r="E8">
-        <v>-266.358</v>
+        <v>-255.001</v>
       </c>
       <c r="F8">
-        <v>68.142</v>
+        <v>79.499</v>
       </c>
       <c r="G8">
         <v>126.2</v>
@@ -1943,28 +1943,28 @@
         <v>163.7</v>
       </c>
       <c r="M8">
-        <v>4.506297086982395</v>
+        <v>5.257346601479461</v>
       </c>
       <c r="N8">
-        <v>159.1937029130176</v>
+        <v>158.4426533985205</v>
       </c>
       <c r="O8">
-        <v>31.83874058260352</v>
+        <v>31.6885306797041</v>
       </c>
       <c r="P8">
-        <v>127.3549623304141</v>
+        <v>126.7541227188164</v>
       </c>
       <c r="Q8">
-        <v>233.7549623304141</v>
+        <v>233.1541227188164</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07606877184228948</v>
+        <v>0.07633231084226588</v>
       </c>
       <c r="T8">
-        <v>0.4682482737772154</v>
+        <v>0.4723251382914047</v>
       </c>
       <c r="U8">
         <v>0.06613097776675758</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.32694357255979</v>
+        <v>31.13738020505124</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07469238383824568</v>
+        <v>0.07470583521193491</v>
       </c>
       <c r="C9">
-        <v>1140.710059235643</v>
+        <v>1128.927528617837</v>
       </c>
       <c r="D9">
-        <v>1094.009059235643</v>
+        <v>1093.583528617836</v>
       </c>
       <c r="E9">
-        <v>-255.001</v>
+        <v>-243.644</v>
       </c>
       <c r="F9">
-        <v>79.49900000000001</v>
+        <v>90.85600000000001</v>
       </c>
       <c r="G9">
         <v>126.2</v>
@@ -2025,28 +2025,28 @@
         <v>163.7</v>
       </c>
       <c r="M9">
-        <v>5.257346601479462</v>
+        <v>6.008396115976527</v>
       </c>
       <c r="N9">
-        <v>158.4426533985205</v>
+        <v>157.6916038840235</v>
       </c>
       <c r="O9">
-        <v>31.6885306797041</v>
+        <v>31.5383207768047</v>
       </c>
       <c r="P9">
-        <v>126.7541227188164</v>
+        <v>126.1532831072188</v>
       </c>
       <c r="Q9">
-        <v>233.1541227188164</v>
+        <v>232.5532831072188</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07633231084226588</v>
+        <v>0.07660157895093742</v>
       </c>
       <c r="T9">
-        <v>0.4723251382914047</v>
+        <v>0.4764906302950329</v>
       </c>
       <c r="U9">
         <v>0.06613097776675758</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.13738020505124</v>
+        <v>27.24520767941983</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07470583521193491</v>
+        <v>0.07471928658562413</v>
       </c>
       <c r="C10">
-        <v>1128.927528617837</v>
+        <v>1117.145328903875</v>
       </c>
       <c r="D10">
-        <v>1093.583528617836</v>
+        <v>1093.158328903875</v>
       </c>
       <c r="E10">
-        <v>-243.644</v>
+        <v>-232.287</v>
       </c>
       <c r="F10">
-        <v>90.85600000000001</v>
+        <v>102.213</v>
       </c>
       <c r="G10">
         <v>126.2</v>
@@ -2107,28 +2107,28 @@
         <v>163.7</v>
       </c>
       <c r="M10">
-        <v>6.008396115976527</v>
+        <v>6.759445630473592</v>
       </c>
       <c r="N10">
-        <v>157.6916038840235</v>
+        <v>156.9405543695264</v>
       </c>
       <c r="O10">
-        <v>31.5383207768047</v>
+        <v>31.38811087390528</v>
       </c>
       <c r="P10">
-        <v>126.1532831072188</v>
+        <v>125.5524434956211</v>
       </c>
       <c r="Q10">
-        <v>232.5532831072188</v>
+        <v>231.9524434956212</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07660157895093742</v>
+        <v>0.07687676504001932</v>
       </c>
       <c r="T10">
-        <v>0.4764906302950329</v>
+        <v>0.4807476715734661</v>
       </c>
       <c r="U10">
         <v>0.06613097776675758</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.24520767941983</v>
+        <v>24.21796238170653</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07471928658562413</v>
+        <v>0.07473273795931333</v>
       </c>
       <c r="C11">
-        <v>1117.145328903875</v>
+        <v>1105.363459707928</v>
       </c>
       <c r="D11">
-        <v>1093.158328903875</v>
+        <v>1092.733459707928</v>
       </c>
       <c r="E11">
-        <v>-232.287</v>
+        <v>-220.93</v>
       </c>
       <c r="F11">
-        <v>102.213</v>
+        <v>113.57</v>
       </c>
       <c r="G11">
         <v>126.2</v>
@@ -2189,28 +2189,28 @@
         <v>163.7</v>
       </c>
       <c r="M11">
-        <v>6.759445630473592</v>
+        <v>7.510495144970658</v>
       </c>
       <c r="N11">
-        <v>156.9405543695264</v>
+        <v>156.1895048550293</v>
       </c>
       <c r="O11">
-        <v>31.38811087390528</v>
+        <v>31.23790097100587</v>
       </c>
       <c r="P11">
-        <v>125.5524434956211</v>
+        <v>124.9516038840235</v>
       </c>
       <c r="Q11">
-        <v>231.9524434956212</v>
+        <v>231.3516038840235</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07687676504001932</v>
+        <v>0.07715806637552526</v>
       </c>
       <c r="T11">
-        <v>0.4807476715734661</v>
+        <v>0.4850993137691978</v>
       </c>
       <c r="U11">
         <v>0.06613097776675758</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.21796238170653</v>
+        <v>21.79616614353587</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07473273795931334</v>
+        <v>0.07474618933300257</v>
       </c>
       <c r="C12">
-        <v>1105.363459707928</v>
+        <v>1093.581920644766</v>
       </c>
       <c r="D12">
-        <v>1092.733459707928</v>
+        <v>1092.308920644766</v>
       </c>
       <c r="E12">
-        <v>-220.93</v>
+        <v>-209.573</v>
       </c>
       <c r="F12">
-        <v>113.57</v>
+        <v>124.927</v>
       </c>
       <c r="G12">
         <v>126.2</v>
@@ -2271,28 +2271,28 @@
         <v>163.7</v>
       </c>
       <c r="M12">
-        <v>7.510495144970659</v>
+        <v>8.261544659467726</v>
       </c>
       <c r="N12">
-        <v>156.1895048550293</v>
+        <v>155.4384553405323</v>
       </c>
       <c r="O12">
-        <v>31.23790097100587</v>
+        <v>31.08769106810646</v>
       </c>
       <c r="P12">
-        <v>124.9516038840235</v>
+        <v>124.3507642724258</v>
       </c>
       <c r="Q12">
-        <v>231.3516038840235</v>
+        <v>230.7507642724258</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07715806637552527</v>
+        <v>0.07744568908935719</v>
       </c>
       <c r="T12">
-        <v>0.485099313769198</v>
+        <v>0.4895487456771933</v>
       </c>
       <c r="U12">
         <v>0.06613097776675758</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.79616614353587</v>
+        <v>19.81469649412352</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07474618933300257</v>
+        <v>0.07475964070669179</v>
       </c>
       <c r="C13">
-        <v>1093.581920644766</v>
+        <v>1081.800711329759</v>
       </c>
       <c r="D13">
-        <v>1092.308920644766</v>
+        <v>1091.884711329759</v>
       </c>
       <c r="E13">
-        <v>-209.573</v>
+        <v>-198.216</v>
       </c>
       <c r="F13">
-        <v>124.927</v>
+        <v>136.284</v>
       </c>
       <c r="G13">
         <v>126.2</v>
@@ -2353,28 +2353,28 @@
         <v>163.7</v>
       </c>
       <c r="M13">
-        <v>8.261544659467726</v>
+        <v>9.012594173964789</v>
       </c>
       <c r="N13">
-        <v>155.4384553405323</v>
+        <v>154.6874058260352</v>
       </c>
       <c r="O13">
-        <v>31.08769106810646</v>
+        <v>30.93748116520704</v>
       </c>
       <c r="P13">
-        <v>124.3507642724258</v>
+        <v>123.7499246608282</v>
       </c>
       <c r="Q13">
-        <v>230.7507642724258</v>
+        <v>230.1499246608282</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07744568908935719</v>
+        <v>0.07773984868304892</v>
       </c>
       <c r="T13">
-        <v>0.4895487456771933</v>
+        <v>0.4940993010376432</v>
       </c>
       <c r="U13">
         <v>0.06613097776675758</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.81469649412352</v>
+        <v>18.16347178627989</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07475964070669179</v>
+        <v>0.07477309208038101</v>
       </c>
       <c r="C14">
-        <v>1081.800711329759</v>
+        <v>1070.019831378872</v>
       </c>
       <c r="D14">
-        <v>1091.884711329759</v>
+        <v>1091.460831378872</v>
       </c>
       <c r="E14">
-        <v>-198.216</v>
+        <v>-186.859</v>
       </c>
       <c r="F14">
-        <v>136.284</v>
+        <v>147.641</v>
       </c>
       <c r="G14">
         <v>126.2</v>
@@ -2435,28 +2435,28 @@
         <v>163.7</v>
       </c>
       <c r="M14">
-        <v>9.012594173964789</v>
+        <v>9.763643688461858</v>
       </c>
       <c r="N14">
-        <v>154.6874058260352</v>
+        <v>153.9363563115381</v>
       </c>
       <c r="O14">
-        <v>30.93748116520704</v>
+        <v>30.78727126230763</v>
       </c>
       <c r="P14">
-        <v>123.7499246608282</v>
+        <v>123.1490850492305</v>
       </c>
       <c r="Q14">
-        <v>230.1499246608282</v>
+        <v>229.5490850492305</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07773984868304892</v>
+        <v>0.07804077056625082</v>
       </c>
       <c r="T14">
-        <v>0.4940993010376432</v>
+        <v>0.4987544668661493</v>
       </c>
       <c r="U14">
         <v>0.06613097776675758</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.16347178627989</v>
+        <v>16.76628164887374</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07477309208038101</v>
+        <v>0.07478654345407022</v>
       </c>
       <c r="C15">
-        <v>1070.019831378872</v>
+        <v>1058.239280408667</v>
       </c>
       <c r="D15">
-        <v>1091.460831378872</v>
+        <v>1091.037280408667</v>
       </c>
       <c r="E15">
-        <v>-186.859</v>
+        <v>-175.502</v>
       </c>
       <c r="F15">
-        <v>147.641</v>
+        <v>158.998</v>
       </c>
       <c r="G15">
         <v>126.2</v>
@@ -2517,28 +2517,28 @@
         <v>163.7</v>
       </c>
       <c r="M15">
-        <v>9.763643688461858</v>
+        <v>10.51469320295892</v>
       </c>
       <c r="N15">
-        <v>153.9363563115381</v>
+        <v>153.1853067970411</v>
       </c>
       <c r="O15">
-        <v>30.78727126230763</v>
+        <v>30.63706135940821</v>
       </c>
       <c r="P15">
-        <v>123.1490850492305</v>
+        <v>122.5482454376328</v>
       </c>
       <c r="Q15">
-        <v>229.5490850492305</v>
+        <v>228.9482454376329</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07804077056625082</v>
+        <v>0.07834869063278299</v>
       </c>
       <c r="T15">
-        <v>0.4987544668661493</v>
+        <v>0.5035178923650858</v>
       </c>
       <c r="U15">
         <v>0.06613097776675758</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.76628164887374</v>
+        <v>15.56869010252562</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07478654345407022</v>
+        <v>0.07479999482775944</v>
       </c>
       <c r="C16">
-        <v>1058.239280408667</v>
+        <v>1046.459058036302</v>
       </c>
       <c r="D16">
-        <v>1091.037280408667</v>
+        <v>1090.614058036302</v>
       </c>
       <c r="E16">
-        <v>-175.502</v>
+        <v>-164.145</v>
       </c>
       <c r="F16">
-        <v>158.998</v>
+        <v>170.355</v>
       </c>
       <c r="G16">
         <v>126.2</v>
@@ -2599,28 +2599,28 @@
         <v>163.7</v>
       </c>
       <c r="M16">
-        <v>10.51469320295892</v>
+        <v>11.26574271745599</v>
       </c>
       <c r="N16">
-        <v>153.1853067970411</v>
+        <v>152.434257282544</v>
       </c>
       <c r="O16">
-        <v>30.63706135940821</v>
+        <v>30.4868514565088</v>
       </c>
       <c r="P16">
-        <v>122.5482454376328</v>
+        <v>121.9474058260352</v>
       </c>
       <c r="Q16">
-        <v>228.9482454376329</v>
+        <v>228.3474058260352</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07834869063278299</v>
+        <v>0.07866385587735121</v>
       </c>
       <c r="T16">
-        <v>0.5035178923650858</v>
+        <v>0.5083933984639973</v>
       </c>
       <c r="U16">
         <v>0.06613097776675758</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.56869010252562</v>
+        <v>14.53077742902391</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07479999482775944</v>
+        <v>0.07481344620144864</v>
       </c>
       <c r="C17">
-        <v>1046.459058036302</v>
+        <v>1034.679163879527</v>
       </c>
       <c r="D17">
-        <v>1090.614058036302</v>
+        <v>1090.191163879527</v>
       </c>
       <c r="E17">
-        <v>-164.145</v>
+        <v>-152.788</v>
       </c>
       <c r="F17">
-        <v>170.355</v>
+        <v>181.712</v>
       </c>
       <c r="G17">
         <v>126.2</v>
@@ -2681,28 +2681,28 @@
         <v>163.7</v>
       </c>
       <c r="M17">
-        <v>11.26574271745599</v>
+        <v>12.01679223195305</v>
       </c>
       <c r="N17">
-        <v>152.434257282544</v>
+        <v>151.6832077680469</v>
       </c>
       <c r="O17">
-        <v>30.4868514565088</v>
+        <v>30.33664155360939</v>
       </c>
       <c r="P17">
-        <v>121.9474058260352</v>
+        <v>121.3465662144376</v>
       </c>
       <c r="Q17">
-        <v>228.3474058260352</v>
+        <v>227.7465662144376</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07866385587735121</v>
+        <v>0.0789865250563139</v>
       </c>
       <c r="T17">
-        <v>0.5083933984639973</v>
+        <v>0.5133849880414543</v>
       </c>
       <c r="U17">
         <v>0.06613097776675758</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.53077742902391</v>
+        <v>13.62260383970992</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07481344620144864</v>
+        <v>0.07482689757513787</v>
       </c>
       <c r="C18">
-        <v>1034.679163879527</v>
+        <v>1022.899597556685</v>
       </c>
       <c r="D18">
-        <v>1090.191163879527</v>
+        <v>1089.768597556684</v>
       </c>
       <c r="E18">
-        <v>-152.788</v>
+        <v>-141.431</v>
       </c>
       <c r="F18">
-        <v>181.712</v>
+        <v>193.069</v>
       </c>
       <c r="G18">
         <v>126.2</v>
@@ -2763,28 +2763,28 @@
         <v>163.7</v>
       </c>
       <c r="M18">
-        <v>12.01679223195305</v>
+        <v>12.76784174645012</v>
       </c>
       <c r="N18">
-        <v>151.6832077680469</v>
+        <v>150.9321582535499</v>
       </c>
       <c r="O18">
-        <v>30.33664155360939</v>
+        <v>30.18643165070997</v>
       </c>
       <c r="P18">
-        <v>121.3465662144376</v>
+        <v>120.7457266028399</v>
       </c>
       <c r="Q18">
-        <v>227.7465662144376</v>
+        <v>227.1457266028399</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0789865250563139</v>
+        <v>0.07931696939621546</v>
       </c>
       <c r="T18">
-        <v>0.5133849880414543</v>
+        <v>0.518496856885838</v>
       </c>
       <c r="U18">
         <v>0.06613097776675758</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.62260383970992</v>
+        <v>12.82127420207992</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07482689757513787</v>
+        <v>0.0750563489488271</v>
       </c>
       <c r="C19">
-        <v>1022.899597556685</v>
+        <v>1004.384649481731</v>
       </c>
       <c r="D19">
-        <v>1089.768597556684</v>
+        <v>1082.610649481731</v>
       </c>
       <c r="E19">
-        <v>-141.431</v>
+        <v>-130.074</v>
       </c>
       <c r="F19">
-        <v>193.069</v>
+        <v>204.426</v>
       </c>
       <c r="G19">
         <v>126.2</v>
@@ -2845,45 +2845,45 @@
         <v>163.7</v>
       </c>
       <c r="M19">
-        <v>12.76784174645012</v>
+        <v>13.82553026094719</v>
       </c>
       <c r="N19">
-        <v>150.9321582535499</v>
+        <v>149.8744697390528</v>
       </c>
       <c r="O19">
-        <v>30.18643165070997</v>
+        <v>29.97489394781056</v>
       </c>
       <c r="P19">
-        <v>120.7457266028399</v>
+        <v>119.8995757912423</v>
       </c>
       <c r="Q19">
-        <v>227.1457266028399</v>
+        <v>226.2995757912423</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07931696939621546</v>
+        <v>0.07965547335416343</v>
       </c>
       <c r="T19">
-        <v>0.518496856885838</v>
+        <v>0.5237334054581336</v>
       </c>
       <c r="U19">
-        <v>0.06613097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05290478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.82127420207992</v>
+        <v>11.8404138510623</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0750563489488271</v>
+        <v>0.07508180032251632</v>
       </c>
       <c r="C20">
-        <v>1004.384649481731</v>
+        <v>992.2394596762432</v>
       </c>
       <c r="D20">
-        <v>1082.610649481731</v>
+        <v>1081.822459676243</v>
       </c>
       <c r="E20">
-        <v>-130.074</v>
+        <v>-118.717</v>
       </c>
       <c r="F20">
-        <v>204.426</v>
+        <v>215.783</v>
       </c>
       <c r="G20">
         <v>126.2</v>
@@ -2927,28 +2927,28 @@
         <v>163.7</v>
       </c>
       <c r="M20">
-        <v>13.82553026094718</v>
+        <v>14.59361527544425</v>
       </c>
       <c r="N20">
-        <v>149.8744697390528</v>
+        <v>149.1063847245557</v>
       </c>
       <c r="O20">
-        <v>29.97489394781056</v>
+        <v>29.82127694491115</v>
       </c>
       <c r="P20">
-        <v>119.8995757912423</v>
+        <v>119.2851077796446</v>
       </c>
       <c r="Q20">
-        <v>226.2995757912423</v>
+        <v>225.6851077796446</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07965547335416341</v>
+        <v>0.08000233543452984</v>
       </c>
       <c r="T20">
-        <v>0.5237334054581335</v>
+        <v>0.5290992515260413</v>
       </c>
       <c r="U20">
         <v>0.06763097776675758</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.8404138510623</v>
+        <v>11.2172341746906</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07508180032251632</v>
+        <v>0.07510725169620554</v>
       </c>
       <c r="C21">
-        <v>992.2394596762432</v>
+        <v>980.0954167118763</v>
       </c>
       <c r="D21">
-        <v>1081.822459676243</v>
+        <v>1081.035416711876</v>
       </c>
       <c r="E21">
-        <v>-118.717</v>
+        <v>-107.36</v>
       </c>
       <c r="F21">
-        <v>215.783</v>
+        <v>227.14</v>
       </c>
       <c r="G21">
         <v>126.2</v>
@@ -3009,28 +3009,28 @@
         <v>163.7</v>
       </c>
       <c r="M21">
-        <v>14.59361527544425</v>
+        <v>15.36170028994132</v>
       </c>
       <c r="N21">
-        <v>149.1063847245557</v>
+        <v>148.3382997100587</v>
       </c>
       <c r="O21">
-        <v>29.82127694491115</v>
+        <v>29.66765994201173</v>
       </c>
       <c r="P21">
-        <v>119.2851077796446</v>
+        <v>118.6706397680469</v>
       </c>
       <c r="Q21">
-        <v>225.6851077796446</v>
+        <v>225.070639768047</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08000233543452984</v>
+        <v>0.0803578690669054</v>
       </c>
       <c r="T21">
-        <v>0.5290992515260413</v>
+        <v>0.5345992437456466</v>
       </c>
       <c r="U21">
         <v>0.06763097776675758</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.2172341746906</v>
+        <v>10.65637246595607</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07510725169620554</v>
+        <v>0.07513270306989475</v>
       </c>
       <c r="C22">
-        <v>980.0954167118763</v>
+        <v>967.9525180874143</v>
       </c>
       <c r="D22">
-        <v>1081.035416711876</v>
+        <v>1080.249518087414</v>
       </c>
       <c r="E22">
-        <v>-107.36</v>
+        <v>-96.00299999999996</v>
       </c>
       <c r="F22">
-        <v>227.14</v>
+        <v>238.497</v>
       </c>
       <c r="G22">
         <v>126.2</v>
@@ -3091,28 +3091,28 @@
         <v>163.7</v>
       </c>
       <c r="M22">
-        <v>15.36170028994132</v>
+        <v>16.12978530443839</v>
       </c>
       <c r="N22">
-        <v>148.3382997100587</v>
+        <v>147.5702146955616</v>
       </c>
       <c r="O22">
-        <v>29.66765994201173</v>
+        <v>29.51404293911233</v>
       </c>
       <c r="P22">
-        <v>118.6706397680469</v>
+        <v>118.0561717564493</v>
       </c>
       <c r="Q22">
-        <v>225.070639768047</v>
+        <v>224.4561717564493</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0803578690669054</v>
+        <v>0.08072240355073351</v>
       </c>
       <c r="T22">
-        <v>0.5345992437456466</v>
+        <v>0.5402384762746092</v>
       </c>
       <c r="U22">
         <v>0.06763097776675758</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.65637246595607</v>
+        <v>10.1489261580534</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07513270306989475</v>
+        <v>0.07545735444358397</v>
       </c>
       <c r="C23">
-        <v>967.9525180874143</v>
+        <v>946.6701199661816</v>
       </c>
       <c r="D23">
-        <v>1080.249518087414</v>
+        <v>1070.324119966182</v>
       </c>
       <c r="E23">
-        <v>-96.00299999999999</v>
+        <v>-84.64599999999999</v>
       </c>
       <c r="F23">
-        <v>238.497</v>
+        <v>249.854</v>
       </c>
       <c r="G23">
         <v>126.2</v>
@@ -3173,45 +3173,45 @@
         <v>163.7</v>
       </c>
       <c r="M23">
-        <v>16.12978530443839</v>
+        <v>17.32262211893545</v>
       </c>
       <c r="N23">
-        <v>147.5702146955616</v>
+        <v>146.3773778810645</v>
       </c>
       <c r="O23">
-        <v>29.51404293911233</v>
+        <v>29.27547557621291</v>
       </c>
       <c r="P23">
-        <v>118.0561717564493</v>
+        <v>117.1019023048516</v>
       </c>
       <c r="Q23">
-        <v>224.4561717564493</v>
+        <v>223.5019023048517</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08072240355073351</v>
+        <v>0.08109628507260849</v>
       </c>
       <c r="T23">
-        <v>0.5402384762746092</v>
+        <v>0.5460223045094426</v>
       </c>
       <c r="U23">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.05410478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.1489261580534</v>
+        <v>9.450070484482755</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07545735444358397</v>
+        <v>0.07549640581727318</v>
       </c>
       <c r="C24">
-        <v>946.6701199661816</v>
+        <v>934.1314981023008</v>
       </c>
       <c r="D24">
-        <v>1070.324119966182</v>
+        <v>1069.142498102301</v>
       </c>
       <c r="E24">
-        <v>-84.64599999999999</v>
+        <v>-73.28899999999999</v>
       </c>
       <c r="F24">
-        <v>249.854</v>
+        <v>261.211</v>
       </c>
       <c r="G24">
         <v>126.2</v>
@@ -3255,28 +3255,28 @@
         <v>163.7</v>
       </c>
       <c r="M24">
-        <v>17.32262211893545</v>
+        <v>18.11001403343251</v>
       </c>
       <c r="N24">
-        <v>146.3773778810645</v>
+        <v>145.5899859665675</v>
       </c>
       <c r="O24">
-        <v>29.27547557621291</v>
+        <v>29.1179971933135</v>
       </c>
       <c r="P24">
-        <v>117.1019023048516</v>
+        <v>116.471988773254</v>
       </c>
       <c r="Q24">
-        <v>223.5019023048517</v>
+        <v>222.871988773254</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08109628507260849</v>
+        <v>0.08147987780284388</v>
       </c>
       <c r="T24">
-        <v>0.5460223045094426</v>
+        <v>0.5519563620490768</v>
       </c>
       <c r="U24">
         <v>0.06933097776675758</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.450070484482755</v>
+        <v>9.039197854722635</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07549640581727318</v>
+        <v>0.0755354571909624</v>
       </c>
       <c r="C25">
-        <v>934.1314981023008</v>
+        <v>921.5954823471411</v>
       </c>
       <c r="D25">
-        <v>1069.142498102301</v>
+        <v>1067.963482347141</v>
       </c>
       <c r="E25">
-        <v>-73.28899999999999</v>
+        <v>-61.93199999999996</v>
       </c>
       <c r="F25">
-        <v>261.211</v>
+        <v>272.568</v>
       </c>
       <c r="G25">
         <v>126.2</v>
@@ -3337,28 +3337,28 @@
         <v>163.7</v>
       </c>
       <c r="M25">
-        <v>18.11001403343251</v>
+        <v>18.89740594792958</v>
       </c>
       <c r="N25">
-        <v>145.5899859665675</v>
+        <v>144.8025940520704</v>
       </c>
       <c r="O25">
-        <v>29.1179971933135</v>
+        <v>28.96051881041409</v>
       </c>
       <c r="P25">
-        <v>116.471988773254</v>
+        <v>115.8420752416563</v>
       </c>
       <c r="Q25">
-        <v>222.871988773254</v>
+        <v>222.2420752416564</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08147987780284388</v>
+        <v>0.08187356507861177</v>
       </c>
       <c r="T25">
-        <v>0.5519563620490768</v>
+        <v>0.5580465789976488</v>
       </c>
       <c r="U25">
         <v>0.06933097776675758</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.039197854722635</v>
+        <v>8.662564610775858</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0755354571909624</v>
+        <v>0.07557450856465162</v>
       </c>
       <c r="C26">
-        <v>921.5954823471411</v>
+        <v>909.0620640884028</v>
       </c>
       <c r="D26">
-        <v>1067.963482347141</v>
+        <v>1066.787064088403</v>
       </c>
       <c r="E26">
-        <v>-61.93200000000002</v>
+        <v>-50.57499999999999</v>
       </c>
       <c r="F26">
-        <v>272.568</v>
+        <v>283.925</v>
       </c>
       <c r="G26">
         <v>126.2</v>
@@ -3419,28 +3419,28 @@
         <v>163.7</v>
       </c>
       <c r="M26">
-        <v>18.89740594792958</v>
+        <v>19.68479786242665</v>
       </c>
       <c r="N26">
-        <v>144.8025940520704</v>
+        <v>144.0152021375733</v>
       </c>
       <c r="O26">
-        <v>28.96051881041409</v>
+        <v>28.80304042751467</v>
       </c>
       <c r="P26">
-        <v>115.8420752416563</v>
+        <v>115.2121617100587</v>
       </c>
       <c r="Q26">
-        <v>222.2420752416564</v>
+        <v>221.6121617100587</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08187356507861177</v>
+        <v>0.08227775068173347</v>
       </c>
       <c r="T26">
-        <v>0.5580465789976486</v>
+        <v>0.5642992017315159</v>
       </c>
       <c r="U26">
         <v>0.06933097776675758</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.66256461077586</v>
+        <v>8.316062026344824</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07557450856465162</v>
+        <v>0.07561355993834085</v>
       </c>
       <c r="C27">
-        <v>909.0620640884028</v>
+        <v>896.5312347516914</v>
       </c>
       <c r="D27">
-        <v>1066.787064088403</v>
+        <v>1065.613234751691</v>
       </c>
       <c r="E27">
-        <v>-50.57499999999999</v>
+        <v>-39.21799999999996</v>
       </c>
       <c r="F27">
-        <v>283.925</v>
+        <v>295.282</v>
       </c>
       <c r="G27">
         <v>126.2</v>
@@ -3501,28 +3501,28 @@
         <v>163.7</v>
       </c>
       <c r="M27">
-        <v>19.68479786242665</v>
+        <v>20.47218977692371</v>
       </c>
       <c r="N27">
-        <v>144.0152021375733</v>
+        <v>143.2278102230763</v>
       </c>
       <c r="O27">
-        <v>28.80304042751467</v>
+        <v>28.64556204461526</v>
       </c>
       <c r="P27">
-        <v>115.2121617100587</v>
+        <v>114.582248178461</v>
       </c>
       <c r="Q27">
-        <v>221.6121617100587</v>
+        <v>220.9822481784611</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08227775068173347</v>
+        <v>0.08269286022007469</v>
       </c>
       <c r="T27">
-        <v>0.5642992017315159</v>
+        <v>0.5707208142690012</v>
       </c>
       <c r="U27">
         <v>0.06933097776675758</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.316062026344824</v>
+        <v>7.996213486870023</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07561355993834085</v>
+        <v>0.07565261131203006</v>
       </c>
       <c r="C28">
-        <v>896.5312347516914</v>
+        <v>884.0029858003112</v>
       </c>
       <c r="D28">
-        <v>1065.613234751691</v>
+        <v>1064.441985800311</v>
       </c>
       <c r="E28">
-        <v>-39.21799999999996</v>
+        <v>-27.86099999999999</v>
       </c>
       <c r="F28">
-        <v>295.282</v>
+        <v>306.639</v>
       </c>
       <c r="G28">
         <v>126.2</v>
@@ -3583,28 +3583,28 @@
         <v>163.7</v>
       </c>
       <c r="M28">
-        <v>20.47218977692371</v>
+        <v>21.25958169142078</v>
       </c>
       <c r="N28">
-        <v>143.2278102230763</v>
+        <v>142.4404183085792</v>
       </c>
       <c r="O28">
-        <v>28.64556204461526</v>
+        <v>28.48808366171584</v>
       </c>
       <c r="P28">
-        <v>114.582248178461</v>
+        <v>113.9523346468634</v>
       </c>
       <c r="Q28">
-        <v>220.9822481784611</v>
+        <v>220.3523346468634</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08269286022007469</v>
+        <v>0.08311934262248002</v>
       </c>
       <c r="T28">
-        <v>0.5707208142690012</v>
+        <v>0.5773183613965546</v>
       </c>
       <c r="U28">
         <v>0.06933097776675758</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.996213486870023</v>
+        <v>7.700057431800762</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07565261131203006</v>
+        <v>0.07587086268571927</v>
       </c>
       <c r="C29">
-        <v>884.0029858003112</v>
+        <v>866.1471939266344</v>
       </c>
       <c r="D29">
-        <v>1064.441985800311</v>
+        <v>1057.943193926634</v>
       </c>
       <c r="E29">
-        <v>-27.86099999999999</v>
+        <v>-16.50399999999996</v>
       </c>
       <c r="F29">
-        <v>306.639</v>
+        <v>317.996</v>
       </c>
       <c r="G29">
         <v>126.2</v>
@@ -3665,45 +3665,45 @@
         <v>163.7</v>
       </c>
       <c r="M29">
-        <v>21.25958169142078</v>
+        <v>22.30137040591785</v>
       </c>
       <c r="N29">
-        <v>142.4404183085792</v>
+        <v>141.3986295940821</v>
       </c>
       <c r="O29">
-        <v>28.48808366171584</v>
+        <v>28.27972591881643</v>
       </c>
       <c r="P29">
-        <v>113.9523346468634</v>
+        <v>113.1189036752657</v>
       </c>
       <c r="Q29">
-        <v>220.3523346468634</v>
+        <v>219.5189036752657</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08311934262248002</v>
+        <v>0.08355767175828552</v>
       </c>
       <c r="T29">
-        <v>0.5773183613965546</v>
+        <v>0.5840991737220954</v>
       </c>
       <c r="U29">
-        <v>0.06933097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.05546478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.700057431800762</v>
+        <v>7.340356086662768</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07587086268571927</v>
+        <v>0.0759163140594085</v>
       </c>
       <c r="C30">
-        <v>866.1471939266344</v>
+        <v>853.4467758920086</v>
       </c>
       <c r="D30">
-        <v>1057.943193926634</v>
+        <v>1056.599775892009</v>
       </c>
       <c r="E30">
-        <v>-16.50399999999996</v>
+        <v>-5.146999999999935</v>
       </c>
       <c r="F30">
-        <v>317.996</v>
+        <v>329.3530000000001</v>
       </c>
       <c r="G30">
         <v>126.2</v>
@@ -3747,28 +3747,28 @@
         <v>163.7</v>
       </c>
       <c r="M30">
-        <v>22.30137040591785</v>
+        <v>23.09784792041491</v>
       </c>
       <c r="N30">
-        <v>141.3986295940821</v>
+        <v>140.6021520795851</v>
       </c>
       <c r="O30">
-        <v>28.27972591881643</v>
+        <v>28.12043041591701</v>
       </c>
       <c r="P30">
-        <v>113.1189036752657</v>
+        <v>112.4817216636681</v>
       </c>
       <c r="Q30">
-        <v>219.5189036752657</v>
+        <v>218.8817216636681</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08355767175828552</v>
+        <v>0.08400834819369118</v>
       </c>
       <c r="T30">
-        <v>0.5840991737220954</v>
+        <v>0.5910709948455389</v>
       </c>
       <c r="U30">
         <v>0.07013097776675759</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.340356086662768</v>
+        <v>7.087240359536465</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07591631405940849</v>
+        <v>0.07596176543309771</v>
       </c>
       <c r="C31">
-        <v>853.4467758920089</v>
+        <v>840.7497653808907</v>
       </c>
       <c r="D31">
-        <v>1056.599775892009</v>
+        <v>1055.259765380891</v>
       </c>
       <c r="E31">
-        <v>-5.146999999999991</v>
+        <v>6.20999999999998</v>
       </c>
       <c r="F31">
-        <v>329.353</v>
+        <v>340.71</v>
       </c>
       <c r="G31">
         <v>126.2</v>
@@ -3829,28 +3829,28 @@
         <v>163.7</v>
       </c>
       <c r="M31">
-        <v>23.09784792041491</v>
+        <v>23.89432543491198</v>
       </c>
       <c r="N31">
-        <v>140.6021520795851</v>
+        <v>139.805674565088</v>
       </c>
       <c r="O31">
-        <v>28.12043041591701</v>
+        <v>27.9611349130176</v>
       </c>
       <c r="P31">
-        <v>112.4817216636681</v>
+        <v>111.8445396520704</v>
       </c>
       <c r="Q31">
-        <v>218.8817216636681</v>
+        <v>218.2445396520704</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08400834819369118</v>
+        <v>0.08447190109867986</v>
       </c>
       <c r="T31">
-        <v>0.5910709948455389</v>
+        <v>0.5982420108582237</v>
       </c>
       <c r="U31">
         <v>0.07013097776675759</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.087240359536466</v>
+        <v>6.850999014218583</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07596176543309771</v>
+        <v>0.07600721680678693</v>
       </c>
       <c r="C32">
-        <v>840.7497653808907</v>
+        <v>828.056149445141</v>
       </c>
       <c r="D32">
-        <v>1055.259765380891</v>
+        <v>1053.923149445141</v>
       </c>
       <c r="E32">
-        <v>6.20999999999998</v>
+        <v>17.56700000000001</v>
       </c>
       <c r="F32">
-        <v>340.71</v>
+        <v>352.067</v>
       </c>
       <c r="G32">
         <v>126.2</v>
@@ -3911,28 +3911,28 @@
         <v>163.7</v>
       </c>
       <c r="M32">
-        <v>23.89432543491198</v>
+        <v>24.69080294940904</v>
       </c>
       <c r="N32">
-        <v>139.805674565088</v>
+        <v>139.009197050591</v>
       </c>
       <c r="O32">
-        <v>27.9611349130176</v>
+        <v>27.80183941011819</v>
       </c>
       <c r="P32">
-        <v>111.8445396520704</v>
+        <v>111.2073576404728</v>
       </c>
       <c r="Q32">
-        <v>218.2445396520704</v>
+        <v>217.6073576404728</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08447190109867986</v>
+        <v>0.08494889031975514</v>
       </c>
       <c r="T32">
-        <v>0.5982420108582237</v>
+        <v>0.6056208824075079</v>
       </c>
       <c r="U32">
         <v>0.07013097776675759</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.850999014218583</v>
+        <v>6.629999046017985</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07600721680678693</v>
+        <v>0.07605266818047614</v>
       </c>
       <c r="C33">
-        <v>828.056149445141</v>
+        <v>815.3659152021387</v>
       </c>
       <c r="D33">
-        <v>1053.923149445141</v>
+        <v>1052.589915202139</v>
       </c>
       <c r="E33">
-        <v>17.56700000000001</v>
+        <v>28.92400000000004</v>
       </c>
       <c r="F33">
-        <v>352.067</v>
+        <v>363.424</v>
       </c>
       <c r="G33">
         <v>126.2</v>
@@ -3993,28 +3993,28 @@
         <v>163.7</v>
       </c>
       <c r="M33">
-        <v>24.69080294940904</v>
+        <v>25.48728046390611</v>
       </c>
       <c r="N33">
-        <v>139.009197050591</v>
+        <v>138.2127195360939</v>
       </c>
       <c r="O33">
-        <v>27.80183941011819</v>
+        <v>27.64254390721878</v>
       </c>
       <c r="P33">
-        <v>111.2073576404728</v>
+        <v>110.5701756288751</v>
       </c>
       <c r="Q33">
-        <v>217.6073576404728</v>
+        <v>216.9701756288752</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08494889031975514</v>
+        <v>0.08543990863556795</v>
       </c>
       <c r="T33">
-        <v>0.6056208824075079</v>
+        <v>0.6132167795905947</v>
       </c>
       <c r="U33">
         <v>0.07013097776675759</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.629999046017985</v>
+        <v>6.422811575829923</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07605266818047614</v>
+        <v>0.07609811955416536</v>
       </c>
       <c r="C34">
-        <v>815.3659152021387</v>
+        <v>802.6790498343669</v>
       </c>
       <c r="D34">
-        <v>1052.589915202139</v>
+        <v>1051.260049834367</v>
       </c>
       <c r="E34">
-        <v>28.92400000000004</v>
+        <v>40.28100000000001</v>
       </c>
       <c r="F34">
-        <v>363.424</v>
+        <v>374.781</v>
       </c>
       <c r="G34">
         <v>126.2</v>
@@ -4075,28 +4075,28 @@
         <v>163.7</v>
       </c>
       <c r="M34">
-        <v>25.48728046390611</v>
+        <v>26.28375797840317</v>
       </c>
       <c r="N34">
-        <v>138.2127195360939</v>
+        <v>137.4162420215968</v>
       </c>
       <c r="O34">
-        <v>27.64254390721878</v>
+        <v>27.48324840431937</v>
       </c>
       <c r="P34">
-        <v>110.5701756288751</v>
+        <v>109.9329936172774</v>
       </c>
       <c r="Q34">
-        <v>216.9701756288752</v>
+        <v>216.3329936172775</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08543990863556795</v>
+        <v>0.08594558421453935</v>
       </c>
       <c r="T34">
-        <v>0.6132167795905947</v>
+        <v>0.6210394199731767</v>
       </c>
       <c r="U34">
         <v>0.07013097776675759</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.422811575829923</v>
+        <v>6.228180922016895</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07609811955416536</v>
+        <v>0.07641557092785459</v>
       </c>
       <c r="C35">
-        <v>802.6790498343669</v>
+        <v>782.1265930322562</v>
       </c>
       <c r="D35">
-        <v>1051.260049834367</v>
+        <v>1042.064593032256</v>
       </c>
       <c r="E35">
-        <v>40.28100000000001</v>
+        <v>51.63800000000003</v>
       </c>
       <c r="F35">
-        <v>374.781</v>
+        <v>386.138</v>
       </c>
       <c r="G35">
         <v>126.2</v>
@@ -4157,45 +4157,45 @@
         <v>163.7</v>
       </c>
       <c r="M35">
-        <v>26.28375797840317</v>
+        <v>27.46637349290024</v>
       </c>
       <c r="N35">
-        <v>137.4162420215968</v>
+        <v>136.2336265070998</v>
       </c>
       <c r="O35">
-        <v>27.48324840431937</v>
+        <v>27.24672530141995</v>
       </c>
       <c r="P35">
-        <v>109.9329936172774</v>
+        <v>108.9869012056798</v>
       </c>
       <c r="Q35">
-        <v>216.3329936172775</v>
+        <v>215.3869012056798</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08594558421453935</v>
+        <v>0.08646658329590381</v>
       </c>
       <c r="T35">
-        <v>0.6210394199731767</v>
+        <v>0.6290991100643216</v>
       </c>
       <c r="U35">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05610478221340607</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.228180922016895</v>
+        <v>5.960015072332525</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07641557092785459</v>
+        <v>0.0764690223015438</v>
       </c>
       <c r="C36">
-        <v>782.1265930322562</v>
+        <v>769.2370937205535</v>
       </c>
       <c r="D36">
-        <v>1042.064593032256</v>
+        <v>1040.532093720554</v>
       </c>
       <c r="E36">
-        <v>51.63800000000003</v>
+        <v>62.99500000000006</v>
       </c>
       <c r="F36">
-        <v>386.138</v>
+        <v>397.4950000000001</v>
       </c>
       <c r="G36">
         <v>126.2</v>
@@ -4239,28 +4239,28 @@
         <v>163.7</v>
       </c>
       <c r="M36">
-        <v>27.46637349290024</v>
+        <v>28.27420800739731</v>
       </c>
       <c r="N36">
-        <v>136.2336265070998</v>
+        <v>135.4257919926027</v>
       </c>
       <c r="O36">
-        <v>27.24672530141995</v>
+        <v>27.08515839852054</v>
       </c>
       <c r="P36">
-        <v>108.9869012056798</v>
+        <v>108.3406335940821</v>
       </c>
       <c r="Q36">
-        <v>215.3869012056798</v>
+        <v>214.7406335940822</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08646658329590381</v>
+        <v>0.08700361311823336</v>
       </c>
       <c r="T36">
-        <v>0.6290991100643216</v>
+        <v>0.6374067906198095</v>
       </c>
       <c r="U36">
         <v>0.07113097776675759</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.960015072332525</v>
+        <v>5.789728927408738</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0764690223015438</v>
+        <v>0.07652247367523302</v>
       </c>
       <c r="C37">
-        <v>769.2370937205535</v>
+        <v>756.3520952917252</v>
       </c>
       <c r="D37">
-        <v>1040.532093720554</v>
+        <v>1039.004095291725</v>
       </c>
       <c r="E37">
-        <v>62.99500000000006</v>
+        <v>74.35200000000009</v>
       </c>
       <c r="F37">
-        <v>397.4950000000001</v>
+        <v>408.8520000000001</v>
       </c>
       <c r="G37">
         <v>126.2</v>
@@ -4321,28 +4321,28 @@
         <v>163.7</v>
       </c>
       <c r="M37">
-        <v>28.27420800739731</v>
+        <v>29.08204252189438</v>
       </c>
       <c r="N37">
-        <v>135.4257919926027</v>
+        <v>134.6179574781056</v>
       </c>
       <c r="O37">
-        <v>27.08515839852054</v>
+        <v>26.92359149562112</v>
       </c>
       <c r="P37">
-        <v>108.3406335940821</v>
+        <v>107.6943659824845</v>
       </c>
       <c r="Q37">
-        <v>214.7406335940822</v>
+        <v>214.0943659824845</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08700361311823336</v>
+        <v>0.08755742512251069</v>
       </c>
       <c r="T37">
-        <v>0.6374067906198095</v>
+        <v>0.6459740861926565</v>
       </c>
       <c r="U37">
         <v>0.07113097776675759</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.789728927408738</v>
+        <v>5.628903123869606</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07652247367523303</v>
+        <v>0.07657592504892224</v>
       </c>
       <c r="C38">
-        <v>756.3520952917248</v>
+        <v>743.4715779465041</v>
       </c>
       <c r="D38">
-        <v>1039.004095291725</v>
+        <v>1037.480577946504</v>
       </c>
       <c r="E38">
-        <v>74.35199999999998</v>
+        <v>85.709</v>
       </c>
       <c r="F38">
-        <v>408.852</v>
+        <v>420.209</v>
       </c>
       <c r="G38">
         <v>126.2</v>
@@ -4403,28 +4403,28 @@
         <v>163.7</v>
       </c>
       <c r="M38">
-        <v>29.08204252189437</v>
+        <v>29.88987703639144</v>
       </c>
       <c r="N38">
-        <v>134.6179574781056</v>
+        <v>133.8101229636085</v>
       </c>
       <c r="O38">
-        <v>26.92359149562112</v>
+        <v>26.76202459272171</v>
       </c>
       <c r="P38">
-        <v>107.6943659824845</v>
+        <v>107.0480983708868</v>
       </c>
       <c r="Q38">
-        <v>214.0943659824845</v>
+        <v>213.4480983708869</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08755742512251069</v>
+        <v>0.08812881846025714</v>
       </c>
       <c r="T38">
-        <v>0.6459740861926564</v>
+        <v>0.6548133594027366</v>
       </c>
       <c r="U38">
         <v>0.07113097776675759</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.628903123869607</v>
+        <v>5.476770607008266</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07657592504892224</v>
+        <v>0.07662937642261144</v>
       </c>
       <c r="C39">
-        <v>743.4715779465041</v>
+        <v>730.595522001583</v>
       </c>
       <c r="D39">
-        <v>1037.480577946504</v>
+        <v>1035.961522001583</v>
       </c>
       <c r="E39">
-        <v>85.709</v>
+        <v>97.06600000000003</v>
       </c>
       <c r="F39">
-        <v>420.209</v>
+        <v>431.566</v>
       </c>
       <c r="G39">
         <v>126.2</v>
@@ -4485,28 +4485,28 @@
         <v>163.7</v>
       </c>
       <c r="M39">
-        <v>29.88987703639144</v>
+        <v>30.69771155088851</v>
       </c>
       <c r="N39">
-        <v>133.8101229636085</v>
+        <v>133.0022884491115</v>
       </c>
       <c r="O39">
-        <v>26.76202459272171</v>
+        <v>26.6004576898223</v>
       </c>
       <c r="P39">
-        <v>107.0480983708868</v>
+        <v>106.4018307592892</v>
       </c>
       <c r="Q39">
-        <v>213.4480983708869</v>
+        <v>212.8018307592892</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08812881846025714</v>
+        <v>0.08871864384115669</v>
       </c>
       <c r="T39">
-        <v>0.6548133594027366</v>
+        <v>0.663937770458303</v>
       </c>
       <c r="U39">
         <v>0.07113097776675759</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.476770607008266</v>
+        <v>5.332645064718576</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07662937642261144</v>
+        <v>0.07668282779630067</v>
       </c>
       <c r="C40">
-        <v>730.595522001583</v>
+        <v>717.7239078887631</v>
       </c>
       <c r="D40">
-        <v>1035.961522001583</v>
+        <v>1034.446907888763</v>
       </c>
       <c r="E40">
-        <v>97.06600000000003</v>
+        <v>108.4230000000001</v>
       </c>
       <c r="F40">
-        <v>431.566</v>
+        <v>442.9230000000001</v>
       </c>
       <c r="G40">
         <v>126.2</v>
@@ -4567,28 +4567,28 @@
         <v>163.7</v>
       </c>
       <c r="M40">
-        <v>30.69771155088851</v>
+        <v>31.50554606538557</v>
       </c>
       <c r="N40">
-        <v>133.0022884491115</v>
+        <v>132.1944539346144</v>
       </c>
       <c r="O40">
-        <v>26.6004576898223</v>
+        <v>26.43889078692288</v>
       </c>
       <c r="P40">
-        <v>106.4018307592892</v>
+        <v>105.7555631476915</v>
       </c>
       <c r="Q40">
-        <v>212.8018307592892</v>
+        <v>212.1555631476916</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08871864384115669</v>
+        <v>0.08932780775913493</v>
       </c>
       <c r="T40">
-        <v>0.663937770458303</v>
+        <v>0.673361342532085</v>
       </c>
       <c r="U40">
         <v>0.07113097776675759</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.332645064718576</v>
+        <v>5.195910575879637</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07668282779630067</v>
+        <v>0.0767362791699899</v>
       </c>
       <c r="C41">
-        <v>717.7239078887631</v>
+        <v>704.8567161541182</v>
       </c>
       <c r="D41">
-        <v>1034.446907888763</v>
+        <v>1032.936716154118</v>
       </c>
       <c r="E41">
-        <v>108.4230000000001</v>
+        <v>119.78</v>
       </c>
       <c r="F41">
-        <v>442.9230000000001</v>
+        <v>454.28</v>
       </c>
       <c r="G41">
         <v>126.2</v>
@@ -4649,28 +4649,28 @@
         <v>163.7</v>
       </c>
       <c r="M41">
-        <v>31.50554606538557</v>
+        <v>32.31338057988264</v>
       </c>
       <c r="N41">
-        <v>132.1944539346144</v>
+        <v>131.3866194201173</v>
       </c>
       <c r="O41">
-        <v>26.43889078692288</v>
+        <v>26.27732388402347</v>
       </c>
       <c r="P41">
-        <v>105.7555631476915</v>
+        <v>105.1092955360939</v>
       </c>
       <c r="Q41">
-        <v>212.1555631476916</v>
+        <v>211.5092955360939</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08932780775913493</v>
+        <v>0.08995727714104579</v>
       </c>
       <c r="T41">
-        <v>0.673361342532085</v>
+        <v>0.683099033674993</v>
       </c>
       <c r="U41">
         <v>0.07113097776675759</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.195910575879637</v>
+        <v>5.066012811482646</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0767362791699899</v>
+        <v>0.0767897305436791</v>
       </c>
       <c r="C42">
-        <v>704.8567161541182</v>
+        <v>691.9939274571599</v>
       </c>
       <c r="D42">
-        <v>1032.936716154118</v>
+        <v>1031.43092745716</v>
       </c>
       <c r="E42">
-        <v>119.78</v>
+        <v>131.1370000000001</v>
       </c>
       <c r="F42">
-        <v>454.28</v>
+        <v>465.6370000000001</v>
       </c>
       <c r="G42">
         <v>126.2</v>
@@ -4731,28 +4731,28 @@
         <v>163.7</v>
       </c>
       <c r="M42">
-        <v>32.31338057988264</v>
+        <v>33.12121509437971</v>
       </c>
       <c r="N42">
-        <v>131.3866194201173</v>
+        <v>130.5787849056203</v>
       </c>
       <c r="O42">
-        <v>26.27732388402347</v>
+        <v>26.11575698112406</v>
       </c>
       <c r="P42">
-        <v>105.1092955360939</v>
+        <v>104.4630279244962</v>
       </c>
       <c r="Q42">
-        <v>211.5092955360939</v>
+        <v>210.8630279244963</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08995727714104579</v>
+        <v>0.09060808446810614</v>
       </c>
       <c r="T42">
-        <v>0.683099033674993</v>
+        <v>0.6931668160430843</v>
       </c>
       <c r="U42">
         <v>0.07113097776675759</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.066012811482646</v>
+        <v>4.942451523397704</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0767897305436791</v>
+        <v>0.07684318191736833</v>
       </c>
       <c r="C43">
-        <v>691.9939274571599</v>
+        <v>679.1355225700099</v>
       </c>
       <c r="D43">
-        <v>1031.43092745716</v>
+        <v>1029.92952257001</v>
       </c>
       <c r="E43">
-        <v>131.1370000000001</v>
+        <v>142.4940000000001</v>
       </c>
       <c r="F43">
-        <v>465.6370000000001</v>
+        <v>476.9940000000001</v>
       </c>
       <c r="G43">
         <v>126.2</v>
@@ -4813,28 +4813,28 @@
         <v>163.7</v>
       </c>
       <c r="M43">
-        <v>33.12121509437971</v>
+        <v>33.92904960887677</v>
       </c>
       <c r="N43">
-        <v>130.5787849056203</v>
+        <v>129.7709503911232</v>
       </c>
       <c r="O43">
-        <v>26.11575698112406</v>
+        <v>25.95419007822465</v>
       </c>
       <c r="P43">
-        <v>104.4630279244962</v>
+        <v>103.8167603128986</v>
       </c>
       <c r="Q43">
-        <v>210.8630279244963</v>
+        <v>210.2167603128986</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09060808446810614</v>
+        <v>0.09128133342713411</v>
       </c>
       <c r="T43">
-        <v>0.6931668160430843</v>
+        <v>0.7035817633204201</v>
       </c>
       <c r="U43">
         <v>0.07113097776675759</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.942451523397704</v>
+        <v>4.824774106173948</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07684318191736833</v>
+        <v>0.07689663329105756</v>
       </c>
       <c r="C44">
-        <v>679.13552257001</v>
+        <v>666.2814823765865</v>
       </c>
       <c r="D44">
-        <v>1029.92952257001</v>
+        <v>1028.432482376586</v>
       </c>
       <c r="E44">
-        <v>142.494</v>
+        <v>153.851</v>
       </c>
       <c r="F44">
-        <v>476.994</v>
+        <v>488.351</v>
       </c>
       <c r="G44">
         <v>126.2</v>
@@ -4895,28 +4895,28 @@
         <v>163.7</v>
       </c>
       <c r="M44">
-        <v>33.92904960887677</v>
+        <v>34.73688412337383</v>
       </c>
       <c r="N44">
-        <v>129.7709503911232</v>
+        <v>128.9631158766261</v>
       </c>
       <c r="O44">
-        <v>25.95419007822465</v>
+        <v>25.79262317532523</v>
       </c>
       <c r="P44">
-        <v>103.8167603128986</v>
+        <v>103.1704927013009</v>
       </c>
       <c r="Q44">
-        <v>210.2167603128986</v>
+        <v>209.570492701301</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0912813334271341</v>
+        <v>0.09197820515665428</v>
       </c>
       <c r="T44">
-        <v>0.70358176332042</v>
+        <v>0.7143621473443291</v>
       </c>
       <c r="U44">
         <v>0.07113097776675759</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.824774106173949</v>
+        <v>4.71257005719316</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07689663329105756</v>
+        <v>0.07695008466474679</v>
       </c>
       <c r="C45">
-        <v>666.2814823765865</v>
+        <v>653.4317878717877</v>
       </c>
       <c r="D45">
-        <v>1028.432482376586</v>
+        <v>1026.939787871788</v>
       </c>
       <c r="E45">
-        <v>153.851</v>
+        <v>165.208</v>
       </c>
       <c r="F45">
-        <v>488.351</v>
+        <v>499.708</v>
       </c>
       <c r="G45">
         <v>126.2</v>
@@ -4977,28 +4977,28 @@
         <v>163.7</v>
       </c>
       <c r="M45">
-        <v>34.73688412337383</v>
+        <v>35.5447186378709</v>
       </c>
       <c r="N45">
-        <v>128.9631158766261</v>
+        <v>128.1552813621291</v>
       </c>
       <c r="O45">
-        <v>25.79262317532523</v>
+        <v>25.63105627242582</v>
       </c>
       <c r="P45">
-        <v>103.1704927013009</v>
+        <v>102.5242250897033</v>
       </c>
       <c r="Q45">
-        <v>209.570492701301</v>
+        <v>208.9242250897033</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09197820515665428</v>
+        <v>0.09269996516222875</v>
       </c>
       <c r="T45">
-        <v>0.7143621473443291</v>
+        <v>0.7255275450833776</v>
       </c>
       <c r="U45">
         <v>0.07113097776675759</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.71257005719316</v>
+        <v>4.605466192256952</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07695008466474679</v>
+        <v>0.07700353603843599</v>
       </c>
       <c r="C46">
-        <v>653.4317878717877</v>
+        <v>640.5864201606921</v>
       </c>
       <c r="D46">
-        <v>1026.939787871788</v>
+        <v>1025.451420160692</v>
       </c>
       <c r="E46">
-        <v>165.208</v>
+        <v>176.5650000000001</v>
       </c>
       <c r="F46">
-        <v>499.708</v>
+        <v>511.0650000000001</v>
       </c>
       <c r="G46">
         <v>126.2</v>
@@ -5059,28 +5059,28 @@
         <v>163.7</v>
       </c>
       <c r="M46">
-        <v>35.5447186378709</v>
+        <v>36.35255315236797</v>
       </c>
       <c r="N46">
-        <v>128.1552813621291</v>
+        <v>127.347446847632</v>
       </c>
       <c r="O46">
-        <v>25.63105627242582</v>
+        <v>25.46948936952641</v>
       </c>
       <c r="P46">
-        <v>102.5242250897033</v>
+        <v>101.8779574781056</v>
       </c>
       <c r="Q46">
-        <v>208.9242250897033</v>
+        <v>208.2779574781057</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09269996516222875</v>
+        <v>0.09344797098618773</v>
       </c>
       <c r="T46">
-        <v>0.7255275450833776</v>
+        <v>0.7370989572856643</v>
       </c>
       <c r="U46">
         <v>0.07113097776675759</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.605466192256952</v>
+        <v>4.503122499095686</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07700353603843599</v>
+        <v>0.07797698741212521</v>
       </c>
       <c r="C47">
-        <v>640.5864201606921</v>
+        <v>602.8587455580744</v>
       </c>
       <c r="D47">
-        <v>1025.451420160692</v>
+        <v>999.0807455580745</v>
       </c>
       <c r="E47">
-        <v>176.5650000000001</v>
+        <v>187.922</v>
       </c>
       <c r="F47">
-        <v>511.0650000000001</v>
+        <v>522.422</v>
       </c>
       <c r="G47">
         <v>126.2</v>
@@ -5141,45 +5141,45 @@
         <v>163.7</v>
       </c>
       <c r="M47">
-        <v>36.35255315236797</v>
+        <v>38.46644266686503</v>
       </c>
       <c r="N47">
-        <v>127.347446847632</v>
+        <v>125.233557333135</v>
       </c>
       <c r="O47">
-        <v>25.46948936952641</v>
+        <v>25.04671146662699</v>
       </c>
       <c r="P47">
-        <v>101.8779574781056</v>
+        <v>100.186845866508</v>
       </c>
       <c r="Q47">
-        <v>208.2779574781057</v>
+        <v>206.586845866508</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09344797098618773</v>
+        <v>0.09422368072955262</v>
       </c>
       <c r="T47">
-        <v>0.7370989572856643</v>
+        <v>0.749098940310258</v>
       </c>
       <c r="U47">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.05690478221340607</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.503122499095686</v>
+        <v>4.25565736394468</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07797698741212521</v>
+        <v>0.07805043878581443</v>
       </c>
       <c r="C48">
-        <v>602.8587455580744</v>
+        <v>589.5668812704422</v>
       </c>
       <c r="D48">
-        <v>999.0807455580745</v>
+        <v>997.1458812704423</v>
       </c>
       <c r="E48">
-        <v>187.922</v>
+        <v>199.2790000000001</v>
       </c>
       <c r="F48">
-        <v>522.422</v>
+        <v>533.7790000000001</v>
       </c>
       <c r="G48">
         <v>126.2</v>
@@ -5223,28 +5223,28 @@
         <v>163.7</v>
       </c>
       <c r="M48">
-        <v>38.46644266686503</v>
+        <v>39.3026696813621</v>
       </c>
       <c r="N48">
-        <v>125.233557333135</v>
+        <v>124.3973303186379</v>
       </c>
       <c r="O48">
-        <v>25.04671146662699</v>
+        <v>24.87946606372758</v>
       </c>
       <c r="P48">
-        <v>100.186845866508</v>
+        <v>99.51786425491032</v>
       </c>
       <c r="Q48">
-        <v>206.586845866508</v>
+        <v>205.9178642549103</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09422368072955262</v>
+        <v>0.09502866253870486</v>
       </c>
       <c r="T48">
-        <v>0.749098940310258</v>
+        <v>0.7615517528829495</v>
       </c>
       <c r="U48">
         <v>0.07363097776675757</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.25565736394468</v>
+        <v>4.165111462584155</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07805043878581443</v>
+        <v>0.07812389015950365</v>
       </c>
       <c r="C49">
-        <v>589.5668812704422</v>
+        <v>576.2824967858713</v>
       </c>
       <c r="D49">
-        <v>997.1458812704423</v>
+        <v>995.2184967858714</v>
       </c>
       <c r="E49">
-        <v>199.2790000000001</v>
+        <v>210.6360000000001</v>
       </c>
       <c r="F49">
-        <v>533.7790000000001</v>
+        <v>545.1360000000001</v>
       </c>
       <c r="G49">
         <v>126.2</v>
@@ -5305,28 +5305,28 @@
         <v>163.7</v>
       </c>
       <c r="M49">
-        <v>39.3026696813621</v>
+        <v>40.13889669585916</v>
       </c>
       <c r="N49">
-        <v>124.3973303186379</v>
+        <v>123.5611033041408</v>
       </c>
       <c r="O49">
-        <v>24.87946606372758</v>
+        <v>24.71222066082817</v>
       </c>
       <c r="P49">
-        <v>99.51786425491032</v>
+        <v>98.84888264331266</v>
       </c>
       <c r="Q49">
-        <v>205.9178642549103</v>
+        <v>205.2488826433127</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09502866253870486</v>
+        <v>0.09586460518667064</v>
       </c>
       <c r="T49">
-        <v>0.7615517528829495</v>
+        <v>0.7744835197853599</v>
       </c>
       <c r="U49">
         <v>0.07363097776675757</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.165111462584155</v>
+        <v>4.078338307113651</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07812389015950363</v>
+        <v>0.07956934153319287</v>
       </c>
       <c r="C50">
-        <v>576.2824967858717</v>
+        <v>528.4569403522006</v>
       </c>
       <c r="D50">
-        <v>995.2184967858717</v>
+        <v>958.7499403522007</v>
       </c>
       <c r="E50">
-        <v>210.636</v>
+        <v>221.9930000000001</v>
       </c>
       <c r="F50">
-        <v>545.136</v>
+        <v>556.4930000000001</v>
       </c>
       <c r="G50">
         <v>126.2</v>
@@ -5387,45 +5387,45 @@
         <v>163.7</v>
       </c>
       <c r="M50">
-        <v>40.13889669585915</v>
+        <v>42.92284921035623</v>
       </c>
       <c r="N50">
-        <v>123.5611033041408</v>
+        <v>120.7771507896438</v>
       </c>
       <c r="O50">
-        <v>24.71222066082817</v>
+        <v>24.15543015792876</v>
       </c>
       <c r="P50">
-        <v>98.84888264331266</v>
+        <v>96.62172063171502</v>
       </c>
       <c r="Q50">
-        <v>205.2488826433127</v>
+        <v>203.0217206317151</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09586460518667064</v>
+        <v>0.09673332989926253</v>
       </c>
       <c r="T50">
-        <v>0.7744835197853599</v>
+        <v>0.7879224148015903</v>
       </c>
       <c r="U50">
-        <v>0.07363097776675757</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.05890478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.078338307113652</v>
+        <v>3.813819515981787</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07956934153319287</v>
+        <v>0.07967079290688207</v>
       </c>
       <c r="C51">
-        <v>528.4569403522006</v>
+        <v>514.6404540971001</v>
       </c>
       <c r="D51">
-        <v>958.7499403522007</v>
+        <v>956.2904540971001</v>
       </c>
       <c r="E51">
-        <v>221.9930000000001</v>
+        <v>233.35</v>
       </c>
       <c r="F51">
-        <v>556.4930000000001</v>
+        <v>567.85</v>
       </c>
       <c r="G51">
         <v>126.2</v>
@@ -5469,28 +5469,28 @@
         <v>163.7</v>
       </c>
       <c r="M51">
-        <v>42.92284921035623</v>
+        <v>43.79882572485329</v>
       </c>
       <c r="N51">
-        <v>120.7771507896438</v>
+        <v>119.9011742751467</v>
       </c>
       <c r="O51">
-        <v>24.15543015792876</v>
+        <v>23.98023485502934</v>
       </c>
       <c r="P51">
-        <v>96.62172063171502</v>
+        <v>95.92093942011736</v>
       </c>
       <c r="Q51">
-        <v>203.0217206317151</v>
+        <v>202.3209394201174</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09673332989926253</v>
+        <v>0.09763680360035809</v>
       </c>
       <c r="T51">
-        <v>0.7879224148015903</v>
+        <v>0.80189886561847</v>
       </c>
       <c r="U51">
         <v>0.07713097776675758</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.813819515981787</v>
+        <v>3.737543125662151</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07967079290688207</v>
+        <v>0.07977224428057131</v>
       </c>
       <c r="C52">
-        <v>514.6404540971001</v>
+        <v>500.8365542201005</v>
       </c>
       <c r="D52">
-        <v>956.2904540971001</v>
+        <v>953.8435542201006</v>
       </c>
       <c r="E52">
-        <v>233.35</v>
+        <v>244.707</v>
       </c>
       <c r="F52">
-        <v>567.85</v>
+        <v>579.207</v>
       </c>
       <c r="G52">
         <v>126.2</v>
@@ -5551,28 +5551,28 @@
         <v>163.7</v>
       </c>
       <c r="M52">
-        <v>43.79882572485329</v>
+        <v>44.67480223935036</v>
       </c>
       <c r="N52">
-        <v>119.9011742751467</v>
+        <v>119.0251977606496</v>
       </c>
       <c r="O52">
-        <v>23.98023485502934</v>
+        <v>23.80503955212993</v>
       </c>
       <c r="P52">
-        <v>95.92093942011736</v>
+        <v>95.22015820851971</v>
       </c>
       <c r="Q52">
-        <v>202.3209394201174</v>
+        <v>201.6201582085197</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09763680360035809</v>
+        <v>0.09857715377904941</v>
       </c>
       <c r="T52">
-        <v>0.80189886561847</v>
+        <v>0.8164457838156306</v>
       </c>
       <c r="U52">
         <v>0.07713097776675758</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.737543125662151</v>
+        <v>3.664257966335442</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07977224428057131</v>
+        <v>0.0798736956542605</v>
       </c>
       <c r="C53">
-        <v>500.8365542201005</v>
+        <v>487.0451443519312</v>
       </c>
       <c r="D53">
-        <v>953.8435542201006</v>
+        <v>951.4091443519313</v>
       </c>
       <c r="E53">
-        <v>244.707</v>
+        <v>256.0640000000001</v>
       </c>
       <c r="F53">
-        <v>579.207</v>
+        <v>590.5640000000001</v>
       </c>
       <c r="G53">
         <v>126.2</v>
@@ -5633,28 +5633,28 @@
         <v>163.7</v>
       </c>
       <c r="M53">
-        <v>44.67480223935036</v>
+        <v>45.55077875384742</v>
       </c>
       <c r="N53">
-        <v>119.0251977606496</v>
+        <v>118.1492212461526</v>
       </c>
       <c r="O53">
-        <v>23.80503955212993</v>
+        <v>23.62984424923052</v>
       </c>
       <c r="P53">
-        <v>95.22015820851971</v>
+        <v>94.51937699692205</v>
       </c>
       <c r="Q53">
-        <v>201.6201582085197</v>
+        <v>200.9193769969221</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09857715377904941</v>
+        <v>0.09955668521518617</v>
       </c>
       <c r="T53">
-        <v>0.8164457838156306</v>
+        <v>0.8315988236043392</v>
       </c>
       <c r="U53">
         <v>0.07713097776675758</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.664257966335442</v>
+        <v>3.593791466982837</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0798736956542605</v>
+        <v>0.07997514702794974</v>
       </c>
       <c r="C54">
-        <v>487.0451443519312</v>
+        <v>473.2661291046322</v>
       </c>
       <c r="D54">
-        <v>951.4091443519313</v>
+        <v>948.9871291046323</v>
       </c>
       <c r="E54">
-        <v>256.0640000000001</v>
+        <v>267.421</v>
       </c>
       <c r="F54">
-        <v>590.5640000000001</v>
+        <v>601.921</v>
       </c>
       <c r="G54">
         <v>126.2</v>
@@ -5715,28 +5715,28 @@
         <v>163.7</v>
       </c>
       <c r="M54">
-        <v>45.55077875384742</v>
+        <v>46.42675526834449</v>
       </c>
       <c r="N54">
-        <v>118.1492212461526</v>
+        <v>117.2732447316555</v>
       </c>
       <c r="O54">
-        <v>23.62984424923052</v>
+        <v>23.4546489463311</v>
       </c>
       <c r="P54">
-        <v>94.51937699692205</v>
+        <v>93.81859578532439</v>
       </c>
       <c r="Q54">
-        <v>200.9193769969221</v>
+        <v>200.2185957853244</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09955668521518617</v>
+        <v>0.1005778988400947</v>
       </c>
       <c r="T54">
-        <v>0.8315988236043392</v>
+        <v>0.847396673596823</v>
       </c>
       <c r="U54">
         <v>0.07713097776675758</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.593791466982837</v>
+        <v>3.52598408081335</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07997514702794974</v>
+        <v>0.08128619840163896</v>
       </c>
       <c r="C55">
-        <v>473.2661291046322</v>
+        <v>431.6835829588158</v>
       </c>
       <c r="D55">
-        <v>948.9871291046323</v>
+        <v>918.7615829588158</v>
       </c>
       <c r="E55">
-        <v>267.421</v>
+        <v>278.778</v>
       </c>
       <c r="F55">
-        <v>601.921</v>
+        <v>613.278</v>
       </c>
       <c r="G55">
         <v>126.2</v>
@@ -5797,45 +5797,45 @@
         <v>163.7</v>
       </c>
       <c r="M55">
-        <v>46.42675526834449</v>
+        <v>49.01991018284156</v>
       </c>
       <c r="N55">
-        <v>117.2732447316555</v>
+        <v>114.6800898171584</v>
       </c>
       <c r="O55">
-        <v>23.4546489463311</v>
+        <v>22.93601796343169</v>
       </c>
       <c r="P55">
-        <v>93.81859578532439</v>
+        <v>91.74407185372675</v>
       </c>
       <c r="Q55">
-        <v>200.2185957853244</v>
+        <v>198.1440718537268</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1005778988400947</v>
+        <v>0.1016435130573906</v>
       </c>
       <c r="T55">
-        <v>0.847396673596823</v>
+        <v>0.8638813866324581</v>
       </c>
       <c r="U55">
-        <v>0.07713097776675758</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.06170478221340606</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.52598408081335</v>
+        <v>3.339459403116163</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08128619840163896</v>
+        <v>0.08141004977532817</v>
       </c>
       <c r="C56">
-        <v>431.6835829588158</v>
+        <v>417.5704952663456</v>
       </c>
       <c r="D56">
-        <v>918.7615829588158</v>
+        <v>916.0054952663456</v>
       </c>
       <c r="E56">
-        <v>278.778</v>
+        <v>290.1350000000001</v>
       </c>
       <c r="F56">
-        <v>613.278</v>
+        <v>624.6350000000001</v>
       </c>
       <c r="G56">
         <v>126.2</v>
@@ -5879,28 +5879,28 @@
         <v>163.7</v>
       </c>
       <c r="M56">
-        <v>49.01991018284156</v>
+        <v>49.92768629733863</v>
       </c>
       <c r="N56">
-        <v>114.6800898171584</v>
+        <v>113.7723137026614</v>
       </c>
       <c r="O56">
-        <v>22.93601796343169</v>
+        <v>22.75446274053228</v>
       </c>
       <c r="P56">
-        <v>91.74407185372675</v>
+        <v>91.01785096212909</v>
       </c>
       <c r="Q56">
-        <v>198.1440718537268</v>
+        <v>197.4178509621291</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1016435130573906</v>
+        <v>0.1027564879065663</v>
       </c>
       <c r="T56">
-        <v>0.8638813866324581</v>
+        <v>0.8810987535807882</v>
       </c>
       <c r="U56">
         <v>0.07993097776675759</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.339459403116163</v>
+        <v>3.278741959423142</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08141004977532817</v>
+        <v>0.0815339011490174</v>
       </c>
       <c r="C57">
-        <v>417.5704952663456</v>
+        <v>403.4738934636426</v>
       </c>
       <c r="D57">
-        <v>916.0054952663456</v>
+        <v>913.2658934636428</v>
       </c>
       <c r="E57">
-        <v>290.1350000000001</v>
+        <v>301.4920000000001</v>
       </c>
       <c r="F57">
-        <v>624.6350000000001</v>
+        <v>635.9920000000001</v>
       </c>
       <c r="G57">
         <v>126.2</v>
@@ -5961,28 +5961,28 @@
         <v>163.7</v>
       </c>
       <c r="M57">
-        <v>49.92768629733863</v>
+        <v>50.8354624118357</v>
       </c>
       <c r="N57">
-        <v>113.7723137026614</v>
+        <v>112.8645375881643</v>
       </c>
       <c r="O57">
-        <v>22.75446274053228</v>
+        <v>22.57290751763286</v>
       </c>
       <c r="P57">
-        <v>91.01785096212909</v>
+        <v>90.29163007053144</v>
       </c>
       <c r="Q57">
-        <v>197.4178509621291</v>
+        <v>196.6916300705315</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1027564879065663</v>
+        <v>0.1039200525216136</v>
       </c>
       <c r="T57">
-        <v>0.8810987535807882</v>
+        <v>0.8990987281176787</v>
       </c>
       <c r="U57">
         <v>0.07993097776675759</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.278741959423142</v>
+        <v>3.220192995862014</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0815339011490174</v>
+        <v>0.08165775252270661</v>
       </c>
       <c r="C58">
-        <v>403.4738934636426</v>
+        <v>389.3936300731099</v>
       </c>
       <c r="D58">
-        <v>913.2658934636428</v>
+        <v>910.5426300731099</v>
       </c>
       <c r="E58">
-        <v>301.4920000000001</v>
+        <v>312.849</v>
       </c>
       <c r="F58">
-        <v>635.9920000000001</v>
+        <v>647.349</v>
       </c>
       <c r="G58">
         <v>126.2</v>
@@ -6043,28 +6043,28 @@
         <v>163.7</v>
       </c>
       <c r="M58">
-        <v>50.8354624118357</v>
+        <v>51.74323852633276</v>
       </c>
       <c r="N58">
-        <v>112.8645375881643</v>
+        <v>111.9567614736672</v>
       </c>
       <c r="O58">
-        <v>22.57290751763286</v>
+        <v>22.39135229473345</v>
       </c>
       <c r="P58">
-        <v>90.29163007053144</v>
+        <v>89.56540917893378</v>
       </c>
       <c r="Q58">
-        <v>196.6916300705315</v>
+        <v>195.9654091789338</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1039200525216136</v>
+        <v>0.1051377364210817</v>
       </c>
       <c r="T58">
-        <v>0.8990987281176787</v>
+        <v>0.917935910772564</v>
       </c>
       <c r="U58">
         <v>0.07993097776675759</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.220192995862014</v>
+        <v>3.163698381899522</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08165775252270661</v>
+        <v>0.08178160389639583</v>
       </c>
       <c r="C59">
-        <v>389.3936300731099</v>
+        <v>375.3295593709699</v>
       </c>
       <c r="D59">
-        <v>910.5426300731099</v>
+        <v>907.83555937097</v>
       </c>
       <c r="E59">
-        <v>312.849</v>
+        <v>324.2060000000001</v>
       </c>
       <c r="F59">
-        <v>647.349</v>
+        <v>658.7060000000001</v>
       </c>
       <c r="G59">
         <v>126.2</v>
@@ -6125,28 +6125,28 @@
         <v>163.7</v>
       </c>
       <c r="M59">
-        <v>51.74323852633276</v>
+        <v>52.65101464082984</v>
       </c>
       <c r="N59">
-        <v>111.9567614736672</v>
+        <v>111.0489853591702</v>
       </c>
       <c r="O59">
-        <v>22.39135229473345</v>
+        <v>22.20979707183403</v>
       </c>
       <c r="P59">
-        <v>89.56540917893378</v>
+        <v>88.83918828733613</v>
       </c>
       <c r="Q59">
-        <v>195.9654091789338</v>
+        <v>195.2391882873362</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1051377364210817</v>
+        <v>0.1064134052681436</v>
       </c>
       <c r="T59">
-        <v>0.917935910772564</v>
+        <v>0.9376701021253011</v>
       </c>
       <c r="U59">
         <v>0.07993097776675759</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.163698381899522</v>
+        <v>3.109151858073668</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08178160389639583</v>
+        <v>0.08190545527008505</v>
       </c>
       <c r="C60">
-        <v>375.3295593709701</v>
+        <v>361.2815373612744</v>
       </c>
       <c r="D60">
-        <v>907.83555937097</v>
+        <v>905.1445373612744</v>
       </c>
       <c r="E60">
-        <v>324.206</v>
+        <v>335.563</v>
       </c>
       <c r="F60">
-        <v>658.706</v>
+        <v>670.063</v>
       </c>
       <c r="G60">
         <v>126.2</v>
@@ -6207,28 +6207,28 @@
         <v>163.7</v>
       </c>
       <c r="M60">
-        <v>52.65101464082983</v>
+        <v>53.55879075532689</v>
       </c>
       <c r="N60">
-        <v>111.0489853591702</v>
+        <v>110.1412092446731</v>
       </c>
       <c r="O60">
-        <v>22.20979707183403</v>
+        <v>22.02824184893462</v>
       </c>
       <c r="P60">
-        <v>88.83918828733613</v>
+        <v>88.11296739573848</v>
       </c>
       <c r="Q60">
-        <v>195.2391882873362</v>
+        <v>194.5129673957385</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1064134052681436</v>
+        <v>0.1077513018638426</v>
       </c>
       <c r="T60">
-        <v>0.9376701021253008</v>
+        <v>0.9583669369586594</v>
       </c>
       <c r="U60">
         <v>0.07993097776675759</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.109151858073669</v>
+        <v>3.056454368953776</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08190545527008505</v>
+        <v>0.08202930664377428</v>
       </c>
       <c r="C61">
-        <v>361.2815373612744</v>
+        <v>347.2494217503698</v>
       </c>
       <c r="D61">
-        <v>905.1445373612744</v>
+        <v>902.4694217503699</v>
       </c>
       <c r="E61">
-        <v>335.563</v>
+        <v>346.92</v>
       </c>
       <c r="F61">
-        <v>670.063</v>
+        <v>681.42</v>
       </c>
       <c r="G61">
         <v>126.2</v>
@@ -6289,28 +6289,28 @@
         <v>163.7</v>
       </c>
       <c r="M61">
-        <v>53.55879075532689</v>
+        <v>54.46656686982395</v>
       </c>
       <c r="N61">
-        <v>110.1412092446731</v>
+        <v>109.233433130176</v>
       </c>
       <c r="O61">
-        <v>22.02824184893462</v>
+        <v>21.84668662603521</v>
       </c>
       <c r="P61">
-        <v>88.11296739573848</v>
+        <v>87.38674650414083</v>
       </c>
       <c r="Q61">
-        <v>194.5129673957385</v>
+        <v>193.7867465041409</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1077513018638426</v>
+        <v>0.1091560932893266</v>
       </c>
       <c r="T61">
-        <v>0.9583669369586594</v>
+        <v>0.9800986135336857</v>
       </c>
       <c r="U61">
         <v>0.07993097776675759</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.056454368953776</v>
+        <v>3.005513462804547</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08202930664377428</v>
+        <v>0.08595955801746348</v>
       </c>
       <c r="C62">
-        <v>347.2494217503698</v>
+        <v>258.5097477468194</v>
       </c>
       <c r="D62">
-        <v>902.4694217503699</v>
+        <v>825.0867477468194</v>
       </c>
       <c r="E62">
-        <v>346.92</v>
+        <v>358.277</v>
       </c>
       <c r="F62">
-        <v>681.42</v>
+        <v>692.777</v>
       </c>
       <c r="G62">
         <v>126.2</v>
@@ -6371,45 +6371,45 @@
         <v>163.7</v>
       </c>
       <c r="M62">
-        <v>54.46656686982395</v>
+        <v>60.77800358432103</v>
       </c>
       <c r="N62">
-        <v>109.233433130176</v>
+        <v>102.921996415679</v>
       </c>
       <c r="O62">
-        <v>21.84668662603521</v>
+        <v>20.5843992831358</v>
       </c>
       <c r="P62">
-        <v>87.38674650414083</v>
+        <v>82.33759713254317</v>
       </c>
       <c r="Q62">
-        <v>193.7867465041409</v>
+        <v>188.7375971325432</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1091560932893266</v>
+        <v>0.1106329253007328</v>
       </c>
       <c r="T62">
-        <v>0.9800986135336857</v>
+        <v>1.002944735061277</v>
       </c>
       <c r="U62">
-        <v>0.07993097776675759</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V62">
         <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.06394478221340608</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.005513462804547</v>
+        <v>2.693408640395518</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08595955801746348</v>
+        <v>0.08614580939115271</v>
       </c>
       <c r="C63">
-        <v>258.5097477468194</v>
+        <v>243.8136520529763</v>
       </c>
       <c r="D63">
-        <v>825.0867477468194</v>
+        <v>821.7476520529763</v>
       </c>
       <c r="E63">
-        <v>358.277</v>
+        <v>369.634</v>
       </c>
       <c r="F63">
-        <v>692.777</v>
+        <v>704.134</v>
       </c>
       <c r="G63">
         <v>126.2</v>
@@ -6453,28 +6453,28 @@
         <v>163.7</v>
       </c>
       <c r="M63">
-        <v>60.77800358432103</v>
+        <v>61.77436429881809</v>
       </c>
       <c r="N63">
-        <v>102.921996415679</v>
+        <v>101.9256357011819</v>
       </c>
       <c r="O63">
-        <v>20.5843992831358</v>
+        <v>20.38512714023638</v>
       </c>
       <c r="P63">
-        <v>82.33759713254317</v>
+        <v>81.54050856094553</v>
       </c>
       <c r="Q63">
-        <v>188.7375971325432</v>
+        <v>187.9405085609455</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1106329253007328</v>
+        <v>0.1121874853127393</v>
       </c>
       <c r="T63">
-        <v>1.002944735061277</v>
+        <v>1.02699328403769</v>
       </c>
       <c r="U63">
         <v>0.08773097776675759</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.693408640395518</v>
+        <v>2.649966565550429</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08614580939115271</v>
+        <v>0.08633206076484193</v>
       </c>
       <c r="C64">
-        <v>243.8136520529763</v>
+        <v>229.1444738198594</v>
       </c>
       <c r="D64">
-        <v>821.7476520529763</v>
+        <v>818.4354738198593</v>
       </c>
       <c r="E64">
-        <v>369.634</v>
+        <v>380.991</v>
       </c>
       <c r="F64">
-        <v>704.134</v>
+        <v>715.491</v>
       </c>
       <c r="G64">
         <v>126.2</v>
@@ -6535,28 +6535,28 @@
         <v>163.7</v>
       </c>
       <c r="M64">
-        <v>61.77436429881809</v>
+        <v>62.77072501331515</v>
       </c>
       <c r="N64">
-        <v>101.9256357011819</v>
+        <v>100.9292749866848</v>
       </c>
       <c r="O64">
-        <v>20.38512714023638</v>
+        <v>20.18585499733697</v>
       </c>
       <c r="P64">
-        <v>81.54050856094553</v>
+        <v>80.74341998934787</v>
       </c>
       <c r="Q64">
-        <v>187.9405085609455</v>
+        <v>187.1434199893479</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1121874853127393</v>
+        <v>0.1138260755956651</v>
       </c>
       <c r="T64">
-        <v>1.02699328403769</v>
+        <v>1.052341754580395</v>
       </c>
       <c r="U64">
         <v>0.08773097776675759</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.649966565550429</v>
+        <v>2.607903604192486</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08633206076484193</v>
+        <v>0.08651831213853114</v>
       </c>
       <c r="C65">
-        <v>229.1444738198594</v>
+        <v>214.501888869424</v>
       </c>
       <c r="D65">
-        <v>818.4354738198593</v>
+        <v>815.149888869424</v>
       </c>
       <c r="E65">
-        <v>380.991</v>
+        <v>392.3480000000001</v>
       </c>
       <c r="F65">
-        <v>715.491</v>
+        <v>726.8480000000001</v>
       </c>
       <c r="G65">
         <v>126.2</v>
@@ -6617,28 +6617,28 @@
         <v>163.7</v>
       </c>
       <c r="M65">
-        <v>62.77072501331515</v>
+        <v>63.76708572781223</v>
       </c>
       <c r="N65">
-        <v>100.9292749866848</v>
+        <v>99.93291427218776</v>
       </c>
       <c r="O65">
-        <v>20.18585499733697</v>
+        <v>19.98658285443755</v>
       </c>
       <c r="P65">
-        <v>80.74341998934787</v>
+        <v>79.9463314177502</v>
       </c>
       <c r="Q65">
-        <v>187.1434199893479</v>
+        <v>186.3463314177502</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1138260755956651</v>
+        <v>0.1155556986720868</v>
       </c>
       <c r="T65">
-        <v>1.052341754580395</v>
+        <v>1.079098473486583</v>
       </c>
       <c r="U65">
         <v>0.08773097776675759</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.607903604192486</v>
+        <v>2.567155110376977</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08651831213853114</v>
+        <v>0.08670456351222036</v>
       </c>
       <c r="C66">
-        <v>214.501888869424</v>
+        <v>199.8855782084237</v>
       </c>
       <c r="D66">
-        <v>815.149888869424</v>
+        <v>811.8905782084237</v>
       </c>
       <c r="E66">
-        <v>392.3480000000001</v>
+        <v>403.705</v>
       </c>
       <c r="F66">
-        <v>726.8480000000001</v>
+        <v>738.205</v>
       </c>
       <c r="G66">
         <v>126.2</v>
@@ -6699,28 +6699,28 @@
         <v>163.7</v>
       </c>
       <c r="M66">
-        <v>63.76708572781223</v>
+        <v>64.76344644230929</v>
       </c>
       <c r="N66">
-        <v>99.93291427218776</v>
+        <v>98.9365535576907</v>
       </c>
       <c r="O66">
-        <v>19.98658285443755</v>
+        <v>19.78731071153814</v>
       </c>
       <c r="P66">
-        <v>79.9463314177502</v>
+        <v>79.14924284615256</v>
       </c>
       <c r="Q66">
-        <v>186.3463314177502</v>
+        <v>185.5492428461526</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1155556986720868</v>
+        <v>0.1173841573528755</v>
       </c>
       <c r="T66">
-        <v>1.079098473486583</v>
+        <v>1.10738414775884</v>
       </c>
       <c r="U66">
         <v>0.08773097776675759</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.567155110376977</v>
+        <v>2.527660416371178</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08670456351222036</v>
+        <v>0.08895001488590959</v>
       </c>
       <c r="C67">
-        <v>199.8855782084237</v>
+        <v>151.1912092549711</v>
       </c>
       <c r="D67">
-        <v>811.8905782084237</v>
+        <v>774.5532092549711</v>
       </c>
       <c r="E67">
-        <v>403.705</v>
+        <v>415.062</v>
       </c>
       <c r="F67">
-        <v>738.205</v>
+        <v>749.562</v>
       </c>
       <c r="G67">
         <v>126.2</v>
@@ -6781,45 +6781,45 @@
         <v>163.7</v>
       </c>
       <c r="M67">
-        <v>64.76344644230929</v>
+        <v>68.68309895680635</v>
       </c>
       <c r="N67">
-        <v>98.9365535576907</v>
+        <v>95.01690104319364</v>
       </c>
       <c r="O67">
-        <v>19.78731071153814</v>
+        <v>19.00338020863873</v>
       </c>
       <c r="P67">
-        <v>79.14924284615256</v>
+        <v>76.01352083455491</v>
       </c>
       <c r="Q67">
-        <v>185.5492428461526</v>
+        <v>182.413520834555</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1173841573528755</v>
+        <v>0.1193201724266517</v>
       </c>
       <c r="T67">
-        <v>1.10738414775884</v>
+        <v>1.137333685223582</v>
       </c>
       <c r="U67">
-        <v>0.08773097776675759</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.07018478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.527660416371178</v>
+        <v>2.383410220073911</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08895001488590959</v>
+        <v>0.08916746625959879</v>
       </c>
       <c r="C68">
-        <v>151.1912092549711</v>
+        <v>136.4000050348095</v>
       </c>
       <c r="D68">
-        <v>774.5532092549711</v>
+        <v>771.1190050348096</v>
       </c>
       <c r="E68">
-        <v>415.062</v>
+        <v>426.4190000000001</v>
       </c>
       <c r="F68">
-        <v>749.562</v>
+        <v>760.9190000000001</v>
       </c>
       <c r="G68">
         <v>126.2</v>
@@ -6863,28 +6863,28 @@
         <v>163.7</v>
       </c>
       <c r="M68">
-        <v>68.68309895680635</v>
+        <v>69.72375197130341</v>
       </c>
       <c r="N68">
-        <v>95.01690104319364</v>
+        <v>93.97624802869657</v>
       </c>
       <c r="O68">
-        <v>19.00338020863873</v>
+        <v>18.79524960573931</v>
       </c>
       <c r="P68">
-        <v>76.01352083455491</v>
+        <v>75.18099842295726</v>
       </c>
       <c r="Q68">
-        <v>182.413520834555</v>
+        <v>181.5809984229573</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1193201724266517</v>
+        <v>0.1213735217473234</v>
       </c>
       <c r="T68">
-        <v>1.137333685223582</v>
+        <v>1.169098346171036</v>
       </c>
       <c r="U68">
         <v>0.09163097776675758</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.383410220073911</v>
+        <v>2.347836933207136</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08916746625959879</v>
+        <v>0.08938491763328801</v>
       </c>
       <c r="C69">
-        <v>136.4000050348095</v>
+        <v>121.6391194507116</v>
       </c>
       <c r="D69">
-        <v>771.1190050348096</v>
+        <v>767.7151194507117</v>
       </c>
       <c r="E69">
-        <v>426.4190000000001</v>
+        <v>437.7760000000001</v>
       </c>
       <c r="F69">
-        <v>760.9190000000001</v>
+        <v>772.2760000000001</v>
       </c>
       <c r="G69">
         <v>126.2</v>
@@ -6945,28 +6945,28 @@
         <v>163.7</v>
       </c>
       <c r="M69">
-        <v>69.72375197130341</v>
+        <v>70.76440498580048</v>
       </c>
       <c r="N69">
-        <v>93.97624802869657</v>
+        <v>92.93559501419951</v>
       </c>
       <c r="O69">
-        <v>18.79524960573931</v>
+        <v>18.5871190028399</v>
       </c>
       <c r="P69">
-        <v>75.18099842295726</v>
+        <v>74.34847601135961</v>
       </c>
       <c r="Q69">
-        <v>181.5809984229573</v>
+        <v>180.7484760113596</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1213735217473234</v>
+        <v>0.1235552054005371</v>
       </c>
       <c r="T69">
-        <v>1.169098346171036</v>
+        <v>1.202848298427705</v>
       </c>
       <c r="U69">
         <v>0.09163097776675758</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.347836933207136</v>
+        <v>2.313309919483501</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08938491763328801</v>
+        <v>0.08960236900697724</v>
       </c>
       <c r="C70">
-        <v>121.6391194507116</v>
+        <v>106.9081527681981</v>
       </c>
       <c r="D70">
-        <v>767.7151194507117</v>
+        <v>764.3411527681982</v>
       </c>
       <c r="E70">
-        <v>437.7760000000001</v>
+        <v>449.1330000000002</v>
       </c>
       <c r="F70">
-        <v>772.2760000000001</v>
+        <v>783.6330000000002</v>
       </c>
       <c r="G70">
         <v>126.2</v>
@@ -7027,28 +7027,28 @@
         <v>163.7</v>
       </c>
       <c r="M70">
-        <v>70.76440498580048</v>
+        <v>71.80505800029755</v>
       </c>
       <c r="N70">
-        <v>92.93559501419951</v>
+        <v>91.89494199970244</v>
       </c>
       <c r="O70">
-        <v>18.5871190028399</v>
+        <v>18.37898839994049</v>
       </c>
       <c r="P70">
-        <v>74.34847601135961</v>
+        <v>73.51595359976196</v>
       </c>
       <c r="Q70">
-        <v>180.7484760113596</v>
+        <v>179.915953599762</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1235552054005371</v>
+        <v>0.1258776428378292</v>
       </c>
       <c r="T70">
-        <v>1.202848298427705</v>
+        <v>1.238775666958999</v>
       </c>
       <c r="U70">
         <v>0.09163097776675758</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.313309919483501</v>
+        <v>2.279783688766349</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08960236900697724</v>
+        <v>0.08981982038066645</v>
       </c>
       <c r="C71">
-        <v>106.9081527681981</v>
+        <v>92.20671224907994</v>
       </c>
       <c r="D71">
-        <v>764.3411527681982</v>
+        <v>760.99671224908</v>
       </c>
       <c r="E71">
-        <v>449.1330000000002</v>
+        <v>460.4900000000001</v>
       </c>
       <c r="F71">
-        <v>783.6330000000002</v>
+        <v>794.9900000000001</v>
       </c>
       <c r="G71">
         <v>126.2</v>
@@ -7109,28 +7109,28 @@
         <v>163.7</v>
       </c>
       <c r="M71">
-        <v>71.80505800029755</v>
+        <v>72.84571101479462</v>
       </c>
       <c r="N71">
-        <v>91.89494199970244</v>
+        <v>90.85428898520537</v>
       </c>
       <c r="O71">
-        <v>18.37898839994049</v>
+        <v>18.17085779704108</v>
       </c>
       <c r="P71">
-        <v>73.51595359976196</v>
+        <v>72.68343118816429</v>
       </c>
       <c r="Q71">
-        <v>179.915953599762</v>
+        <v>179.0834311881643</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1258776428378292</v>
+        <v>0.1283549094376074</v>
       </c>
       <c r="T71">
-        <v>1.238775666958999</v>
+        <v>1.277098193392378</v>
       </c>
       <c r="U71">
         <v>0.09163097776675758</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.279783688766349</v>
+        <v>2.247215350355401</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08981982038066645</v>
+        <v>0.09003727175435566</v>
       </c>
       <c r="C72">
-        <v>92.20671224907994</v>
+        <v>77.53441199906081</v>
       </c>
       <c r="D72">
-        <v>760.99671224908</v>
+        <v>757.6814119990609</v>
       </c>
       <c r="E72">
-        <v>460.4900000000001</v>
+        <v>471.8470000000001</v>
       </c>
       <c r="F72">
-        <v>794.9900000000001</v>
+        <v>806.3470000000001</v>
       </c>
       <c r="G72">
         <v>126.2</v>
@@ -7191,28 +7191,28 @@
         <v>163.7</v>
       </c>
       <c r="M72">
-        <v>72.84571101479462</v>
+        <v>73.88636402929168</v>
       </c>
       <c r="N72">
-        <v>90.85428898520537</v>
+        <v>89.8136359707083</v>
       </c>
       <c r="O72">
-        <v>18.17085779704108</v>
+        <v>17.96272719414166</v>
       </c>
       <c r="P72">
-        <v>72.68343118816429</v>
+        <v>71.85090877656664</v>
       </c>
       <c r="Q72">
-        <v>179.0834311881643</v>
+        <v>178.2509087765667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1283549094376074</v>
+        <v>0.131003022009784</v>
       </c>
       <c r="T72">
-        <v>1.277098193392378</v>
+        <v>1.318063652683233</v>
       </c>
       <c r="U72">
         <v>0.09163097776675758</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.247215350355401</v>
+        <v>2.21556442992786</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09003727175435566</v>
+        <v>0.09025472312804489</v>
       </c>
       <c r="C73">
-        <v>77.53441199906092</v>
+        <v>62.8908728193062</v>
       </c>
       <c r="D73">
-        <v>757.6814119990609</v>
+        <v>754.3948728193061</v>
       </c>
       <c r="E73">
-        <v>471.847</v>
+        <v>483.204</v>
       </c>
       <c r="F73">
-        <v>806.347</v>
+        <v>817.704</v>
       </c>
       <c r="G73">
         <v>126.2</v>
@@ -7273,28 +7273,28 @@
         <v>163.7</v>
       </c>
       <c r="M73">
-        <v>73.88636402929167</v>
+        <v>74.92701704378874</v>
       </c>
       <c r="N73">
-        <v>89.81363597070832</v>
+        <v>88.77298295621125</v>
       </c>
       <c r="O73">
-        <v>17.96272719414166</v>
+        <v>17.75459659124225</v>
       </c>
       <c r="P73">
-        <v>71.85090877656665</v>
+        <v>71.018386364969</v>
       </c>
       <c r="Q73">
-        <v>178.2509087765667</v>
+        <v>177.418386364969</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.131003022009784</v>
+        <v>0.1338402854799733</v>
       </c>
       <c r="T73">
-        <v>1.318063652683232</v>
+        <v>1.361955216209147</v>
       </c>
       <c r="U73">
         <v>0.09163097776675758</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.215564429927861</v>
+        <v>2.184792701734418</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09025472312804489</v>
+        <v>0.0904721745017341</v>
       </c>
       <c r="C74">
-        <v>62.8908728193062</v>
+        <v>48.27572206185857</v>
       </c>
       <c r="D74">
-        <v>754.3948728193061</v>
+        <v>751.1367220618586</v>
       </c>
       <c r="E74">
-        <v>483.204</v>
+        <v>494.561</v>
       </c>
       <c r="F74">
-        <v>817.704</v>
+        <v>829.061</v>
       </c>
       <c r="G74">
         <v>126.2</v>
@@ -7355,28 +7355,28 @@
         <v>163.7</v>
       </c>
       <c r="M74">
-        <v>74.92701704378874</v>
+        <v>75.9676700582858</v>
       </c>
       <c r="N74">
-        <v>88.77298295621125</v>
+        <v>87.73232994171418</v>
       </c>
       <c r="O74">
-        <v>17.75459659124225</v>
+        <v>17.54646598834284</v>
       </c>
       <c r="P74">
-        <v>71.018386364969</v>
+        <v>70.18586395337135</v>
       </c>
       <c r="Q74">
-        <v>177.418386364969</v>
+        <v>176.5858639533714</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1338402854799733</v>
+        <v>0.136887716614621</v>
       </c>
       <c r="T74">
-        <v>1.361955216209147</v>
+        <v>1.409098006662908</v>
       </c>
       <c r="U74">
         <v>0.09163097776675758</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.184792701734418</v>
+        <v>2.154864034587371</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0904721745017341</v>
+        <v>0.09068962587542333</v>
       </c>
       <c r="C75">
-        <v>48.27572206185857</v>
+        <v>33.68859348878266</v>
       </c>
       <c r="D75">
-        <v>751.1367220618586</v>
+        <v>747.9065934887826</v>
       </c>
       <c r="E75">
-        <v>494.561</v>
+        <v>505.918</v>
       </c>
       <c r="F75">
-        <v>829.061</v>
+        <v>840.418</v>
       </c>
       <c r="G75">
         <v>126.2</v>
@@ -7437,28 +7437,28 @@
         <v>163.7</v>
       </c>
       <c r="M75">
-        <v>75.9676700582858</v>
+        <v>77.00832307278287</v>
       </c>
       <c r="N75">
-        <v>87.73232994171418</v>
+        <v>86.69167692721712</v>
       </c>
       <c r="O75">
-        <v>17.54646598834284</v>
+        <v>17.33833538544343</v>
       </c>
       <c r="P75">
-        <v>70.18586395337135</v>
+        <v>69.35334154177369</v>
       </c>
       <c r="Q75">
-        <v>176.5858639533714</v>
+        <v>175.7533415417737</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.136887716614621</v>
+        <v>0.140169565528857</v>
       </c>
       <c r="T75">
-        <v>1.409098006662908</v>
+        <v>1.459867165613112</v>
       </c>
       <c r="U75">
         <v>0.09163097776675758</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.154864034587371</v>
+        <v>2.125744250336191</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09068962587542333</v>
+        <v>0.09090707724911254</v>
       </c>
       <c r="C76">
-        <v>33.68859348878266</v>
+        <v>19.12912713493029</v>
       </c>
       <c r="D76">
-        <v>747.9065934887826</v>
+        <v>744.7041271349303</v>
       </c>
       <c r="E76">
-        <v>505.918</v>
+        <v>517.2750000000001</v>
       </c>
       <c r="F76">
-        <v>840.418</v>
+        <v>851.7750000000001</v>
       </c>
       <c r="G76">
         <v>126.2</v>
@@ -7519,28 +7519,28 @@
         <v>163.7</v>
       </c>
       <c r="M76">
-        <v>77.00832307278287</v>
+        <v>78.04897608727994</v>
       </c>
       <c r="N76">
-        <v>86.69167692721712</v>
+        <v>85.65102391272005</v>
       </c>
       <c r="O76">
-        <v>17.33833538544343</v>
+        <v>17.13020478254401</v>
       </c>
       <c r="P76">
-        <v>69.35334154177369</v>
+        <v>68.52081913017604</v>
       </c>
       <c r="Q76">
-        <v>175.7533415417737</v>
+        <v>174.9208191301761</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.140169565528857</v>
+        <v>0.143713962356232</v>
       </c>
       <c r="T76">
-        <v>1.459867165613112</v>
+        <v>1.514697857279332</v>
       </c>
       <c r="U76">
         <v>0.09163097776675758</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.125744250336191</v>
+        <v>2.097400993665041</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09090707724911254</v>
+        <v>0.09112452862280176</v>
       </c>
       <c r="C77">
-        <v>19.12912713493029</v>
+        <v>4.596969174215133</v>
       </c>
       <c r="D77">
-        <v>744.7041271349303</v>
+        <v>741.5289691742151</v>
       </c>
       <c r="E77">
-        <v>517.2750000000001</v>
+        <v>528.6320000000001</v>
       </c>
       <c r="F77">
-        <v>851.7750000000001</v>
+        <v>863.1320000000001</v>
       </c>
       <c r="G77">
         <v>126.2</v>
@@ -7601,28 +7601,28 @@
         <v>163.7</v>
       </c>
       <c r="M77">
-        <v>78.04897608727994</v>
+        <v>79.08962910177701</v>
       </c>
       <c r="N77">
-        <v>85.65102391272005</v>
+        <v>84.61037089822298</v>
       </c>
       <c r="O77">
-        <v>17.13020478254401</v>
+        <v>16.9220741796446</v>
       </c>
       <c r="P77">
-        <v>68.52081913017604</v>
+        <v>67.68829671857839</v>
       </c>
       <c r="Q77">
-        <v>174.9208191301761</v>
+        <v>174.0882967185784</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.143713962356232</v>
+        <v>0.1475537255858881</v>
       </c>
       <c r="T77">
-        <v>1.514697857279332</v>
+        <v>1.574097773251071</v>
       </c>
       <c r="U77">
         <v>0.09163097776675758</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.097400993665041</v>
+        <v>2.069803612169449</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09112452862280176</v>
+        <v>0.09134197999649098</v>
       </c>
       <c r="C78">
-        <v>4.596969174215133</v>
+        <v>-9.908228210705374</v>
       </c>
       <c r="D78">
-        <v>741.5289691742151</v>
+        <v>738.3807717892946</v>
       </c>
       <c r="E78">
-        <v>528.6320000000001</v>
+        <v>539.989</v>
       </c>
       <c r="F78">
-        <v>863.1320000000001</v>
+        <v>874.489</v>
       </c>
       <c r="G78">
         <v>126.2</v>
@@ -7683,28 +7683,28 @@
         <v>163.7</v>
       </c>
       <c r="M78">
-        <v>79.08962910177701</v>
+        <v>80.13028211627407</v>
       </c>
       <c r="N78">
-        <v>84.61037089822298</v>
+        <v>83.56971788372591</v>
       </c>
       <c r="O78">
-        <v>16.9220741796446</v>
+        <v>16.71394357674518</v>
       </c>
       <c r="P78">
-        <v>67.68829671857839</v>
+        <v>66.85577430698073</v>
       </c>
       <c r="Q78">
-        <v>174.0882967185784</v>
+        <v>173.2557743069808</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1475537255858881</v>
+        <v>0.151727381270297</v>
       </c>
       <c r="T78">
-        <v>1.574097773251071</v>
+        <v>1.638662899307308</v>
       </c>
       <c r="U78">
         <v>0.09163097776675758</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.069803612169449</v>
+        <v>2.042923045777638</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09134197999649098</v>
+        <v>0.0915594313701802</v>
       </c>
       <c r="C79">
-        <v>-9.908228210705374</v>
+        <v>-24.3868069554436</v>
       </c>
       <c r="D79">
-        <v>738.3807717892946</v>
+        <v>735.2591930445565</v>
       </c>
       <c r="E79">
-        <v>539.989</v>
+        <v>551.3460000000001</v>
       </c>
       <c r="F79">
-        <v>874.489</v>
+        <v>885.8460000000001</v>
       </c>
       <c r="G79">
         <v>126.2</v>
@@ -7765,28 +7765,28 @@
         <v>163.7</v>
       </c>
       <c r="M79">
-        <v>80.13028211627407</v>
+        <v>81.17093513077114</v>
       </c>
       <c r="N79">
-        <v>83.56971788372591</v>
+        <v>82.52906486922885</v>
       </c>
       <c r="O79">
-        <v>16.71394357674518</v>
+        <v>16.50581297384577</v>
       </c>
       <c r="P79">
-        <v>66.85577430698073</v>
+        <v>66.02325189538308</v>
       </c>
       <c r="Q79">
-        <v>173.2557743069808</v>
+        <v>172.4232518953831</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.151727381270297</v>
+        <v>0.156280460198743</v>
       </c>
       <c r="T79">
-        <v>1.638662899307308</v>
+        <v>1.709097582277749</v>
       </c>
       <c r="U79">
         <v>0.09163097776675758</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.042923045777638</v>
+        <v>2.016731724677924</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0915594313701802</v>
+        <v>0.1007512827438694</v>
       </c>
       <c r="C80">
-        <v>-24.3868069554436</v>
+        <v>-147.2169861234677</v>
       </c>
       <c r="D80">
-        <v>735.2591930445565</v>
+        <v>623.7860138765324</v>
       </c>
       <c r="E80">
-        <v>551.3460000000001</v>
+        <v>562.7030000000001</v>
       </c>
       <c r="F80">
-        <v>885.8460000000001</v>
+        <v>897.2030000000001</v>
       </c>
       <c r="G80">
         <v>126.2</v>
@@ -7847,45 +7847,45 @@
         <v>163.7</v>
       </c>
       <c r="M80">
-        <v>81.17093513077114</v>
+        <v>94.95187074526821</v>
       </c>
       <c r="N80">
-        <v>82.52906486922885</v>
+        <v>68.74812925473178</v>
       </c>
       <c r="O80">
-        <v>16.50581297384577</v>
+        <v>13.74962585094636</v>
       </c>
       <c r="P80">
-        <v>66.02325189538308</v>
+        <v>54.99850340378542</v>
       </c>
       <c r="Q80">
-        <v>172.4232518953831</v>
+        <v>161.3985034037855</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.156280460198743</v>
+        <v>0.161267165691803</v>
       </c>
       <c r="T80">
-        <v>1.709097582277749</v>
+        <v>1.786240330292994</v>
       </c>
       <c r="U80">
-        <v>0.09163097776675758</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V80">
         <v>0.2</v>
       </c>
       <c r="W80">
-        <v>0.07330478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.016731724677924</v>
+        <v>1.724031329926775</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1007512827438694</v>
+        <v>0.1010823341175586</v>
       </c>
       <c r="C81">
-        <v>-147.2169861234677</v>
+        <v>-161.9615929458035</v>
       </c>
       <c r="D81">
-        <v>623.7860138765324</v>
+        <v>620.3984070541965</v>
       </c>
       <c r="E81">
-        <v>562.7030000000001</v>
+        <v>574.0600000000001</v>
       </c>
       <c r="F81">
-        <v>897.2030000000001</v>
+        <v>908.5600000000001</v>
       </c>
       <c r="G81">
         <v>126.2</v>
@@ -7929,28 +7929,28 @@
         <v>163.7</v>
       </c>
       <c r="M81">
-        <v>94.95187074526821</v>
+        <v>96.15379315976527</v>
       </c>
       <c r="N81">
-        <v>68.74812925473178</v>
+        <v>67.54620684023472</v>
       </c>
       <c r="O81">
-        <v>13.74962585094636</v>
+        <v>13.50924136804694</v>
       </c>
       <c r="P81">
-        <v>54.99850340378542</v>
+        <v>54.03696547218777</v>
       </c>
       <c r="Q81">
-        <v>161.3985034037855</v>
+        <v>160.4369654721878</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.161267165691803</v>
+        <v>0.1667525417341689</v>
       </c>
       <c r="T81">
-        <v>1.786240330292994</v>
+        <v>1.871097353109764</v>
       </c>
       <c r="U81">
         <v>0.1058309777667576</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.724031329926775</v>
+        <v>1.70248093830269</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1010823341175586</v>
+        <v>0.1014133854912478</v>
       </c>
       <c r="C82">
-        <v>-161.9615929458035</v>
+        <v>-176.6696042239267</v>
       </c>
       <c r="D82">
-        <v>620.3984070541965</v>
+        <v>617.0473957760734</v>
       </c>
       <c r="E82">
-        <v>574.0600000000001</v>
+        <v>585.4170000000001</v>
       </c>
       <c r="F82">
-        <v>908.5600000000001</v>
+        <v>919.9170000000001</v>
       </c>
       <c r="G82">
         <v>126.2</v>
@@ -8011,28 +8011,28 @@
         <v>163.7</v>
       </c>
       <c r="M82">
-        <v>96.15379315976527</v>
+        <v>97.35571557426235</v>
       </c>
       <c r="N82">
-        <v>67.54620684023472</v>
+        <v>66.34428442573764</v>
       </c>
       <c r="O82">
-        <v>13.50924136804694</v>
+        <v>13.26885688514753</v>
       </c>
       <c r="P82">
-        <v>54.03696547218777</v>
+        <v>53.07542754059011</v>
       </c>
       <c r="Q82">
-        <v>160.4369654721878</v>
+        <v>159.4754275405901</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1667525417341689</v>
+        <v>0.1728153257809945</v>
       </c>
       <c r="T82">
-        <v>1.871097353109764</v>
+        <v>1.964886694117772</v>
       </c>
       <c r="U82">
         <v>0.1058309777667576</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.70248093830269</v>
+        <v>1.681462655113768</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1014133854912478</v>
+        <v>0.1017444368649371</v>
       </c>
       <c r="C83">
-        <v>-176.6696042239267</v>
+        <v>-191.3416097720046</v>
       </c>
       <c r="D83">
-        <v>617.0473957760734</v>
+        <v>613.7323902279954</v>
       </c>
       <c r="E83">
-        <v>585.4170000000001</v>
+        <v>596.7740000000001</v>
       </c>
       <c r="F83">
-        <v>919.9170000000001</v>
+        <v>931.2740000000001</v>
       </c>
       <c r="G83">
         <v>126.2</v>
@@ -8093,28 +8093,28 @@
         <v>163.7</v>
       </c>
       <c r="M83">
-        <v>97.35571557426235</v>
+        <v>98.55763798875941</v>
       </c>
       <c r="N83">
-        <v>66.34428442573764</v>
+        <v>65.14236201124058</v>
       </c>
       <c r="O83">
-        <v>13.26885688514753</v>
+        <v>13.02847240224812</v>
       </c>
       <c r="P83">
-        <v>53.07542754059011</v>
+        <v>52.11388960899247</v>
       </c>
       <c r="Q83">
-        <v>159.4754275405901</v>
+        <v>158.5138896089925</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1728153257809945</v>
+        <v>0.1795517524996894</v>
       </c>
       <c r="T83">
-        <v>1.964886694117772</v>
+        <v>2.069097073015559</v>
       </c>
       <c r="U83">
         <v>0.1058309777667576</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.681462655113768</v>
+        <v>1.660957012978234</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1017444368649371</v>
+        <v>0.1020754882386263</v>
       </c>
       <c r="C84">
-        <v>-191.3416097720046</v>
+        <v>-205.9781867971408</v>
       </c>
       <c r="D84">
-        <v>613.7323902279954</v>
+        <v>610.4528132028593</v>
       </c>
       <c r="E84">
-        <v>596.7740000000001</v>
+        <v>608.1310000000001</v>
       </c>
       <c r="F84">
-        <v>931.2740000000001</v>
+        <v>942.6310000000001</v>
       </c>
       <c r="G84">
         <v>126.2</v>
@@ -8175,28 +8175,28 @@
         <v>163.7</v>
       </c>
       <c r="M84">
-        <v>98.55763798875941</v>
+        <v>99.75956040325647</v>
       </c>
       <c r="N84">
-        <v>65.14236201124058</v>
+        <v>63.94043959674352</v>
       </c>
       <c r="O84">
-        <v>13.02847240224812</v>
+        <v>12.7880879193487</v>
       </c>
       <c r="P84">
-        <v>52.11388960899247</v>
+        <v>51.15235167739481</v>
       </c>
       <c r="Q84">
-        <v>158.5138896089925</v>
+        <v>157.5523516773949</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1795517524996894</v>
+        <v>0.1870807000088192</v>
       </c>
       <c r="T84">
-        <v>2.069097073015559</v>
+        <v>2.185567496489556</v>
       </c>
       <c r="U84">
         <v>0.1058309777667576</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.660957012978234</v>
+        <v>1.640945482701388</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1020754882386263</v>
+        <v>0.1024065396123155</v>
       </c>
       <c r="C85">
-        <v>-205.9781867971408</v>
+        <v>-220.5799002344226</v>
       </c>
       <c r="D85">
-        <v>610.4528132028593</v>
+        <v>607.2080997655776</v>
       </c>
       <c r="E85">
-        <v>608.1310000000001</v>
+        <v>619.4880000000002</v>
       </c>
       <c r="F85">
-        <v>942.6310000000001</v>
+        <v>953.9880000000002</v>
       </c>
       <c r="G85">
         <v>126.2</v>
@@ -8257,28 +8257,28 @@
         <v>163.7</v>
       </c>
       <c r="M85">
-        <v>99.75956040325647</v>
+        <v>100.9614828177535</v>
       </c>
       <c r="N85">
-        <v>63.94043959674352</v>
+        <v>62.73851718224644</v>
       </c>
       <c r="O85">
-        <v>12.7880879193487</v>
+        <v>12.54770343644929</v>
       </c>
       <c r="P85">
-        <v>51.15235167739481</v>
+        <v>50.19081374579715</v>
       </c>
       <c r="Q85">
-        <v>157.5523516773949</v>
+        <v>156.5908137457972</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1870807000088192</v>
+        <v>0.1955507659565901</v>
       </c>
       <c r="T85">
-        <v>2.185567496489556</v>
+        <v>2.316596722897803</v>
       </c>
       <c r="U85">
         <v>0.1058309777667576</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.640945482701388</v>
+        <v>1.621410417431133</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1024065396123155</v>
+        <v>0.1027375909860047</v>
       </c>
       <c r="C86">
-        <v>-220.5799002344224</v>
+        <v>-235.1473030713413</v>
       </c>
       <c r="D86">
-        <v>607.2080997655776</v>
+        <v>603.9976969286587</v>
       </c>
       <c r="E86">
-        <v>619.4880000000001</v>
+        <v>630.845</v>
       </c>
       <c r="F86">
-        <v>953.9880000000001</v>
+        <v>965.345</v>
       </c>
       <c r="G86">
         <v>126.2</v>
@@ -8339,28 +8339,28 @@
         <v>163.7</v>
       </c>
       <c r="M86">
-        <v>100.9614828177535</v>
+        <v>102.1634052322506</v>
       </c>
       <c r="N86">
-        <v>62.73851718224645</v>
+        <v>61.53659476774939</v>
       </c>
       <c r="O86">
-        <v>12.54770343644929</v>
+        <v>12.30731895354988</v>
       </c>
       <c r="P86">
-        <v>50.19081374579716</v>
+        <v>49.22927581419951</v>
       </c>
       <c r="Q86">
-        <v>156.5908137457972</v>
+        <v>155.6292758141996</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.19555076595659</v>
+        <v>0.2051501740307304</v>
       </c>
       <c r="T86">
-        <v>2.316596722897802</v>
+        <v>2.465096512827148</v>
       </c>
       <c r="U86">
         <v>0.1058309777667576</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.621410417431134</v>
+        <v>1.602335000755473</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1027375909860047</v>
+        <v>0.1030686423596939</v>
       </c>
       <c r="C87">
-        <v>-235.1473030713413</v>
+        <v>-249.6809366619763</v>
       </c>
       <c r="D87">
-        <v>603.9976969286587</v>
+        <v>600.8210633380237</v>
       </c>
       <c r="E87">
-        <v>630.845</v>
+        <v>642.202</v>
       </c>
       <c r="F87">
-        <v>965.345</v>
+        <v>976.702</v>
       </c>
       <c r="G87">
         <v>126.2</v>
@@ -8421,28 +8421,28 @@
         <v>163.7</v>
       </c>
       <c r="M87">
-        <v>102.1634052322506</v>
+        <v>103.3653276467477</v>
       </c>
       <c r="N87">
-        <v>61.53659476774939</v>
+        <v>60.33467235325233</v>
       </c>
       <c r="O87">
-        <v>12.30731895354988</v>
+        <v>12.06693447065047</v>
       </c>
       <c r="P87">
-        <v>49.22927581419951</v>
+        <v>48.26773788260186</v>
       </c>
       <c r="Q87">
-        <v>155.6292758141996</v>
+        <v>154.6677378826019</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2051501740307304</v>
+        <v>0.2161209261154623</v>
       </c>
       <c r="T87">
-        <v>2.465096512827148</v>
+        <v>2.634810558460687</v>
       </c>
       <c r="U87">
         <v>0.1058309777667576</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.602335000755473</v>
+        <v>1.583703198421107</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1030686423596939</v>
+        <v>0.1033996937333831</v>
       </c>
       <c r="C88">
-        <v>-249.6809366619763</v>
+        <v>-264.181331031314</v>
       </c>
       <c r="D88">
-        <v>600.8210633380237</v>
+        <v>597.677668968686</v>
       </c>
       <c r="E88">
-        <v>642.202</v>
+        <v>653.5590000000001</v>
       </c>
       <c r="F88">
-        <v>976.702</v>
+        <v>988.0590000000001</v>
       </c>
       <c r="G88">
         <v>126.2</v>
@@ -8503,28 +8503,28 @@
         <v>163.7</v>
       </c>
       <c r="M88">
-        <v>103.3653276467477</v>
+        <v>104.5672500612447</v>
       </c>
       <c r="N88">
-        <v>60.33467235325233</v>
+        <v>59.13274993875525</v>
       </c>
       <c r="O88">
-        <v>12.06693447065047</v>
+        <v>11.82654998775105</v>
       </c>
       <c r="P88">
-        <v>48.26773788260186</v>
+        <v>47.3061999510042</v>
       </c>
       <c r="Q88">
-        <v>154.6677378826019</v>
+        <v>153.7061999510042</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2161209261154623</v>
+        <v>0.2287794862132298</v>
       </c>
       <c r="T88">
-        <v>2.634810558460687</v>
+        <v>2.830634457268616</v>
       </c>
       <c r="U88">
         <v>0.1058309777667576</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.583703198421107</v>
+        <v>1.565499713381784</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1033996937333831</v>
+        <v>0.1037307451070724</v>
       </c>
       <c r="C89">
-        <v>-264.181331031314</v>
+        <v>-278.649005170065</v>
       </c>
       <c r="D89">
-        <v>597.677668968686</v>
+        <v>594.566994829935</v>
       </c>
       <c r="E89">
-        <v>653.5590000000001</v>
+        <v>664.9160000000001</v>
       </c>
       <c r="F89">
-        <v>988.0590000000001</v>
+        <v>999.4160000000001</v>
       </c>
       <c r="G89">
         <v>126.2</v>
@@ -8585,28 +8585,28 @@
         <v>163.7</v>
       </c>
       <c r="M89">
-        <v>104.5672500612447</v>
+        <v>105.7691724757418</v>
       </c>
       <c r="N89">
-        <v>59.13274993875525</v>
+        <v>57.93082752425819</v>
       </c>
       <c r="O89">
-        <v>11.82654998775105</v>
+        <v>11.58616550485164</v>
       </c>
       <c r="P89">
-        <v>47.3061999510042</v>
+        <v>46.34466201940656</v>
       </c>
       <c r="Q89">
-        <v>153.7061999510042</v>
+        <v>152.7446620194066</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2287794862132298</v>
+        <v>0.243547806327292</v>
       </c>
       <c r="T89">
-        <v>2.830634457268616</v>
+        <v>3.059095672544534</v>
       </c>
       <c r="U89">
         <v>0.1058309777667576</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.565499713381784</v>
+        <v>1.547709943911537</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1037307451070724</v>
+        <v>0.1040617964807616</v>
       </c>
       <c r="C90">
-        <v>-278.649005170065</v>
+        <v>-293.0844673203227</v>
       </c>
       <c r="D90">
-        <v>594.566994829935</v>
+        <v>591.4885326796773</v>
       </c>
       <c r="E90">
-        <v>664.9160000000001</v>
+        <v>676.273</v>
       </c>
       <c r="F90">
-        <v>999.4160000000001</v>
+        <v>1010.773</v>
       </c>
       <c r="G90">
         <v>126.2</v>
@@ -8667,28 +8667,28 @@
         <v>163.7</v>
       </c>
       <c r="M90">
-        <v>105.7691724757418</v>
+        <v>106.9710948902389</v>
       </c>
       <c r="N90">
-        <v>57.93082752425819</v>
+        <v>56.72890510976113</v>
       </c>
       <c r="O90">
-        <v>11.58616550485164</v>
+        <v>11.34578102195223</v>
       </c>
       <c r="P90">
-        <v>46.34466201940656</v>
+        <v>45.3831240878089</v>
       </c>
       <c r="Q90">
-        <v>152.7446620194066</v>
+        <v>151.7831240878089</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.243547806327292</v>
+        <v>0.2610012755530018</v>
       </c>
       <c r="T90">
-        <v>3.059095672544534</v>
+        <v>3.329095290597891</v>
       </c>
       <c r="U90">
         <v>0.1058309777667576</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.547709943911537</v>
+        <v>1.530319944541744</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1040617964807616</v>
+        <v>0.1043928478544508</v>
       </c>
       <c r="C91">
-        <v>-293.0844673203227</v>
+        <v>-307.4882152523935</v>
       </c>
       <c r="D91">
-        <v>591.4885326796773</v>
+        <v>588.4417847476066</v>
       </c>
       <c r="E91">
-        <v>676.273</v>
+        <v>687.6300000000001</v>
       </c>
       <c r="F91">
-        <v>1010.773</v>
+        <v>1022.13</v>
       </c>
       <c r="G91">
         <v>126.2</v>
@@ -8749,28 +8749,28 @@
         <v>163.7</v>
       </c>
       <c r="M91">
-        <v>106.9710948902389</v>
+        <v>108.1730173047359</v>
       </c>
       <c r="N91">
-        <v>56.72890510976113</v>
+        <v>55.52698269526405</v>
       </c>
       <c r="O91">
-        <v>11.34578102195223</v>
+        <v>11.10539653905281</v>
       </c>
       <c r="P91">
-        <v>45.3831240878089</v>
+        <v>44.42158615621124</v>
       </c>
       <c r="Q91">
-        <v>151.7831240878089</v>
+        <v>150.8215861562113</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2610012755530018</v>
+        <v>0.2819454386238536</v>
       </c>
       <c r="T91">
-        <v>3.329095290597891</v>
+        <v>3.65309483226192</v>
       </c>
       <c r="U91">
         <v>0.1058309777667576</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.530319944541744</v>
+        <v>1.513316389602391</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1043928478544508</v>
+        <v>0.1469815930701214</v>
       </c>
       <c r="C92">
-        <v>-307.4882152523935</v>
+        <v>-553.3707548481361</v>
       </c>
       <c r="D92">
-        <v>588.4417847476066</v>
+        <v>353.916245151864</v>
       </c>
       <c r="E92">
-        <v>687.6300000000001</v>
+        <v>698.9870000000001</v>
       </c>
       <c r="F92">
-        <v>1022.13</v>
+        <v>1033.487</v>
       </c>
       <c r="G92">
         <v>126.2</v>
@@ -8831,45 +8831,45 @@
         <v>163.7</v>
       </c>
       <c r="M92">
-        <v>108.1730173047359</v>
+        <v>168.077001319233</v>
       </c>
       <c r="N92">
-        <v>55.52698269526405</v>
+        <v>-4.377001319233017</v>
       </c>
       <c r="O92">
-        <v>11.10539653905281</v>
+        <v>-0.8754002638466034</v>
       </c>
       <c r="P92">
-        <v>44.42158615621124</v>
+        <v>-3.501601055386414</v>
       </c>
       <c r="Q92">
-        <v>150.8215861562113</v>
+        <v>102.8983989446136</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2819454386238536</v>
+        <v>0.3090604319460724</v>
       </c>
       <c r="T92">
-        <v>3.65309483226192</v>
+        <v>4.072555155355404</v>
       </c>
       <c r="U92">
-        <v>0.1058309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V92">
-        <v>0.2</v>
+        <v>0.194791671335307</v>
       </c>
       <c r="W92">
-        <v>0.08466478221340606</v>
+        <v>0.1309518177966757</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.513316389602391</v>
+        <v>0.9739583566765351</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1469815930701214</v>
+        <v>0.148149902847789</v>
       </c>
       <c r="C93">
-        <v>-553.3707548481361</v>
+        <v>-568.5553660555727</v>
       </c>
       <c r="D93">
-        <v>353.916245151864</v>
+        <v>350.0886339444273</v>
       </c>
       <c r="E93">
-        <v>698.9870000000001</v>
+        <v>710.3440000000001</v>
       </c>
       <c r="F93">
-        <v>1033.487</v>
+        <v>1044.844</v>
       </c>
       <c r="G93">
         <v>126.2</v>
@@ -8913,37 +8913,37 @@
         <v>163.7</v>
       </c>
       <c r="M93">
-        <v>168.077001319233</v>
+        <v>169.9240013337301</v>
       </c>
       <c r="N93">
-        <v>-4.377001319233017</v>
+        <v>-6.224001333730087</v>
       </c>
       <c r="O93">
-        <v>-0.8754002638466034</v>
+        <v>-1.244800266746017</v>
       </c>
       <c r="P93">
-        <v>-3.501601055386414</v>
+        <v>-4.97920106698407</v>
       </c>
       <c r="Q93">
-        <v>102.8983989446136</v>
+        <v>101.420798933016</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3090604319460724</v>
+        <v>0.3419679859393316</v>
       </c>
       <c r="T93">
-        <v>4.072555155355404</v>
+        <v>4.581624549774831</v>
       </c>
       <c r="U93">
         <v>0.1626309777667576</v>
       </c>
       <c r="V93">
-        <v>0.194791671335307</v>
+        <v>0.1926743705599232</v>
       </c>
       <c r="W93">
-        <v>0.1309518177966757</v>
+        <v>0.1312961564920027</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9739583566765351</v>
+        <v>0.9633718527996161</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.148149902847789</v>
+        <v>0.1493182126254566</v>
       </c>
       <c r="C94">
-        <v>-568.5553660555727</v>
+        <v>-583.658071691216</v>
       </c>
       <c r="D94">
-        <v>350.0886339444273</v>
+        <v>346.3429283087839</v>
       </c>
       <c r="E94">
-        <v>710.3440000000001</v>
+        <v>721.701</v>
       </c>
       <c r="F94">
-        <v>1044.844</v>
+        <v>1056.201</v>
       </c>
       <c r="G94">
         <v>126.2</v>
@@ -8995,37 +8995,37 @@
         <v>163.7</v>
       </c>
       <c r="M94">
-        <v>169.9240013337301</v>
+        <v>171.7710013482271</v>
       </c>
       <c r="N94">
-        <v>-6.224001333730087</v>
+        <v>-8.071001348227128</v>
       </c>
       <c r="O94">
-        <v>-1.244800266746017</v>
+        <v>-1.614200269645426</v>
       </c>
       <c r="P94">
-        <v>-4.97920106698407</v>
+        <v>-6.456801078581702</v>
       </c>
       <c r="Q94">
-        <v>101.420798933016</v>
+        <v>99.94319892141833</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3419679859393316</v>
+        <v>0.3842776982163789</v>
       </c>
       <c r="T94">
-        <v>4.581624549774831</v>
+        <v>5.236142342599806</v>
       </c>
       <c r="U94">
         <v>0.1626309777667576</v>
       </c>
       <c r="V94">
-        <v>0.1926743705599232</v>
+        <v>0.1906026031345477</v>
       </c>
       <c r="W94">
-        <v>0.1312961564920027</v>
+        <v>0.1316330900540968</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9633718527996161</v>
+        <v>0.9530130156727387</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1493182126254566</v>
+        <v>0.1504865224031242</v>
       </c>
       <c r="C95">
-        <v>-583.658071691216</v>
+        <v>-598.6814729228524</v>
       </c>
       <c r="D95">
-        <v>346.3429283087839</v>
+        <v>342.6765270771479</v>
       </c>
       <c r="E95">
-        <v>721.701</v>
+        <v>733.0580000000002</v>
       </c>
       <c r="F95">
-        <v>1056.201</v>
+        <v>1067.558</v>
       </c>
       <c r="G95">
         <v>126.2</v>
@@ -9077,37 +9077,37 @@
         <v>163.7</v>
       </c>
       <c r="M95">
-        <v>171.7710013482271</v>
+        <v>173.6180013627242</v>
       </c>
       <c r="N95">
-        <v>-8.071001348227128</v>
+        <v>-9.918001362724226</v>
       </c>
       <c r="O95">
-        <v>-1.614200269645426</v>
+        <v>-1.983600272544845</v>
       </c>
       <c r="P95">
-        <v>-6.456801078581702</v>
+        <v>-7.934401090179381</v>
       </c>
       <c r="Q95">
-        <v>99.94319892141833</v>
+        <v>98.46559890982066</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3842776982163789</v>
+        <v>0.4406906479191089</v>
       </c>
       <c r="T95">
-        <v>5.236142342599806</v>
+        <v>6.108832733033109</v>
       </c>
       <c r="U95">
         <v>0.1626309777667576</v>
       </c>
       <c r="V95">
-        <v>0.1906026031345477</v>
+        <v>0.1885749158671589</v>
       </c>
       <c r="W95">
-        <v>0.1316330900540968</v>
+        <v>0.1319628548169975</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9530130156727387</v>
+        <v>0.9428745793357944</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1504865224031242</v>
+        <v>0.1516548321807917</v>
       </c>
       <c r="C96">
-        <v>-598.6814729228524</v>
+        <v>-613.6280619277456</v>
       </c>
       <c r="D96">
-        <v>342.6765270771479</v>
+        <v>339.0869380722545</v>
       </c>
       <c r="E96">
-        <v>733.0580000000002</v>
+        <v>744.4150000000002</v>
       </c>
       <c r="F96">
-        <v>1067.558</v>
+        <v>1078.915</v>
       </c>
       <c r="G96">
         <v>126.2</v>
@@ -9159,37 +9159,37 @@
         <v>163.7</v>
       </c>
       <c r="M96">
-        <v>173.6180013627242</v>
+        <v>175.4650013772213</v>
       </c>
       <c r="N96">
-        <v>-9.918001362724226</v>
+        <v>-11.7650013772213</v>
       </c>
       <c r="O96">
-        <v>-1.983600272544845</v>
+        <v>-2.353000275444259</v>
       </c>
       <c r="P96">
-        <v>-7.934401090179381</v>
+        <v>-9.412001101777037</v>
       </c>
       <c r="Q96">
-        <v>98.46559890982066</v>
+        <v>96.987998898223</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4406906479191089</v>
+        <v>0.5196687775029308</v>
       </c>
       <c r="T96">
-        <v>6.108832733033109</v>
+        <v>7.330599279639735</v>
       </c>
       <c r="U96">
         <v>0.1626309777667576</v>
       </c>
       <c r="V96">
-        <v>0.1885749158671589</v>
+        <v>0.1865899167527678</v>
       </c>
       <c r="W96">
-        <v>0.1319628548169975</v>
+        <v>0.132285677163837</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9428745793357944</v>
+        <v>0.9329495837638387</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1516548321807917</v>
+        <v>0.1528231419584593</v>
       </c>
       <c r="C97">
-        <v>-613.6280619277456</v>
+        <v>-628.5002275419256</v>
       </c>
       <c r="D97">
-        <v>339.0869380722545</v>
+        <v>335.5717724580746</v>
       </c>
       <c r="E97">
-        <v>744.4150000000002</v>
+        <v>755.7720000000002</v>
       </c>
       <c r="F97">
-        <v>1078.915</v>
+        <v>1090.272</v>
       </c>
       <c r="G97">
         <v>126.2</v>
@@ -9241,37 +9241,37 @@
         <v>163.7</v>
       </c>
       <c r="M97">
-        <v>175.4650013772213</v>
+        <v>177.3120013917184</v>
       </c>
       <c r="N97">
-        <v>-11.7650013772213</v>
+        <v>-13.61200139171837</v>
       </c>
       <c r="O97">
-        <v>-2.353000275444259</v>
+        <v>-2.722400278343673</v>
       </c>
       <c r="P97">
-        <v>-9.412001101777037</v>
+        <v>-10.88960111337469</v>
       </c>
       <c r="Q97">
-        <v>96.987998898223</v>
+        <v>95.51039888662534</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5196687775029308</v>
+        <v>0.6381359718786639</v>
       </c>
       <c r="T97">
-        <v>7.330599279639735</v>
+        <v>9.163249099549674</v>
       </c>
       <c r="U97">
         <v>0.1626309777667576</v>
       </c>
       <c r="V97">
-        <v>0.1865899167527678</v>
+        <v>0.1846462717865931</v>
       </c>
       <c r="W97">
-        <v>0.132285677163837</v>
+        <v>0.1326017740451175</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9329495837638387</v>
+        <v>0.9232313589329654</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1528231419584593</v>
+        <v>0.1539914517361269</v>
       </c>
       <c r="C98">
-        <v>-628.5002275419251</v>
+        <v>-643.3002605616919</v>
       </c>
       <c r="D98">
-        <v>335.5717724580747</v>
+        <v>332.128739438308</v>
       </c>
       <c r="E98">
-        <v>755.7719999999999</v>
+        <v>767.1289999999999</v>
       </c>
       <c r="F98">
-        <v>1090.272</v>
+        <v>1101.629</v>
       </c>
       <c r="G98">
         <v>126.2</v>
@@ -9323,37 +9323,37 @@
         <v>163.7</v>
       </c>
       <c r="M98">
-        <v>177.3120013917183</v>
+        <v>179.1590014062154</v>
       </c>
       <c r="N98">
-        <v>-13.61200139171834</v>
+        <v>-15.45900140621538</v>
       </c>
       <c r="O98">
-        <v>-2.722400278343668</v>
+        <v>-3.091800281243076</v>
       </c>
       <c r="P98">
-        <v>-10.88960111337467</v>
+        <v>-12.3672011249723</v>
       </c>
       <c r="Q98">
-        <v>95.51039888662537</v>
+        <v>94.03279887502774</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6381359718786623</v>
+        <v>0.8355812958382163</v>
       </c>
       <c r="T98">
-        <v>9.163249099549649</v>
+        <v>12.2176654660662</v>
       </c>
       <c r="U98">
         <v>0.1626309777667576</v>
       </c>
       <c r="V98">
-        <v>0.1846462717865931</v>
+        <v>0.1827427019743602</v>
       </c>
       <c r="W98">
-        <v>0.1326017740451175</v>
+        <v>0.1329113534649282</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9232313589329656</v>
+        <v>0.9137135098718011</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1539914517361269</v>
+        <v>0.1551597615137945</v>
       </c>
       <c r="C99">
-        <v>-643.3002605616919</v>
+        <v>-658.0303587220744</v>
       </c>
       <c r="D99">
-        <v>332.128739438308</v>
+        <v>328.7556412779257</v>
       </c>
       <c r="E99">
-        <v>767.1289999999999</v>
+        <v>778.4860000000001</v>
       </c>
       <c r="F99">
-        <v>1101.629</v>
+        <v>1112.986</v>
       </c>
       <c r="G99">
         <v>126.2</v>
@@ -9405,37 +9405,37 @@
         <v>163.7</v>
       </c>
       <c r="M99">
-        <v>179.1590014062154</v>
+        <v>181.0060014207125</v>
       </c>
       <c r="N99">
-        <v>-15.45900140621538</v>
+        <v>-17.30600142071248</v>
       </c>
       <c r="O99">
-        <v>-3.091800281243076</v>
+        <v>-3.461200284142496</v>
       </c>
       <c r="P99">
-        <v>-12.3672011249723</v>
+        <v>-13.84480113656998</v>
       </c>
       <c r="Q99">
-        <v>94.03279887502774</v>
+        <v>92.55519886343005</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8355812958382163</v>
+        <v>1.230471943757325</v>
       </c>
       <c r="T99">
-        <v>12.2176654660662</v>
+        <v>18.3264981990993</v>
       </c>
       <c r="U99">
         <v>0.1626309777667576</v>
       </c>
       <c r="V99">
-        <v>0.1827427019743602</v>
+        <v>0.1808779805256422</v>
       </c>
       <c r="W99">
-        <v>0.1329113534649282</v>
+        <v>0.1332146149373959</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9137135098718011</v>
+        <v>0.9043899026282112</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1551597615137945</v>
+        <v>0.156328071291462</v>
       </c>
       <c r="C100">
-        <v>-658.0303587220744</v>
+        <v>-672.6926313749658</v>
       </c>
       <c r="D100">
-        <v>328.7556412779257</v>
+        <v>325.4503686250343</v>
       </c>
       <c r="E100">
-        <v>778.4860000000001</v>
+        <v>789.8430000000001</v>
       </c>
       <c r="F100">
-        <v>1112.986</v>
+        <v>1124.343</v>
       </c>
       <c r="G100">
         <v>126.2</v>
@@ -9487,37 +9487,37 @@
         <v>163.7</v>
       </c>
       <c r="M100">
-        <v>181.0060014207125</v>
+        <v>182.8530014352095</v>
       </c>
       <c r="N100">
-        <v>-17.30600142071248</v>
+        <v>-19.15300143520955</v>
       </c>
       <c r="O100">
-        <v>-3.461200284142496</v>
+        <v>-3.830600287041909</v>
       </c>
       <c r="P100">
-        <v>-13.84480113656998</v>
+        <v>-15.32240114816764</v>
       </c>
       <c r="Q100">
-        <v>92.55519886343005</v>
+        <v>91.07759885183239</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.230471943757325</v>
+        <v>2.415143887514649</v>
       </c>
       <c r="T100">
-        <v>18.3264981990993</v>
+        <v>36.6529963981986</v>
       </c>
       <c r="U100">
         <v>0.1626309777667576</v>
       </c>
       <c r="V100">
-        <v>0.1808779805256422</v>
+        <v>0.1790509302173024</v>
       </c>
       <c r="W100">
-        <v>0.1332146149373959</v>
+        <v>0.1335117499154702</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.9043899026282112</v>
+        <v>0.895254651086512</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.156328071291462</v>
-      </c>
-      <c r="C101">
-        <v>-672.6926313749658</v>
-      </c>
-      <c r="D101">
-        <v>325.4503686250343</v>
-      </c>
-      <c r="E101">
-        <v>789.8430000000001</v>
-      </c>
-      <c r="F101">
-        <v>1124.343</v>
-      </c>
-      <c r="G101">
-        <v>126.2</v>
-      </c>
-      <c r="H101">
-        <v>801.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>270.1</v>
-      </c>
-      <c r="K101">
-        <v>106.4</v>
-      </c>
-      <c r="L101">
-        <v>163.7</v>
-      </c>
-      <c r="M101">
-        <v>182.8530014352095</v>
-      </c>
-      <c r="N101">
-        <v>-19.15300143520955</v>
-      </c>
-      <c r="O101">
-        <v>-3.830600287041909</v>
-      </c>
-      <c r="P101">
-        <v>-15.32240114816764</v>
-      </c>
-      <c r="Q101">
-        <v>91.07759885183239</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.415143887514649</v>
-      </c>
-      <c r="T101">
-        <v>36.6529963981986</v>
-      </c>
-      <c r="U101">
-        <v>0.1626309777667576</v>
-      </c>
-      <c r="V101">
-        <v>0.1790509302173024</v>
-      </c>
-      <c r="W101">
-        <v>0.1335117499154702</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.895254651086512</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
